--- a/public/data/record.xlsx
+++ b/public/data/record.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\cursor-usage\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB68D755-E1B4-41A5-A919-C9ABCCA1A4B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F19A01C-A8A4-4320-A703-B73BB13244B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19020" yWindow="0" windowWidth="19380" windowHeight="20970" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cursor Usageの記録" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1088" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1092" uniqueCount="31">
   <si>
     <t>番号</t>
   </si>
@@ -10713,7 +10713,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92559261-86B2-49A9-AE5C-FC3176987B65}">
-  <dimension ref="A1:E197"/>
+  <dimension ref="A1:E198"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="5.453125" bestFit="1" customWidth="1"/>
@@ -12108,7 +12108,7 @@
     </row>
     <row r="74" spans="1:5" s="5" customFormat="1" ht="14.5">
       <c r="A74" s="6">
-        <f t="shared" ref="A74:A197" si="2">ROW()-1</f>
+        <f t="shared" ref="A74:A198" si="2">ROW()-1</f>
         <v>73</v>
       </c>
       <c r="B74" s="7">
@@ -14167,7 +14167,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="7">
-        <f t="shared" ref="B179:B197" si="12">B178+1</f>
+        <f t="shared" ref="B179:B198" si="12">B178+1</f>
         <v>46259</v>
       </c>
       <c r="C179" s="6">
@@ -14271,7 +14271,7 @@
         <v>46264</v>
       </c>
       <c r="C184" s="6">
-        <f t="shared" ref="C184:C197" si="13">C183+1</f>
+        <f t="shared" ref="C184:C198" si="13">C183+1</f>
         <v>8</v>
       </c>
       <c r="D184" s="13">
@@ -14538,6 +14538,26 @@
         <v>0</v>
       </c>
       <c r="E197" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5" ht="14" customHeight="1">
+      <c r="A198" s="6">
+        <f t="shared" si="2"/>
+        <v>197</v>
+      </c>
+      <c r="B198" s="7">
+        <f t="shared" si="12"/>
+        <v>46278</v>
+      </c>
+      <c r="C198" s="6">
+        <f t="shared" si="13"/>
+        <v>22</v>
+      </c>
+      <c r="D198" s="13">
+        <v>1438</v>
+      </c>
+      <c r="E198" s="13">
         <v>0</v>
       </c>
     </row>
@@ -14550,7 +14570,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E31F5C3B-0571-4A35-9FD2-A50C21726EAB}">
-  <dimension ref="A1:J767"/>
+  <dimension ref="A1:J769"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="11.36328125" bestFit="1" customWidth="1"/>
@@ -38341,7 +38361,7 @@
     </row>
     <row r="722" spans="1:10">
       <c r="A722" s="24">
-        <f t="shared" ref="A722:A767" si="14">A720+1</f>
+        <f t="shared" ref="A722:A769" si="14">A720+1</f>
         <v>46255</v>
       </c>
       <c r="B722" s="23" t="s">
@@ -39855,6 +39875,72 @@
       </c>
       <c r="J767" s="31">
         <v>0.42699999999999999</v>
+      </c>
+    </row>
+    <row r="768" spans="1:10">
+      <c r="A768" s="24">
+        <f t="shared" si="14"/>
+        <v>46278</v>
+      </c>
+      <c r="B768" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C768" s="25">
+        <v>283804067</v>
+      </c>
+      <c r="D768" s="25">
+        <v>1997206</v>
+      </c>
+      <c r="E768" s="25">
+        <v>16930950</v>
+      </c>
+      <c r="F768" s="25">
+        <v>1975380</v>
+      </c>
+      <c r="G768" s="25">
+        <v>304707603</v>
+      </c>
+      <c r="H768" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I768" s="27">
+        <v>0</v>
+      </c>
+      <c r="J768" s="31">
+        <v>0.443</v>
+      </c>
+    </row>
+    <row r="769" spans="1:10">
+      <c r="A769" s="24">
+        <f t="shared" si="14"/>
+        <v>46278</v>
+      </c>
+      <c r="B769" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C769" s="25">
+        <v>283804067</v>
+      </c>
+      <c r="D769" s="25">
+        <v>1997206</v>
+      </c>
+      <c r="E769" s="25">
+        <v>16930950</v>
+      </c>
+      <c r="F769" s="25">
+        <v>1975380</v>
+      </c>
+      <c r="G769" s="25">
+        <v>304707603</v>
+      </c>
+      <c r="H769" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I769" s="27">
+        <v>0</v>
+      </c>
+      <c r="J769" s="31">
+        <v>0.443</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/record.xlsx
+++ b/public/data/record.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\cursor-usage\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F19A01C-A8A4-4320-A703-B73BB13244B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21C91F8A-10E4-4099-9111-0C6426DA6F2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1092" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1096" uniqueCount="31">
   <si>
     <t>番号</t>
   </si>
@@ -10713,7 +10713,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92559261-86B2-49A9-AE5C-FC3176987B65}">
-  <dimension ref="A1:E198"/>
+  <dimension ref="A1:E199"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="5.453125" bestFit="1" customWidth="1"/>
@@ -12108,7 +12108,7 @@
     </row>
     <row r="74" spans="1:5" s="5" customFormat="1" ht="14.5">
       <c r="A74" s="6">
-        <f t="shared" ref="A74:A198" si="2">ROW()-1</f>
+        <f t="shared" ref="A74:A199" si="2">ROW()-1</f>
         <v>73</v>
       </c>
       <c r="B74" s="7">
@@ -14167,7 +14167,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="7">
-        <f t="shared" ref="B179:B198" si="12">B178+1</f>
+        <f t="shared" ref="B179:B199" si="12">B178+1</f>
         <v>46259</v>
       </c>
       <c r="C179" s="6">
@@ -14271,7 +14271,7 @@
         <v>46264</v>
       </c>
       <c r="C184" s="6">
-        <f t="shared" ref="C184:C198" si="13">C183+1</f>
+        <f t="shared" ref="C184:C199" si="13">C183+1</f>
         <v>8</v>
       </c>
       <c r="D184" s="13">
@@ -14558,6 +14558,26 @@
         <v>1438</v>
       </c>
       <c r="E198" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5" ht="14" customHeight="1">
+      <c r="A199" s="6">
+        <f t="shared" si="2"/>
+        <v>198</v>
+      </c>
+      <c r="B199" s="7">
+        <f t="shared" si="12"/>
+        <v>46279</v>
+      </c>
+      <c r="C199" s="6">
+        <f t="shared" si="13"/>
+        <v>23</v>
+      </c>
+      <c r="D199" s="13">
+        <v>3811</v>
+      </c>
+      <c r="E199" s="13">
         <v>0</v>
       </c>
     </row>
@@ -14570,7 +14590,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E31F5C3B-0571-4A35-9FD2-A50C21726EAB}">
-  <dimension ref="A1:J769"/>
+  <dimension ref="A1:J771"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="11.36328125" bestFit="1" customWidth="1"/>
@@ -38361,7 +38381,7 @@
     </row>
     <row r="722" spans="1:10">
       <c r="A722" s="24">
-        <f t="shared" ref="A722:A769" si="14">A720+1</f>
+        <f t="shared" ref="A722:A771" si="14">A720+1</f>
         <v>46255</v>
       </c>
       <c r="B722" s="23" t="s">
@@ -39941,6 +39961,72 @@
       </c>
       <c r="J769" s="31">
         <v>0.443</v>
+      </c>
+    </row>
+    <row r="770" spans="1:10">
+      <c r="A770" s="24">
+        <f t="shared" si="14"/>
+        <v>46279</v>
+      </c>
+      <c r="B770" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C770" s="25">
+        <v>296058403</v>
+      </c>
+      <c r="D770" s="25">
+        <v>1997206</v>
+      </c>
+      <c r="E770" s="25">
+        <v>17529151</v>
+      </c>
+      <c r="F770" s="25">
+        <v>2075371</v>
+      </c>
+      <c r="G770" s="25">
+        <v>317660131</v>
+      </c>
+      <c r="H770" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I770" s="27">
+        <v>0</v>
+      </c>
+      <c r="J770" s="31">
+        <v>0.46100000000000002</v>
+      </c>
+    </row>
+    <row r="771" spans="1:10">
+      <c r="A771" s="24">
+        <f t="shared" si="14"/>
+        <v>46279</v>
+      </c>
+      <c r="B771" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C771" s="25">
+        <v>296058403</v>
+      </c>
+      <c r="D771" s="25">
+        <v>1997206</v>
+      </c>
+      <c r="E771" s="25">
+        <v>17529151</v>
+      </c>
+      <c r="F771" s="25">
+        <v>2075371</v>
+      </c>
+      <c r="G771" s="25">
+        <v>317660131</v>
+      </c>
+      <c r="H771" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I771" s="27">
+        <v>0</v>
+      </c>
+      <c r="J771" s="31">
+        <v>0.46100000000000002</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/record.xlsx
+++ b/public/data/record.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\cursor-usage\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21C91F8A-10E4-4099-9111-0C6426DA6F2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2CEBD8D-1738-4D44-B95B-E968234D6ACD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1096" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1100" uniqueCount="31">
   <si>
     <t>番号</t>
   </si>
@@ -10713,7 +10713,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92559261-86B2-49A9-AE5C-FC3176987B65}">
-  <dimension ref="A1:E199"/>
+  <dimension ref="A1:E200"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="5.453125" bestFit="1" customWidth="1"/>
@@ -12108,7 +12108,7 @@
     </row>
     <row r="74" spans="1:5" s="5" customFormat="1" ht="14.5">
       <c r="A74" s="6">
-        <f t="shared" ref="A74:A199" si="2">ROW()-1</f>
+        <f t="shared" ref="A74:A200" si="2">ROW()-1</f>
         <v>73</v>
       </c>
       <c r="B74" s="7">
@@ -14167,7 +14167,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="7">
-        <f t="shared" ref="B179:B199" si="12">B178+1</f>
+        <f t="shared" ref="B179:B200" si="12">B178+1</f>
         <v>46259</v>
       </c>
       <c r="C179" s="6">
@@ -14271,7 +14271,7 @@
         <v>46264</v>
       </c>
       <c r="C184" s="6">
-        <f t="shared" ref="C184:C199" si="13">C183+1</f>
+        <f t="shared" ref="C184:C200" si="13">C183+1</f>
         <v>8</v>
       </c>
       <c r="D184" s="13">
@@ -14578,6 +14578,26 @@
         <v>3811</v>
       </c>
       <c r="E199" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5" ht="14" customHeight="1">
+      <c r="A200" s="6">
+        <f t="shared" si="2"/>
+        <v>199</v>
+      </c>
+      <c r="B200" s="7">
+        <f t="shared" si="12"/>
+        <v>46280</v>
+      </c>
+      <c r="C200" s="6">
+        <f t="shared" si="13"/>
+        <v>24</v>
+      </c>
+      <c r="D200" s="13">
+        <v>6388</v>
+      </c>
+      <c r="E200" s="13">
         <v>0</v>
       </c>
     </row>
@@ -14590,7 +14610,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E31F5C3B-0571-4A35-9FD2-A50C21726EAB}">
-  <dimension ref="A1:J771"/>
+  <dimension ref="A1:J773"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="11.36328125" bestFit="1" customWidth="1"/>
@@ -38381,7 +38401,7 @@
     </row>
     <row r="722" spans="1:10">
       <c r="A722" s="24">
-        <f t="shared" ref="A722:A771" si="14">A720+1</f>
+        <f t="shared" ref="A722:A773" si="14">A720+1</f>
         <v>46255</v>
       </c>
       <c r="B722" s="23" t="s">
@@ -40027,6 +40047,72 @@
       </c>
       <c r="J771" s="31">
         <v>0.46100000000000002</v>
+      </c>
+    </row>
+    <row r="772" spans="1:10">
+      <c r="A772" s="24">
+        <f t="shared" si="14"/>
+        <v>46280</v>
+      </c>
+      <c r="B772" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C772" s="25">
+        <v>306733603</v>
+      </c>
+      <c r="D772" s="25">
+        <v>1997206</v>
+      </c>
+      <c r="E772" s="25">
+        <v>18716309</v>
+      </c>
+      <c r="F772" s="25">
+        <v>2142671</v>
+      </c>
+      <c r="G772" s="25">
+        <v>329589789</v>
+      </c>
+      <c r="H772" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I772" s="27">
+        <v>0</v>
+      </c>
+      <c r="J772" s="31">
+        <v>0.47899999999999998</v>
+      </c>
+    </row>
+    <row r="773" spans="1:10">
+      <c r="A773" s="24">
+        <f t="shared" si="14"/>
+        <v>46280</v>
+      </c>
+      <c r="B773" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C773" s="25">
+        <v>306733603</v>
+      </c>
+      <c r="D773" s="25">
+        <v>1997206</v>
+      </c>
+      <c r="E773" s="25">
+        <v>18716309</v>
+      </c>
+      <c r="F773" s="25">
+        <v>2142671</v>
+      </c>
+      <c r="G773" s="25">
+        <v>329589789</v>
+      </c>
+      <c r="H773" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I773" s="27">
+        <v>0</v>
+      </c>
+      <c r="J773" s="31">
+        <v>0.47899999999999998</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/record.xlsx
+++ b/public/data/record.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\cursor-usage\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2CEBD8D-1738-4D44-B95B-E968234D6ACD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B83EAC1-372E-4560-9FC9-BA44C03DFC57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1100" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1104" uniqueCount="31">
   <si>
     <t>番号</t>
   </si>
@@ -10713,7 +10713,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92559261-86B2-49A9-AE5C-FC3176987B65}">
-  <dimension ref="A1:E200"/>
+  <dimension ref="A1:E201"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="5.453125" bestFit="1" customWidth="1"/>
@@ -12108,7 +12108,7 @@
     </row>
     <row r="74" spans="1:5" s="5" customFormat="1" ht="14.5">
       <c r="A74" s="6">
-        <f t="shared" ref="A74:A200" si="2">ROW()-1</f>
+        <f t="shared" ref="A74:A201" si="2">ROW()-1</f>
         <v>73</v>
       </c>
       <c r="B74" s="7">
@@ -14167,7 +14167,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="7">
-        <f t="shared" ref="B179:B200" si="12">B178+1</f>
+        <f t="shared" ref="B179:B201" si="12">B178+1</f>
         <v>46259</v>
       </c>
       <c r="C179" s="6">
@@ -14271,7 +14271,7 @@
         <v>46264</v>
       </c>
       <c r="C184" s="6">
-        <f t="shared" ref="C184:C200" si="13">C183+1</f>
+        <f t="shared" ref="C184:C201" si="13">C183+1</f>
         <v>8</v>
       </c>
       <c r="D184" s="13">
@@ -14598,6 +14598,26 @@
         <v>6388</v>
       </c>
       <c r="E200" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5" ht="14" customHeight="1">
+      <c r="A201" s="6">
+        <f t="shared" si="2"/>
+        <v>200</v>
+      </c>
+      <c r="B201" s="7">
+        <f t="shared" si="12"/>
+        <v>46281</v>
+      </c>
+      <c r="C201" s="6">
+        <f t="shared" si="13"/>
+        <v>25</v>
+      </c>
+      <c r="D201" s="13">
+        <v>0</v>
+      </c>
+      <c r="E201" s="13">
         <v>0</v>
       </c>
     </row>
@@ -14610,7 +14630,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E31F5C3B-0571-4A35-9FD2-A50C21726EAB}">
-  <dimension ref="A1:J773"/>
+  <dimension ref="A1:J775"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="11.36328125" bestFit="1" customWidth="1"/>
@@ -38401,7 +38421,7 @@
     </row>
     <row r="722" spans="1:10">
       <c r="A722" s="24">
-        <f t="shared" ref="A722:A773" si="14">A720+1</f>
+        <f t="shared" ref="A722:A775" si="14">A720+1</f>
         <v>46255</v>
       </c>
       <c r="B722" s="23" t="s">
@@ -40112,6 +40132,72 @@
         <v>0</v>
       </c>
       <c r="J773" s="31">
+        <v>0.47899999999999998</v>
+      </c>
+    </row>
+    <row r="774" spans="1:10">
+      <c r="A774" s="24">
+        <f t="shared" si="14"/>
+        <v>46281</v>
+      </c>
+      <c r="B774" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C774" s="25">
+        <v>306733603</v>
+      </c>
+      <c r="D774" s="25">
+        <v>1997206</v>
+      </c>
+      <c r="E774" s="25">
+        <v>18716309</v>
+      </c>
+      <c r="F774" s="25">
+        <v>2142671</v>
+      </c>
+      <c r="G774" s="25">
+        <v>329589789</v>
+      </c>
+      <c r="H774" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I774" s="27">
+        <v>0</v>
+      </c>
+      <c r="J774" s="31">
+        <v>0.47899999999999998</v>
+      </c>
+    </row>
+    <row r="775" spans="1:10">
+      <c r="A775" s="24">
+        <f t="shared" si="14"/>
+        <v>46281</v>
+      </c>
+      <c r="B775" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C775" s="25">
+        <v>306733603</v>
+      </c>
+      <c r="D775" s="25">
+        <v>1997206</v>
+      </c>
+      <c r="E775" s="25">
+        <v>18716309</v>
+      </c>
+      <c r="F775" s="25">
+        <v>2142671</v>
+      </c>
+      <c r="G775" s="25">
+        <v>329589789</v>
+      </c>
+      <c r="H775" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I775" s="27">
+        <v>0</v>
+      </c>
+      <c r="J775" s="31">
         <v>0.47899999999999998</v>
       </c>
     </row>

--- a/public/data/record.xlsx
+++ b/public/data/record.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\cursor-usage\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B83EAC1-372E-4560-9FC9-BA44C03DFC57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9115572C-4E5F-448D-BDAD-788404F12450}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1104" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1108" uniqueCount="31">
   <si>
     <t>番号</t>
   </si>
@@ -10713,7 +10713,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92559261-86B2-49A9-AE5C-FC3176987B65}">
-  <dimension ref="A1:E201"/>
+  <dimension ref="A1:E202"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="5.453125" bestFit="1" customWidth="1"/>
@@ -12108,7 +12108,7 @@
     </row>
     <row r="74" spans="1:5" s="5" customFormat="1" ht="14.5">
       <c r="A74" s="6">
-        <f t="shared" ref="A74:A201" si="2">ROW()-1</f>
+        <f t="shared" ref="A74:A202" si="2">ROW()-1</f>
         <v>73</v>
       </c>
       <c r="B74" s="7">
@@ -14167,7 +14167,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="7">
-        <f t="shared" ref="B179:B201" si="12">B178+1</f>
+        <f t="shared" ref="B179:B202" si="12">B178+1</f>
         <v>46259</v>
       </c>
       <c r="C179" s="6">
@@ -14271,7 +14271,7 @@
         <v>46264</v>
       </c>
       <c r="C184" s="6">
-        <f t="shared" ref="C184:C201" si="13">C183+1</f>
+        <f t="shared" ref="C184:C202" si="13">C183+1</f>
         <v>8</v>
       </c>
       <c r="D184" s="13">
@@ -14618,6 +14618,26 @@
         <v>0</v>
       </c>
       <c r="E201" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5" ht="14" customHeight="1">
+      <c r="A202" s="6">
+        <f t="shared" si="2"/>
+        <v>201</v>
+      </c>
+      <c r="B202" s="7">
+        <f t="shared" si="12"/>
+        <v>46282</v>
+      </c>
+      <c r="C202" s="6">
+        <f t="shared" si="13"/>
+        <v>26</v>
+      </c>
+      <c r="D202" s="13">
+        <v>5144</v>
+      </c>
+      <c r="E202" s="13">
         <v>0</v>
       </c>
     </row>
@@ -14630,7 +14650,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E31F5C3B-0571-4A35-9FD2-A50C21726EAB}">
-  <dimension ref="A1:J775"/>
+  <dimension ref="A1:J777"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="11.36328125" bestFit="1" customWidth="1"/>
@@ -38421,7 +38441,7 @@
     </row>
     <row r="722" spans="1:10">
       <c r="A722" s="24">
-        <f t="shared" ref="A722:A775" si="14">A720+1</f>
+        <f t="shared" ref="A722:A777" si="14">A720+1</f>
         <v>46255</v>
       </c>
       <c r="B722" s="23" t="s">
@@ -40199,6 +40219,72 @@
       </c>
       <c r="J775" s="31">
         <v>0.47899999999999998</v>
+      </c>
+    </row>
+    <row r="776" spans="1:10">
+      <c r="A776" s="24">
+        <f t="shared" si="14"/>
+        <v>46282</v>
+      </c>
+      <c r="B776" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C776" s="25">
+        <v>317947299</v>
+      </c>
+      <c r="D776" s="25">
+        <v>1997206</v>
+      </c>
+      <c r="E776" s="25">
+        <v>19736475</v>
+      </c>
+      <c r="F776" s="25">
+        <v>2247798</v>
+      </c>
+      <c r="G776" s="25">
+        <v>341928778</v>
+      </c>
+      <c r="H776" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I776" s="27">
+        <v>0</v>
+      </c>
+      <c r="J776" s="31">
+        <v>0.498</v>
+      </c>
+    </row>
+    <row r="777" spans="1:10">
+      <c r="A777" s="24">
+        <f t="shared" si="14"/>
+        <v>46282</v>
+      </c>
+      <c r="B777" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C777" s="25">
+        <v>317947299</v>
+      </c>
+      <c r="D777" s="25">
+        <v>1997206</v>
+      </c>
+      <c r="E777" s="25">
+        <v>19736475</v>
+      </c>
+      <c r="F777" s="25">
+        <v>2247798</v>
+      </c>
+      <c r="G777" s="25">
+        <v>341928778</v>
+      </c>
+      <c r="H777" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I777" s="27">
+        <v>0</v>
+      </c>
+      <c r="J777" s="31">
+        <v>0.498</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/record.xlsx
+++ b/public/data/record.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\cursor-usage\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9115572C-4E5F-448D-BDAD-788404F12450}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8C4C316-9565-4CDA-AB34-A5E2861F1CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1108" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1112" uniqueCount="31">
   <si>
     <t>番号</t>
   </si>
@@ -10713,7 +10713,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92559261-86B2-49A9-AE5C-FC3176987B65}">
-  <dimension ref="A1:E202"/>
+  <dimension ref="A1:E203"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="5.453125" bestFit="1" customWidth="1"/>
@@ -12108,7 +12108,7 @@
     </row>
     <row r="74" spans="1:5" s="5" customFormat="1" ht="14.5">
       <c r="A74" s="6">
-        <f t="shared" ref="A74:A202" si="2">ROW()-1</f>
+        <f t="shared" ref="A74:A203" si="2">ROW()-1</f>
         <v>73</v>
       </c>
       <c r="B74" s="7">
@@ -14167,7 +14167,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="7">
-        <f t="shared" ref="B179:B202" si="12">B178+1</f>
+        <f t="shared" ref="B179:B203" si="12">B178+1</f>
         <v>46259</v>
       </c>
       <c r="C179" s="6">
@@ -14271,7 +14271,7 @@
         <v>46264</v>
       </c>
       <c r="C184" s="6">
-        <f t="shared" ref="C184:C202" si="13">C183+1</f>
+        <f t="shared" ref="C184:C203" si="13">C183+1</f>
         <v>8</v>
       </c>
       <c r="D184" s="13">
@@ -14638,6 +14638,26 @@
         <v>5144</v>
       </c>
       <c r="E202" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5" ht="14" customHeight="1">
+      <c r="A203" s="6">
+        <f t="shared" si="2"/>
+        <v>202</v>
+      </c>
+      <c r="B203" s="7">
+        <f t="shared" si="12"/>
+        <v>46283</v>
+      </c>
+      <c r="C203" s="6">
+        <f t="shared" si="13"/>
+        <v>27</v>
+      </c>
+      <c r="D203" s="13">
+        <v>0</v>
+      </c>
+      <c r="E203" s="13">
         <v>0</v>
       </c>
     </row>
@@ -14650,7 +14670,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E31F5C3B-0571-4A35-9FD2-A50C21726EAB}">
-  <dimension ref="A1:J777"/>
+  <dimension ref="A1:J779"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="11.36328125" bestFit="1" customWidth="1"/>
@@ -38441,7 +38461,7 @@
     </row>
     <row r="722" spans="1:10">
       <c r="A722" s="24">
-        <f t="shared" ref="A722:A777" si="14">A720+1</f>
+        <f t="shared" ref="A722:A779" si="14">A720+1</f>
         <v>46255</v>
       </c>
       <c r="B722" s="23" t="s">
@@ -40284,6 +40304,72 @@
         <v>0</v>
       </c>
       <c r="J777" s="31">
+        <v>0.498</v>
+      </c>
+    </row>
+    <row r="778" spans="1:10">
+      <c r="A778" s="24">
+        <f t="shared" si="14"/>
+        <v>46283</v>
+      </c>
+      <c r="B778" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C778" s="25">
+        <v>317947299</v>
+      </c>
+      <c r="D778" s="25">
+        <v>1997206</v>
+      </c>
+      <c r="E778" s="25">
+        <v>19736475</v>
+      </c>
+      <c r="F778" s="25">
+        <v>2247798</v>
+      </c>
+      <c r="G778" s="25">
+        <v>341928778</v>
+      </c>
+      <c r="H778" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I778" s="27">
+        <v>0</v>
+      </c>
+      <c r="J778" s="31">
+        <v>0.498</v>
+      </c>
+    </row>
+    <row r="779" spans="1:10">
+      <c r="A779" s="24">
+        <f t="shared" si="14"/>
+        <v>46283</v>
+      </c>
+      <c r="B779" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C779" s="25">
+        <v>317947299</v>
+      </c>
+      <c r="D779" s="25">
+        <v>1997206</v>
+      </c>
+      <c r="E779" s="25">
+        <v>19736475</v>
+      </c>
+      <c r="F779" s="25">
+        <v>2247798</v>
+      </c>
+      <c r="G779" s="25">
+        <v>341928778</v>
+      </c>
+      <c r="H779" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I779" s="27">
+        <v>0</v>
+      </c>
+      <c r="J779" s="31">
         <v>0.498</v>
       </c>
     </row>

--- a/public/data/record.xlsx
+++ b/public/data/record.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\cursor-usage\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8C4C316-9565-4CDA-AB34-A5E2861F1CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFDB82E5-CB49-4A10-ACB0-3C2D4EFB62A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1112" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1116" uniqueCount="31">
   <si>
     <t>番号</t>
   </si>
@@ -10713,7 +10713,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92559261-86B2-49A9-AE5C-FC3176987B65}">
-  <dimension ref="A1:E203"/>
+  <dimension ref="A1:E204"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="5.453125" bestFit="1" customWidth="1"/>
@@ -12108,7 +12108,7 @@
     </row>
     <row r="74" spans="1:5" s="5" customFormat="1" ht="14.5">
       <c r="A74" s="6">
-        <f t="shared" ref="A74:A203" si="2">ROW()-1</f>
+        <f t="shared" ref="A74:A204" si="2">ROW()-1</f>
         <v>73</v>
       </c>
       <c r="B74" s="7">
@@ -14167,7 +14167,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="7">
-        <f t="shared" ref="B179:B203" si="12">B178+1</f>
+        <f t="shared" ref="B179:B204" si="12">B178+1</f>
         <v>46259</v>
       </c>
       <c r="C179" s="6">
@@ -14271,7 +14271,7 @@
         <v>46264</v>
       </c>
       <c r="C184" s="6">
-        <f t="shared" ref="C184:C203" si="13">C183+1</f>
+        <f t="shared" ref="C184:C204" si="13">C183+1</f>
         <v>8</v>
       </c>
       <c r="D184" s="13">
@@ -14659,6 +14659,26 @@
       </c>
       <c r="E203" s="13">
         <v>0</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5" ht="14" customHeight="1">
+      <c r="A204" s="6">
+        <f t="shared" si="2"/>
+        <v>203</v>
+      </c>
+      <c r="B204" s="7">
+        <f t="shared" si="12"/>
+        <v>46284</v>
+      </c>
+      <c r="C204" s="6">
+        <f t="shared" si="13"/>
+        <v>28</v>
+      </c>
+      <c r="D204" s="13">
+        <v>285</v>
+      </c>
+      <c r="E204" s="13">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -14670,7 +14690,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E31F5C3B-0571-4A35-9FD2-A50C21726EAB}">
-  <dimension ref="A1:J779"/>
+  <dimension ref="A1:J781"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="11.36328125" bestFit="1" customWidth="1"/>
@@ -38461,7 +38481,7 @@
     </row>
     <row r="722" spans="1:10">
       <c r="A722" s="24">
-        <f t="shared" ref="A722:A779" si="14">A720+1</f>
+        <f t="shared" ref="A722:A781" si="14">A720+1</f>
         <v>46255</v>
       </c>
       <c r="B722" s="23" t="s">
@@ -40370,6 +40390,72 @@
         <v>0</v>
       </c>
       <c r="J779" s="31">
+        <v>0.498</v>
+      </c>
+    </row>
+    <row r="780" spans="1:10">
+      <c r="A780" s="24">
+        <f t="shared" si="14"/>
+        <v>46284</v>
+      </c>
+      <c r="B780" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C780" s="25">
+        <v>318022307</v>
+      </c>
+      <c r="D780" s="25">
+        <v>1997206</v>
+      </c>
+      <c r="E780" s="25">
+        <v>19783148</v>
+      </c>
+      <c r="F780" s="25">
+        <v>2250501</v>
+      </c>
+      <c r="G780" s="25">
+        <v>342053162</v>
+      </c>
+      <c r="H780" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I780" s="27">
+        <v>0</v>
+      </c>
+      <c r="J780" s="31">
+        <v>0.498</v>
+      </c>
+    </row>
+    <row r="781" spans="1:10">
+      <c r="A781" s="24">
+        <f t="shared" si="14"/>
+        <v>46284</v>
+      </c>
+      <c r="B781" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C781" s="25">
+        <v>318022307</v>
+      </c>
+      <c r="D781" s="25">
+        <v>1997206</v>
+      </c>
+      <c r="E781" s="25">
+        <v>19783148</v>
+      </c>
+      <c r="F781" s="25">
+        <v>2250501</v>
+      </c>
+      <c r="G781" s="25">
+        <v>342053162</v>
+      </c>
+      <c r="H781" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I781" s="27">
+        <v>0</v>
+      </c>
+      <c r="J781" s="31">
         <v>0.498</v>
       </c>
     </row>

--- a/public/data/record.xlsx
+++ b/public/data/record.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\cursor-usage\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFDB82E5-CB49-4A10-ACB0-3C2D4EFB62A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C13C5020-DBC1-481D-9B02-E706C30F3C1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19020" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cursor Usageの記録" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1116" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1120" uniqueCount="31">
   <si>
     <t>番号</t>
   </si>
@@ -10713,7 +10713,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92559261-86B2-49A9-AE5C-FC3176987B65}">
-  <dimension ref="A1:E204"/>
+  <dimension ref="A1:E205"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="5.453125" bestFit="1" customWidth="1"/>
@@ -12108,7 +12108,7 @@
     </row>
     <row r="74" spans="1:5" s="5" customFormat="1" ht="14.5">
       <c r="A74" s="6">
-        <f t="shared" ref="A74:A204" si="2">ROW()-1</f>
+        <f t="shared" ref="A74:A205" si="2">ROW()-1</f>
         <v>73</v>
       </c>
       <c r="B74" s="7">
@@ -14167,7 +14167,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="7">
-        <f t="shared" ref="B179:B204" si="12">B178+1</f>
+        <f t="shared" ref="B179:B205" si="12">B178+1</f>
         <v>46259</v>
       </c>
       <c r="C179" s="6">
@@ -14271,7 +14271,7 @@
         <v>46264</v>
       </c>
       <c r="C184" s="6">
-        <f t="shared" ref="C184:C204" si="13">C183+1</f>
+        <f t="shared" ref="C184:C205" si="13">C183+1</f>
         <v>8</v>
       </c>
       <c r="D184" s="13">
@@ -14679,6 +14679,26 @@
       </c>
       <c r="E204" s="13">
         <v>1</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5" ht="14" customHeight="1">
+      <c r="A205" s="6">
+        <f t="shared" si="2"/>
+        <v>204</v>
+      </c>
+      <c r="B205" s="7">
+        <f t="shared" si="12"/>
+        <v>46285</v>
+      </c>
+      <c r="C205" s="6">
+        <f t="shared" si="13"/>
+        <v>29</v>
+      </c>
+      <c r="D205" s="13">
+        <v>2341</v>
+      </c>
+      <c r="E205" s="13">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -14690,7 +14710,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E31F5C3B-0571-4A35-9FD2-A50C21726EAB}">
-  <dimension ref="A1:J781"/>
+  <dimension ref="A1:J783"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="11.36328125" bestFit="1" customWidth="1"/>
@@ -38481,7 +38501,7 @@
     </row>
     <row r="722" spans="1:10">
       <c r="A722" s="24">
-        <f t="shared" ref="A722:A781" si="14">A720+1</f>
+        <f t="shared" ref="A722:A783" si="14">A720+1</f>
         <v>46255</v>
       </c>
       <c r="B722" s="23" t="s">
@@ -40457,6 +40477,72 @@
       </c>
       <c r="J781" s="31">
         <v>0.498</v>
+      </c>
+    </row>
+    <row r="782" spans="1:10">
+      <c r="A782" s="24">
+        <f t="shared" si="14"/>
+        <v>46285</v>
+      </c>
+      <c r="B782" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C782" s="25">
+        <v>327720739</v>
+      </c>
+      <c r="D782" s="25">
+        <v>1997206</v>
+      </c>
+      <c r="E782" s="25">
+        <v>20485842</v>
+      </c>
+      <c r="F782" s="25">
+        <v>2323883</v>
+      </c>
+      <c r="G782" s="25">
+        <v>352527670</v>
+      </c>
+      <c r="H782" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I782" s="27">
+        <v>0</v>
+      </c>
+      <c r="J782" s="31">
+        <v>0.51300000000000001</v>
+      </c>
+    </row>
+    <row r="783" spans="1:10">
+      <c r="A783" s="24">
+        <f t="shared" si="14"/>
+        <v>46285</v>
+      </c>
+      <c r="B783" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C783" s="25">
+        <v>327720739</v>
+      </c>
+      <c r="D783" s="25">
+        <v>1997206</v>
+      </c>
+      <c r="E783" s="25">
+        <v>20485842</v>
+      </c>
+      <c r="F783" s="25">
+        <v>2323883</v>
+      </c>
+      <c r="G783" s="25">
+        <v>352527670</v>
+      </c>
+      <c r="H783" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I783" s="27">
+        <v>0</v>
+      </c>
+      <c r="J783" s="31">
+        <v>0.51300000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/record.xlsx
+++ b/public/data/record.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\cursor-usage\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C13C5020-DBC1-481D-9B02-E706C30F3C1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B82509FC-1E7C-4E9A-B68A-18957AE87B33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19020" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cursor Usageの記録" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1120" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1124" uniqueCount="31">
   <si>
     <t>番号</t>
   </si>
@@ -10713,7 +10713,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92559261-86B2-49A9-AE5C-FC3176987B65}">
-  <dimension ref="A1:E205"/>
+  <dimension ref="A1:E206"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="5.453125" bestFit="1" customWidth="1"/>
@@ -12108,7 +12108,7 @@
     </row>
     <row r="74" spans="1:5" s="5" customFormat="1" ht="14.5">
       <c r="A74" s="6">
-        <f t="shared" ref="A74:A205" si="2">ROW()-1</f>
+        <f t="shared" ref="A74:A206" si="2">ROW()-1</f>
         <v>73</v>
       </c>
       <c r="B74" s="7">
@@ -14167,7 +14167,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="7">
-        <f t="shared" ref="B179:B205" si="12">B178+1</f>
+        <f t="shared" ref="B179:B206" si="12">B178+1</f>
         <v>46259</v>
       </c>
       <c r="C179" s="6">
@@ -14271,7 +14271,7 @@
         <v>46264</v>
       </c>
       <c r="C184" s="6">
-        <f t="shared" ref="C184:C205" si="13">C183+1</f>
+        <f t="shared" ref="C184:C206" si="13">C183+1</f>
         <v>8</v>
       </c>
       <c r="D184" s="13">
@@ -14698,6 +14698,26 @@
         <v>2341</v>
       </c>
       <c r="E205" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5" ht="14" customHeight="1">
+      <c r="A206" s="6">
+        <f t="shared" si="2"/>
+        <v>205</v>
+      </c>
+      <c r="B206" s="7">
+        <f t="shared" si="12"/>
+        <v>46286</v>
+      </c>
+      <c r="C206" s="6">
+        <f t="shared" si="13"/>
+        <v>30</v>
+      </c>
+      <c r="D206" s="13">
+        <v>272</v>
+      </c>
+      <c r="E206" s="13">
         <v>0</v>
       </c>
     </row>
@@ -14710,7 +14730,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E31F5C3B-0571-4A35-9FD2-A50C21726EAB}">
-  <dimension ref="A1:J783"/>
+  <dimension ref="A1:J785"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="11.36328125" bestFit="1" customWidth="1"/>
@@ -38501,7 +38521,7 @@
     </row>
     <row r="722" spans="1:10">
       <c r="A722" s="24">
-        <f t="shared" ref="A722:A783" si="14">A720+1</f>
+        <f t="shared" ref="A722:A785" si="14">A720+1</f>
         <v>46255</v>
       </c>
       <c r="B722" s="23" t="s">
@@ -40543,6 +40563,72 @@
       </c>
       <c r="J783" s="31">
         <v>0.51300000000000001</v>
+      </c>
+    </row>
+    <row r="784" spans="1:10">
+      <c r="A784" s="24">
+        <f t="shared" si="14"/>
+        <v>46286</v>
+      </c>
+      <c r="B784" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C784" s="25">
+        <v>328692771</v>
+      </c>
+      <c r="D784" s="25">
+        <v>1997206</v>
+      </c>
+      <c r="E784" s="25">
+        <v>20727285</v>
+      </c>
+      <c r="F784" s="25">
+        <v>2335576</v>
+      </c>
+      <c r="G784" s="25">
+        <v>353752838</v>
+      </c>
+      <c r="H784" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I784" s="27">
+        <v>0</v>
+      </c>
+      <c r="J784" s="31">
+        <v>0.51500000000000001</v>
+      </c>
+    </row>
+    <row r="785" spans="1:10">
+      <c r="A785" s="24">
+        <f t="shared" si="14"/>
+        <v>46286</v>
+      </c>
+      <c r="B785" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C785" s="25">
+        <v>328692771</v>
+      </c>
+      <c r="D785" s="25">
+        <v>1997206</v>
+      </c>
+      <c r="E785" s="25">
+        <v>20727285</v>
+      </c>
+      <c r="F785" s="25">
+        <v>2335576</v>
+      </c>
+      <c r="G785" s="25">
+        <v>353752838</v>
+      </c>
+      <c r="H785" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I785" s="27">
+        <v>0</v>
+      </c>
+      <c r="J785" s="31">
+        <v>0.51500000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/record.xlsx
+++ b/public/data/record.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\cursor-usage\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B82509FC-1E7C-4E9A-B68A-18957AE87B33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58A01297-5557-4D43-A433-1D72FC2BF58C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1124" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1128" uniqueCount="31">
   <si>
     <t>番号</t>
   </si>
@@ -10713,7 +10713,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92559261-86B2-49A9-AE5C-FC3176987B65}">
-  <dimension ref="A1:E206"/>
+  <dimension ref="A1:E207"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="5.453125" bestFit="1" customWidth="1"/>
@@ -12108,7 +12108,7 @@
     </row>
     <row r="74" spans="1:5" s="5" customFormat="1" ht="14.5">
       <c r="A74" s="6">
-        <f t="shared" ref="A74:A206" si="2">ROW()-1</f>
+        <f t="shared" ref="A74:A207" si="2">ROW()-1</f>
         <v>73</v>
       </c>
       <c r="B74" s="7">
@@ -14167,7 +14167,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="7">
-        <f t="shared" ref="B179:B206" si="12">B178+1</f>
+        <f t="shared" ref="B179:B207" si="12">B178+1</f>
         <v>46259</v>
       </c>
       <c r="C179" s="6">
@@ -14271,7 +14271,7 @@
         <v>46264</v>
       </c>
       <c r="C184" s="6">
-        <f t="shared" ref="C184:C206" si="13">C183+1</f>
+        <f t="shared" ref="C184:C207" si="13">C183+1</f>
         <v>8</v>
       </c>
       <c r="D184" s="13">
@@ -14718,6 +14718,26 @@
         <v>272</v>
       </c>
       <c r="E206" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5" ht="14" customHeight="1">
+      <c r="A207" s="6">
+        <f t="shared" si="2"/>
+        <v>206</v>
+      </c>
+      <c r="B207" s="7">
+        <f t="shared" si="12"/>
+        <v>46287</v>
+      </c>
+      <c r="C207" s="6">
+        <f t="shared" si="13"/>
+        <v>31</v>
+      </c>
+      <c r="D207" s="13">
+        <v>1436</v>
+      </c>
+      <c r="E207" s="13">
         <v>0</v>
       </c>
     </row>
@@ -14730,7 +14750,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E31F5C3B-0571-4A35-9FD2-A50C21726EAB}">
-  <dimension ref="A1:J785"/>
+  <dimension ref="A1:J787"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="11.36328125" bestFit="1" customWidth="1"/>
@@ -38521,7 +38541,7 @@
     </row>
     <row r="722" spans="1:10">
       <c r="A722" s="24">
-        <f t="shared" ref="A722:A785" si="14">A720+1</f>
+        <f t="shared" ref="A722:A786" si="14">A720+1</f>
         <v>46255</v>
       </c>
       <c r="B722" s="23" t="s">
@@ -40629,6 +40649,72 @@
       </c>
       <c r="J785" s="31">
         <v>0.51500000000000001</v>
+      </c>
+    </row>
+    <row r="786" spans="1:10">
+      <c r="A786" s="24">
+        <f t="shared" si="14"/>
+        <v>46287</v>
+      </c>
+      <c r="B786" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C786" s="25">
+        <v>331860003</v>
+      </c>
+      <c r="D786" s="25">
+        <v>1997206</v>
+      </c>
+      <c r="E786" s="25">
+        <v>21784282</v>
+      </c>
+      <c r="F786" s="25">
+        <v>2382322</v>
+      </c>
+      <c r="G786" s="25">
+        <v>358023813</v>
+      </c>
+      <c r="H786" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I786" s="27">
+        <v>0</v>
+      </c>
+      <c r="J786" s="31">
+        <v>0.52400000000000002</v>
+      </c>
+    </row>
+    <row r="787" spans="1:10">
+      <c r="A787" s="24">
+        <f t="shared" ref="A787" si="15">A785+1</f>
+        <v>46287</v>
+      </c>
+      <c r="B787" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C787" s="25">
+        <v>331860003</v>
+      </c>
+      <c r="D787" s="25">
+        <v>1997206</v>
+      </c>
+      <c r="E787" s="25">
+        <v>21784282</v>
+      </c>
+      <c r="F787" s="25">
+        <v>2382322</v>
+      </c>
+      <c r="G787" s="25">
+        <v>358023813</v>
+      </c>
+      <c r="H787" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I787" s="27">
+        <v>0</v>
+      </c>
+      <c r="J787" s="31">
+        <v>0.52400000000000002</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/record.xlsx
+++ b/public/data/record.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\cursor-usage\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58A01297-5557-4D43-A433-1D72FC2BF58C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FD8E7D5-42AF-4041-9687-45588E70C402}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cursor Usageの記録" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1128" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1132" uniqueCount="31">
   <si>
     <t>番号</t>
   </si>
@@ -10713,7 +10713,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92559261-86B2-49A9-AE5C-FC3176987B65}">
-  <dimension ref="A1:E207"/>
+  <dimension ref="A1:E208"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="5.453125" bestFit="1" customWidth="1"/>
@@ -12108,7 +12108,7 @@
     </row>
     <row r="74" spans="1:5" s="5" customFormat="1" ht="14.5">
       <c r="A74" s="6">
-        <f t="shared" ref="A74:A207" si="2">ROW()-1</f>
+        <f t="shared" ref="A74:A208" si="2">ROW()-1</f>
         <v>73</v>
       </c>
       <c r="B74" s="7">
@@ -14167,7 +14167,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="7">
-        <f t="shared" ref="B179:B207" si="12">B178+1</f>
+        <f t="shared" ref="B179:B208" si="12">B178+1</f>
         <v>46259</v>
       </c>
       <c r="C179" s="6">
@@ -14271,7 +14271,7 @@
         <v>46264</v>
       </c>
       <c r="C184" s="6">
-        <f t="shared" ref="C184:C207" si="13">C183+1</f>
+        <f t="shared" ref="C184:C208" si="13">C183+1</f>
         <v>8</v>
       </c>
       <c r="D184" s="13">
@@ -14738,6 +14738,26 @@
         <v>1436</v>
       </c>
       <c r="E207" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5" ht="14" customHeight="1">
+      <c r="A208" s="6">
+        <f t="shared" si="2"/>
+        <v>207</v>
+      </c>
+      <c r="B208" s="7">
+        <f t="shared" si="12"/>
+        <v>46288</v>
+      </c>
+      <c r="C208" s="6">
+        <f t="shared" si="13"/>
+        <v>32</v>
+      </c>
+      <c r="D208" s="13">
+        <v>0</v>
+      </c>
+      <c r="E208" s="13">
         <v>0</v>
       </c>
     </row>
@@ -14750,7 +14770,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E31F5C3B-0571-4A35-9FD2-A50C21726EAB}">
-  <dimension ref="A1:J787"/>
+  <dimension ref="A1:J789"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="11.36328125" bestFit="1" customWidth="1"/>
@@ -38541,7 +38561,7 @@
     </row>
     <row r="722" spans="1:10">
       <c r="A722" s="24">
-        <f t="shared" ref="A722:A786" si="14">A720+1</f>
+        <f t="shared" ref="A722:A788" si="14">A720+1</f>
         <v>46255</v>
       </c>
       <c r="B722" s="23" t="s">
@@ -40686,7 +40706,7 @@
     </row>
     <row r="787" spans="1:10">
       <c r="A787" s="24">
-        <f t="shared" ref="A787" si="15">A785+1</f>
+        <f t="shared" ref="A787:A789" si="15">A785+1</f>
         <v>46287</v>
       </c>
       <c r="B787" s="23" t="s">
@@ -40714,6 +40734,72 @@
         <v>0</v>
       </c>
       <c r="J787" s="31">
+        <v>0.52400000000000002</v>
+      </c>
+    </row>
+    <row r="788" spans="1:10">
+      <c r="A788" s="24">
+        <f t="shared" si="14"/>
+        <v>46288</v>
+      </c>
+      <c r="B788" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C788" s="25">
+        <v>331860003</v>
+      </c>
+      <c r="D788" s="25">
+        <v>1997206</v>
+      </c>
+      <c r="E788" s="25">
+        <v>21784282</v>
+      </c>
+      <c r="F788" s="25">
+        <v>2382322</v>
+      </c>
+      <c r="G788" s="25">
+        <v>358023813</v>
+      </c>
+      <c r="H788" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I788" s="27">
+        <v>0</v>
+      </c>
+      <c r="J788" s="31">
+        <v>0.52400000000000002</v>
+      </c>
+    </row>
+    <row r="789" spans="1:10">
+      <c r="A789" s="24">
+        <f t="shared" si="15"/>
+        <v>46288</v>
+      </c>
+      <c r="B789" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C789" s="25">
+        <v>331860003</v>
+      </c>
+      <c r="D789" s="25">
+        <v>1997206</v>
+      </c>
+      <c r="E789" s="25">
+        <v>21784282</v>
+      </c>
+      <c r="F789" s="25">
+        <v>2382322</v>
+      </c>
+      <c r="G789" s="25">
+        <v>358023813</v>
+      </c>
+      <c r="H789" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I789" s="27">
+        <v>0</v>
+      </c>
+      <c r="J789" s="31">
         <v>0.52400000000000002</v>
       </c>
     </row>

--- a/public/data/record.xlsx
+++ b/public/data/record.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\cursor-usage\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FD8E7D5-42AF-4041-9687-45588E70C402}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDF348A2-D7FD-4B8A-817A-F2C851E8A3BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1132" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1136" uniqueCount="31">
   <si>
     <t>番号</t>
   </si>
@@ -10713,7 +10713,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92559261-86B2-49A9-AE5C-FC3176987B65}">
-  <dimension ref="A1:E208"/>
+  <dimension ref="A1:E209"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="5.453125" bestFit="1" customWidth="1"/>
@@ -12108,7 +12108,7 @@
     </row>
     <row r="74" spans="1:5" s="5" customFormat="1" ht="14.5">
       <c r="A74" s="6">
-        <f t="shared" ref="A74:A208" si="2">ROW()-1</f>
+        <f t="shared" ref="A74:A209" si="2">ROW()-1</f>
         <v>73</v>
       </c>
       <c r="B74" s="7">
@@ -14167,7 +14167,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="7">
-        <f t="shared" ref="B179:B208" si="12">B178+1</f>
+        <f t="shared" ref="B179:B209" si="12">B178+1</f>
         <v>46259</v>
       </c>
       <c r="C179" s="6">
@@ -14271,7 +14271,7 @@
         <v>46264</v>
       </c>
       <c r="C184" s="6">
-        <f t="shared" ref="C184:C208" si="13">C183+1</f>
+        <f t="shared" ref="C184:C209" si="13">C183+1</f>
         <v>8</v>
       </c>
       <c r="D184" s="13">
@@ -14751,13 +14751,32 @@
         <v>46288</v>
       </c>
       <c r="C208" s="6">
+        <v>1</v>
+      </c>
+      <c r="D208" s="13">
+        <v>0</v>
+      </c>
+      <c r="E208" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5" ht="14" customHeight="1">
+      <c r="A209" s="6">
+        <f t="shared" si="2"/>
+        <v>208</v>
+      </c>
+      <c r="B209" s="7">
+        <f t="shared" si="12"/>
+        <v>46289</v>
+      </c>
+      <c r="C209" s="6">
         <f t="shared" si="13"/>
-        <v>32</v>
-      </c>
-      <c r="D208" s="13">
-        <v>0</v>
-      </c>
-      <c r="E208" s="13">
+        <v>2</v>
+      </c>
+      <c r="D209" s="13">
+        <v>2527</v>
+      </c>
+      <c r="E209" s="13">
         <v>0</v>
       </c>
     </row>
@@ -14770,7 +14789,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E31F5C3B-0571-4A35-9FD2-A50C21726EAB}">
-  <dimension ref="A1:J789"/>
+  <dimension ref="A1:J791"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="11.36328125" bestFit="1" customWidth="1"/>
@@ -38561,7 +38580,7 @@
     </row>
     <row r="722" spans="1:10">
       <c r="A722" s="24">
-        <f t="shared" ref="A722:A788" si="14">A720+1</f>
+        <f t="shared" ref="A722:A790" si="14">A720+1</f>
         <v>46255</v>
       </c>
       <c r="B722" s="23" t="s">
@@ -40706,7 +40725,7 @@
     </row>
     <row r="787" spans="1:10">
       <c r="A787" s="24">
-        <f t="shared" ref="A787:A789" si="15">A785+1</f>
+        <f t="shared" ref="A787:A791" si="15">A785+1</f>
         <v>46287</v>
       </c>
       <c r="B787" s="23" t="s">
@@ -40801,6 +40820,72 @@
       </c>
       <c r="J789" s="31">
         <v>0.52400000000000002</v>
+      </c>
+    </row>
+    <row r="790" spans="1:10">
+      <c r="A790" s="24">
+        <f t="shared" si="14"/>
+        <v>46289</v>
+      </c>
+      <c r="B790" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C790" s="25">
+        <v>938624</v>
+      </c>
+      <c r="D790" s="25">
+        <v>0</v>
+      </c>
+      <c r="E790" s="25">
+        <v>373535</v>
+      </c>
+      <c r="F790" s="25">
+        <v>27046</v>
+      </c>
+      <c r="G790" s="25">
+        <v>1339205</v>
+      </c>
+      <c r="H790" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I790" s="27">
+        <v>0</v>
+      </c>
+      <c r="J790" s="31">
+        <v>3.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="791" spans="1:10">
+      <c r="A791" s="24">
+        <f t="shared" si="15"/>
+        <v>46289</v>
+      </c>
+      <c r="B791" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C791" s="25">
+        <v>938624</v>
+      </c>
+      <c r="D791" s="25">
+        <v>0</v>
+      </c>
+      <c r="E791" s="25">
+        <v>373535</v>
+      </c>
+      <c r="F791" s="25">
+        <v>27046</v>
+      </c>
+      <c r="G791" s="25">
+        <v>1339205</v>
+      </c>
+      <c r="H791" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I791" s="27">
+        <v>0</v>
+      </c>
+      <c r="J791" s="31">
+        <v>3.0000000000000001E-3</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/record.xlsx
+++ b/public/data/record.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\cursor-usage\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDF348A2-D7FD-4B8A-817A-F2C851E8A3BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47664057-8302-422C-AD51-5F429861431F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19020" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cursor Usageの記録" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1136" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1140" uniqueCount="31">
   <si>
     <t>番号</t>
   </si>
@@ -10713,7 +10713,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92559261-86B2-49A9-AE5C-FC3176987B65}">
-  <dimension ref="A1:E209"/>
+  <dimension ref="A1:E210"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="5.453125" bestFit="1" customWidth="1"/>
@@ -12108,7 +12108,7 @@
     </row>
     <row r="74" spans="1:5" s="5" customFormat="1" ht="14.5">
       <c r="A74" s="6">
-        <f t="shared" ref="A74:A209" si="2">ROW()-1</f>
+        <f t="shared" ref="A74:A210" si="2">ROW()-1</f>
         <v>73</v>
       </c>
       <c r="B74" s="7">
@@ -14167,7 +14167,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="7">
-        <f t="shared" ref="B179:B209" si="12">B178+1</f>
+        <f t="shared" ref="B179:B210" si="12">B178+1</f>
         <v>46259</v>
       </c>
       <c r="C179" s="6">
@@ -14271,7 +14271,7 @@
         <v>46264</v>
       </c>
       <c r="C184" s="6">
-        <f t="shared" ref="C184:C209" si="13">C183+1</f>
+        <f t="shared" ref="C184:C210" si="13">C183+1</f>
         <v>8</v>
       </c>
       <c r="D184" s="13">
@@ -14777,6 +14777,26 @@
         <v>2527</v>
       </c>
       <c r="E209" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5" ht="14" customHeight="1">
+      <c r="A210" s="6">
+        <f t="shared" si="2"/>
+        <v>209</v>
+      </c>
+      <c r="B210" s="7">
+        <f t="shared" si="12"/>
+        <v>46290</v>
+      </c>
+      <c r="C210" s="6">
+        <f t="shared" si="13"/>
+        <v>3</v>
+      </c>
+      <c r="D210" s="13">
+        <v>2471</v>
+      </c>
+      <c r="E210" s="13">
         <v>0</v>
       </c>
     </row>
@@ -14789,7 +14809,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E31F5C3B-0571-4A35-9FD2-A50C21726EAB}">
-  <dimension ref="A1:J791"/>
+  <dimension ref="A1:J793"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="11.36328125" bestFit="1" customWidth="1"/>
@@ -38580,7 +38600,7 @@
     </row>
     <row r="722" spans="1:10">
       <c r="A722" s="24">
-        <f t="shared" ref="A722:A790" si="14">A720+1</f>
+        <f t="shared" ref="A722:A792" si="14">A720+1</f>
         <v>46255</v>
       </c>
       <c r="B722" s="23" t="s">
@@ -40725,7 +40745,7 @@
     </row>
     <row r="787" spans="1:10">
       <c r="A787" s="24">
-        <f t="shared" ref="A787:A791" si="15">A785+1</f>
+        <f t="shared" ref="A787:A793" si="15">A785+1</f>
         <v>46287</v>
       </c>
       <c r="B787" s="23" t="s">
@@ -40886,6 +40906,72 @@
       </c>
       <c r="J791" s="31">
         <v>3.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="792" spans="1:10">
+      <c r="A792" s="24">
+        <f t="shared" si="14"/>
+        <v>46290</v>
+      </c>
+      <c r="B792" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C792" s="25">
+        <v>2004864</v>
+      </c>
+      <c r="D792" s="25">
+        <v>0</v>
+      </c>
+      <c r="E792" s="25">
+        <v>703739</v>
+      </c>
+      <c r="F792" s="25">
+        <v>55845</v>
+      </c>
+      <c r="G792" s="25">
+        <v>2764448</v>
+      </c>
+      <c r="H792" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I792" s="27">
+        <v>0</v>
+      </c>
+      <c r="J792" s="31">
+        <v>6.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="793" spans="1:10">
+      <c r="A793" s="24">
+        <f t="shared" si="15"/>
+        <v>46290</v>
+      </c>
+      <c r="B793" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C793" s="25">
+        <v>2004864</v>
+      </c>
+      <c r="D793" s="25">
+        <v>0</v>
+      </c>
+      <c r="E793" s="25">
+        <v>703739</v>
+      </c>
+      <c r="F793" s="25">
+        <v>55845</v>
+      </c>
+      <c r="G793" s="25">
+        <v>2764448</v>
+      </c>
+      <c r="H793" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I793" s="27">
+        <v>0</v>
+      </c>
+      <c r="J793" s="31">
+        <v>6.0000000000000001E-3</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/record.xlsx
+++ b/public/data/record.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\cursor-usage\public\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\everyday-use\cursor-usage\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47664057-8302-422C-AD51-5F429861431F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{641DD3F2-CC6D-4E92-AEB6-06B90281A9FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19020" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cursor Usageの記録" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1140" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1144" uniqueCount="31">
   <si>
     <t>番号</t>
   </si>
@@ -10713,7 +10713,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92559261-86B2-49A9-AE5C-FC3176987B65}">
-  <dimension ref="A1:E210"/>
+  <dimension ref="A1:E211"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="5.453125" bestFit="1" customWidth="1"/>
@@ -12108,7 +12108,7 @@
     </row>
     <row r="74" spans="1:5" s="5" customFormat="1" ht="14.5">
       <c r="A74" s="6">
-        <f t="shared" ref="A74:A210" si="2">ROW()-1</f>
+        <f t="shared" ref="A74:A211" si="2">ROW()-1</f>
         <v>73</v>
       </c>
       <c r="B74" s="7">
@@ -14167,7 +14167,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="7">
-        <f t="shared" ref="B179:B210" si="12">B178+1</f>
+        <f t="shared" ref="B179:B211" si="12">B178+1</f>
         <v>46259</v>
       </c>
       <c r="C179" s="6">
@@ -14271,7 +14271,7 @@
         <v>46264</v>
       </c>
       <c r="C184" s="6">
-        <f t="shared" ref="C184:C210" si="13">C183+1</f>
+        <f t="shared" ref="C184:C211" si="13">C183+1</f>
         <v>8</v>
       </c>
       <c r="D184" s="13">
@@ -14797,6 +14797,26 @@
         <v>2471</v>
       </c>
       <c r="E210" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5" ht="14" customHeight="1">
+      <c r="A211" s="6">
+        <f t="shared" si="2"/>
+        <v>210</v>
+      </c>
+      <c r="B211" s="7">
+        <f t="shared" si="12"/>
+        <v>46291</v>
+      </c>
+      <c r="C211" s="6">
+        <f t="shared" si="13"/>
+        <v>4</v>
+      </c>
+      <c r="D211" s="13">
+        <v>5945</v>
+      </c>
+      <c r="E211" s="13">
         <v>0</v>
       </c>
     </row>
@@ -14809,7 +14829,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E31F5C3B-0571-4A35-9FD2-A50C21726EAB}">
-  <dimension ref="A1:J793"/>
+  <dimension ref="A1:J795"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="11.36328125" bestFit="1" customWidth="1"/>
@@ -38600,7 +38620,7 @@
     </row>
     <row r="722" spans="1:10">
       <c r="A722" s="24">
-        <f t="shared" ref="A722:A792" si="14">A720+1</f>
+        <f t="shared" ref="A722:A794" si="14">A720+1</f>
         <v>46255</v>
       </c>
       <c r="B722" s="23" t="s">
@@ -40745,7 +40765,7 @@
     </row>
     <row r="787" spans="1:10">
       <c r="A787" s="24">
-        <f t="shared" ref="A787:A793" si="15">A785+1</f>
+        <f t="shared" ref="A787:A795" si="15">A785+1</f>
         <v>46287</v>
       </c>
       <c r="B787" s="23" t="s">
@@ -40972,6 +40992,72 @@
       </c>
       <c r="J793" s="31">
         <v>6.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="794" spans="1:10">
+      <c r="A794" s="24">
+        <f t="shared" si="14"/>
+        <v>46291</v>
+      </c>
+      <c r="B794" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C794" s="25">
+        <v>10880512</v>
+      </c>
+      <c r="D794" s="25">
+        <v>0</v>
+      </c>
+      <c r="E794" s="25">
+        <v>2898781</v>
+      </c>
+      <c r="F794" s="25">
+        <v>214371</v>
+      </c>
+      <c r="G794" s="25">
+        <v>13993664</v>
+      </c>
+      <c r="H794" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I794" s="27">
+        <v>0</v>
+      </c>
+      <c r="J794" s="31">
+        <v>2.8000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="795" spans="1:10">
+      <c r="A795" s="24">
+        <f t="shared" si="15"/>
+        <v>46291</v>
+      </c>
+      <c r="B795" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C795" s="25">
+        <v>10880512</v>
+      </c>
+      <c r="D795" s="25">
+        <v>0</v>
+      </c>
+      <c r="E795" s="25">
+        <v>2898781</v>
+      </c>
+      <c r="F795" s="25">
+        <v>214371</v>
+      </c>
+      <c r="G795" s="25">
+        <v>13993664</v>
+      </c>
+      <c r="H795" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I795" s="27">
+        <v>0</v>
+      </c>
+      <c r="J795" s="31">
+        <v>2.8000000000000001E-2</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/record.xlsx
+++ b/public/data/record.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\everyday-use\cursor-usage\public\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\cursor-usage\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{641DD3F2-CC6D-4E92-AEB6-06B90281A9FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A85D14A-C4EC-403B-8A7F-BA25FCCF2A75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1144" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1148" uniqueCount="31">
   <si>
     <t>番号</t>
   </si>
@@ -10713,7 +10713,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92559261-86B2-49A9-AE5C-FC3176987B65}">
-  <dimension ref="A1:E211"/>
+  <dimension ref="A1:E212"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="5.453125" bestFit="1" customWidth="1"/>
@@ -12108,7 +12108,7 @@
     </row>
     <row r="74" spans="1:5" s="5" customFormat="1" ht="14.5">
       <c r="A74" s="6">
-        <f t="shared" ref="A74:A211" si="2">ROW()-1</f>
+        <f t="shared" ref="A74:A212" si="2">ROW()-1</f>
         <v>73</v>
       </c>
       <c r="B74" s="7">
@@ -14167,7 +14167,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="7">
-        <f t="shared" ref="B179:B211" si="12">B178+1</f>
+        <f t="shared" ref="B179:B212" si="12">B178+1</f>
         <v>46259</v>
       </c>
       <c r="C179" s="6">
@@ -14271,7 +14271,7 @@
         <v>46264</v>
       </c>
       <c r="C184" s="6">
-        <f t="shared" ref="C184:C211" si="13">C183+1</f>
+        <f t="shared" ref="C184:C212" si="13">C183+1</f>
         <v>8</v>
       </c>
       <c r="D184" s="13">
@@ -14817,6 +14817,26 @@
         <v>5945</v>
       </c>
       <c r="E211" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5" ht="14" customHeight="1">
+      <c r="A212" s="6">
+        <f t="shared" si="2"/>
+        <v>211</v>
+      </c>
+      <c r="B212" s="7">
+        <f t="shared" si="12"/>
+        <v>46292</v>
+      </c>
+      <c r="C212" s="6">
+        <f t="shared" si="13"/>
+        <v>5</v>
+      </c>
+      <c r="D212" s="13">
+        <v>1632</v>
+      </c>
+      <c r="E212" s="13">
         <v>0</v>
       </c>
     </row>
@@ -14829,7 +14849,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E31F5C3B-0571-4A35-9FD2-A50C21726EAB}">
-  <dimension ref="A1:J795"/>
+  <dimension ref="A1:J797"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="11.36328125" bestFit="1" customWidth="1"/>
@@ -38620,7 +38640,7 @@
     </row>
     <row r="722" spans="1:10">
       <c r="A722" s="24">
-        <f t="shared" ref="A722:A794" si="14">A720+1</f>
+        <f t="shared" ref="A722:A796" si="14">A720+1</f>
         <v>46255</v>
       </c>
       <c r="B722" s="23" t="s">
@@ -40765,7 +40785,7 @@
     </row>
     <row r="787" spans="1:10">
       <c r="A787" s="24">
-        <f t="shared" ref="A787:A795" si="15">A785+1</f>
+        <f t="shared" ref="A787:A797" si="15">A785+1</f>
         <v>46287</v>
       </c>
       <c r="B787" s="23" t="s">
@@ -41058,6 +41078,72 @@
       </c>
       <c r="J795" s="31">
         <v>2.8000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="796" spans="1:10">
+      <c r="A796" s="24">
+        <f t="shared" si="14"/>
+        <v>46292</v>
+      </c>
+      <c r="B796" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C796" s="25">
+        <v>14445241</v>
+      </c>
+      <c r="D796" s="25">
+        <v>271618</v>
+      </c>
+      <c r="E796" s="25">
+        <v>2898925</v>
+      </c>
+      <c r="F796" s="25">
+        <v>255287</v>
+      </c>
+      <c r="G796" s="25">
+        <v>17871071</v>
+      </c>
+      <c r="H796" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I796" s="27">
+        <v>0</v>
+      </c>
+      <c r="J796" s="31">
+        <v>3.4000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="797" spans="1:10">
+      <c r="A797" s="24">
+        <f t="shared" si="15"/>
+        <v>46292</v>
+      </c>
+      <c r="B797" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C797" s="25">
+        <v>14445241</v>
+      </c>
+      <c r="D797" s="25">
+        <v>271618</v>
+      </c>
+      <c r="E797" s="25">
+        <v>2898925</v>
+      </c>
+      <c r="F797" s="25">
+        <v>255287</v>
+      </c>
+      <c r="G797" s="25">
+        <v>17871071</v>
+      </c>
+      <c r="H797" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I797" s="27">
+        <v>0</v>
+      </c>
+      <c r="J797" s="31">
+        <v>3.4000000000000002E-2</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/record.xlsx
+++ b/public/data/record.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\cursor-usage\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A85D14A-C4EC-403B-8A7F-BA25FCCF2A75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50549901-4103-4CA7-925D-EBB50F427EFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19020" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cursor Usageの記録" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1148" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1152" uniqueCount="31">
   <si>
     <t>番号</t>
   </si>
@@ -10713,7 +10713,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92559261-86B2-49A9-AE5C-FC3176987B65}">
-  <dimension ref="A1:E212"/>
+  <dimension ref="A1:E213"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="5.453125" bestFit="1" customWidth="1"/>
@@ -12108,7 +12108,7 @@
     </row>
     <row r="74" spans="1:5" s="5" customFormat="1" ht="14.5">
       <c r="A74" s="6">
-        <f t="shared" ref="A74:A212" si="2">ROW()-1</f>
+        <f t="shared" ref="A74:A213" si="2">ROW()-1</f>
         <v>73</v>
       </c>
       <c r="B74" s="7">
@@ -14167,7 +14167,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="7">
-        <f t="shared" ref="B179:B212" si="12">B178+1</f>
+        <f t="shared" ref="B179:B213" si="12">B178+1</f>
         <v>46259</v>
       </c>
       <c r="C179" s="6">
@@ -14271,7 +14271,7 @@
         <v>46264</v>
       </c>
       <c r="C184" s="6">
-        <f t="shared" ref="C184:C212" si="13">C183+1</f>
+        <f t="shared" ref="C184:C213" si="13">C183+1</f>
         <v>8</v>
       </c>
       <c r="D184" s="13">
@@ -14837,6 +14837,26 @@
         <v>1632</v>
       </c>
       <c r="E212" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5" ht="14" customHeight="1">
+      <c r="A213" s="6">
+        <f t="shared" si="2"/>
+        <v>212</v>
+      </c>
+      <c r="B213" s="7">
+        <f t="shared" si="12"/>
+        <v>46293</v>
+      </c>
+      <c r="C213" s="6">
+        <f t="shared" si="13"/>
+        <v>6</v>
+      </c>
+      <c r="D213" s="13">
+        <v>0</v>
+      </c>
+      <c r="E213" s="13">
         <v>0</v>
       </c>
     </row>
@@ -14849,7 +14869,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E31F5C3B-0571-4A35-9FD2-A50C21726EAB}">
-  <dimension ref="A1:J797"/>
+  <dimension ref="A1:J799"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="11.36328125" bestFit="1" customWidth="1"/>
@@ -38640,7 +38660,7 @@
     </row>
     <row r="722" spans="1:10">
       <c r="A722" s="24">
-        <f t="shared" ref="A722:A796" si="14">A720+1</f>
+        <f t="shared" ref="A722:A798" si="14">A720+1</f>
         <v>46255</v>
       </c>
       <c r="B722" s="23" t="s">
@@ -40785,7 +40805,7 @@
     </row>
     <row r="787" spans="1:10">
       <c r="A787" s="24">
-        <f t="shared" ref="A787:A797" si="15">A785+1</f>
+        <f t="shared" ref="A787:A799" si="15">A785+1</f>
         <v>46287</v>
       </c>
       <c r="B787" s="23" t="s">
@@ -41143,6 +41163,72 @@
         <v>0</v>
       </c>
       <c r="J797" s="31">
+        <v>3.4000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="798" spans="1:10">
+      <c r="A798" s="24">
+        <f t="shared" si="14"/>
+        <v>46293</v>
+      </c>
+      <c r="B798" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C798" s="25">
+        <v>14445241</v>
+      </c>
+      <c r="D798" s="25">
+        <v>271618</v>
+      </c>
+      <c r="E798" s="25">
+        <v>2898925</v>
+      </c>
+      <c r="F798" s="25">
+        <v>255287</v>
+      </c>
+      <c r="G798" s="25">
+        <v>17871071</v>
+      </c>
+      <c r="H798" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I798" s="27">
+        <v>0</v>
+      </c>
+      <c r="J798" s="31">
+        <v>3.4000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="799" spans="1:10">
+      <c r="A799" s="24">
+        <f t="shared" si="15"/>
+        <v>46293</v>
+      </c>
+      <c r="B799" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C799" s="25">
+        <v>14445241</v>
+      </c>
+      <c r="D799" s="25">
+        <v>271618</v>
+      </c>
+      <c r="E799" s="25">
+        <v>2898925</v>
+      </c>
+      <c r="F799" s="25">
+        <v>255287</v>
+      </c>
+      <c r="G799" s="25">
+        <v>17871071</v>
+      </c>
+      <c r="H799" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I799" s="27">
+        <v>0</v>
+      </c>
+      <c r="J799" s="31">
         <v>3.4000000000000002E-2</v>
       </c>
     </row>

--- a/public/data/record.xlsx
+++ b/public/data/record.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\cursor-usage\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50549901-4103-4CA7-925D-EBB50F427EFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53C829B8-7FDA-4546-9CB3-54D12EA32110}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19020" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19110" yWindow="0" windowWidth="19290" windowHeight="20880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cursor Usageの記録" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1152" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1156" uniqueCount="31">
   <si>
     <t>番号</t>
   </si>
@@ -10713,7 +10713,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92559261-86B2-49A9-AE5C-FC3176987B65}">
-  <dimension ref="A1:E213"/>
+  <dimension ref="A1:E214"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="5.453125" bestFit="1" customWidth="1"/>
@@ -12108,7 +12108,7 @@
     </row>
     <row r="74" spans="1:5" s="5" customFormat="1" ht="14.5">
       <c r="A74" s="6">
-        <f t="shared" ref="A74:A213" si="2">ROW()-1</f>
+        <f t="shared" ref="A74:A214" si="2">ROW()-1</f>
         <v>73</v>
       </c>
       <c r="B74" s="7">
@@ -14167,7 +14167,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="7">
-        <f t="shared" ref="B179:B213" si="12">B178+1</f>
+        <f t="shared" ref="B179:B214" si="12">B178+1</f>
         <v>46259</v>
       </c>
       <c r="C179" s="6">
@@ -14271,7 +14271,7 @@
         <v>46264</v>
       </c>
       <c r="C184" s="6">
-        <f t="shared" ref="C184:C213" si="13">C183+1</f>
+        <f t="shared" ref="C184:C214" si="13">C183+1</f>
         <v>8</v>
       </c>
       <c r="D184" s="13">
@@ -14857,6 +14857,26 @@
         <v>0</v>
       </c>
       <c r="E213" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5" ht="14" customHeight="1">
+      <c r="A214" s="6">
+        <f t="shared" si="2"/>
+        <v>213</v>
+      </c>
+      <c r="B214" s="7">
+        <f t="shared" si="12"/>
+        <v>46294</v>
+      </c>
+      <c r="C214" s="6">
+        <f t="shared" si="13"/>
+        <v>7</v>
+      </c>
+      <c r="D214" s="13">
+        <v>1157</v>
+      </c>
+      <c r="E214" s="13">
         <v>0</v>
       </c>
     </row>
@@ -14869,7 +14889,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E31F5C3B-0571-4A35-9FD2-A50C21726EAB}">
-  <dimension ref="A1:J799"/>
+  <dimension ref="A1:J801"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="11.36328125" bestFit="1" customWidth="1"/>
@@ -38660,7 +38680,7 @@
     </row>
     <row r="722" spans="1:10">
       <c r="A722" s="24">
-        <f t="shared" ref="A722:A798" si="14">A720+1</f>
+        <f t="shared" ref="A722:A800" si="14">A720+1</f>
         <v>46255</v>
       </c>
       <c r="B722" s="23" t="s">
@@ -40805,7 +40825,7 @@
     </row>
     <row r="787" spans="1:10">
       <c r="A787" s="24">
-        <f t="shared" ref="A787:A799" si="15">A785+1</f>
+        <f t="shared" ref="A787:A801" si="15">A785+1</f>
         <v>46287</v>
       </c>
       <c r="B787" s="23" t="s">
@@ -41230,6 +41250,72 @@
       </c>
       <c r="J799" s="31">
         <v>3.4000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="800" spans="1:10">
+      <c r="A800" s="24">
+        <f t="shared" si="14"/>
+        <v>46294</v>
+      </c>
+      <c r="B800" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C800" s="25">
+        <v>26002157</v>
+      </c>
+      <c r="D800" s="25">
+        <v>808054</v>
+      </c>
+      <c r="E800" s="25">
+        <v>2899143</v>
+      </c>
+      <c r="F800" s="25">
+        <v>347488</v>
+      </c>
+      <c r="G800" s="25">
+        <v>30056842</v>
+      </c>
+      <c r="H800" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I800" s="27">
+        <v>0</v>
+      </c>
+      <c r="J800" s="31">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="801" spans="1:10">
+      <c r="A801" s="24">
+        <f t="shared" si="15"/>
+        <v>46294</v>
+      </c>
+      <c r="B801" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C801" s="25">
+        <v>26002157</v>
+      </c>
+      <c r="D801" s="25">
+        <v>808054</v>
+      </c>
+      <c r="E801" s="25">
+        <v>2899143</v>
+      </c>
+      <c r="F801" s="25">
+        <v>347488</v>
+      </c>
+      <c r="G801" s="25">
+        <v>30056842</v>
+      </c>
+      <c r="H801" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I801" s="27">
+        <v>0</v>
+      </c>
+      <c r="J801" s="31">
+        <v>0.05</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/record.xlsx
+++ b/public/data/record.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\cursor-usage\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53C829B8-7FDA-4546-9CB3-54D12EA32110}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B43935B0-8CE7-4B0E-AEE8-FD23EF133F47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19110" yWindow="0" windowWidth="19290" windowHeight="20880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cursor Usageの記録" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1156" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1160" uniqueCount="31">
   <si>
     <t>番号</t>
   </si>
@@ -10713,7 +10713,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92559261-86B2-49A9-AE5C-FC3176987B65}">
-  <dimension ref="A1:E214"/>
+  <dimension ref="A1:E215"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="5.453125" bestFit="1" customWidth="1"/>
@@ -12108,7 +12108,7 @@
     </row>
     <row r="74" spans="1:5" s="5" customFormat="1" ht="14.5">
       <c r="A74" s="6">
-        <f t="shared" ref="A74:A214" si="2">ROW()-1</f>
+        <f t="shared" ref="A74:A215" si="2">ROW()-1</f>
         <v>73</v>
       </c>
       <c r="B74" s="7">
@@ -14167,7 +14167,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="7">
-        <f t="shared" ref="B179:B214" si="12">B178+1</f>
+        <f t="shared" ref="B179:B215" si="12">B178+1</f>
         <v>46259</v>
       </c>
       <c r="C179" s="6">
@@ -14271,7 +14271,7 @@
         <v>46264</v>
       </c>
       <c r="C184" s="6">
-        <f t="shared" ref="C184:C214" si="13">C183+1</f>
+        <f t="shared" ref="C184:C215" si="13">C183+1</f>
         <v>8</v>
       </c>
       <c r="D184" s="13">
@@ -14877,6 +14877,26 @@
         <v>1157</v>
       </c>
       <c r="E214" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5" ht="14" customHeight="1">
+      <c r="A215" s="6">
+        <f t="shared" si="2"/>
+        <v>214</v>
+      </c>
+      <c r="B215" s="7">
+        <f t="shared" si="12"/>
+        <v>46295</v>
+      </c>
+      <c r="C215" s="6">
+        <f t="shared" si="13"/>
+        <v>8</v>
+      </c>
+      <c r="D215" s="13">
+        <v>1008</v>
+      </c>
+      <c r="E215" s="13">
         <v>0</v>
       </c>
     </row>
@@ -14889,7 +14909,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E31F5C3B-0571-4A35-9FD2-A50C21726EAB}">
-  <dimension ref="A1:J801"/>
+  <dimension ref="A1:J803"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="11.36328125" bestFit="1" customWidth="1"/>
@@ -38680,7 +38700,7 @@
     </row>
     <row r="722" spans="1:10">
       <c r="A722" s="24">
-        <f t="shared" ref="A722:A800" si="14">A720+1</f>
+        <f t="shared" ref="A722:A802" si="14">A720+1</f>
         <v>46255</v>
       </c>
       <c r="B722" s="23" t="s">
@@ -40825,7 +40845,7 @@
     </row>
     <row r="787" spans="1:10">
       <c r="A787" s="24">
-        <f t="shared" ref="A787:A801" si="15">A785+1</f>
+        <f t="shared" ref="A787:A803" si="15">A785+1</f>
         <v>46287</v>
       </c>
       <c r="B787" s="23" t="s">
@@ -41316,6 +41336,72 @@
       </c>
       <c r="J801" s="31">
         <v>0.05</v>
+      </c>
+    </row>
+    <row r="802" spans="1:10">
+      <c r="A802" s="24">
+        <f t="shared" si="14"/>
+        <v>46295</v>
+      </c>
+      <c r="B802" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C802" s="25">
+        <v>26666046</v>
+      </c>
+      <c r="D802" s="25">
+        <v>923146</v>
+      </c>
+      <c r="E802" s="25">
+        <v>2899229</v>
+      </c>
+      <c r="F802" s="25">
+        <v>361950</v>
+      </c>
+      <c r="G802" s="25">
+        <v>30850371</v>
+      </c>
+      <c r="H802" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I802" s="27">
+        <v>0</v>
+      </c>
+      <c r="J802" s="31">
+        <v>5.0999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="803" spans="1:10">
+      <c r="A803" s="24">
+        <f t="shared" si="15"/>
+        <v>46295</v>
+      </c>
+      <c r="B803" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C803" s="25">
+        <v>26666046</v>
+      </c>
+      <c r="D803" s="25">
+        <v>923146</v>
+      </c>
+      <c r="E803" s="25">
+        <v>2899229</v>
+      </c>
+      <c r="F803" s="25">
+        <v>361950</v>
+      </c>
+      <c r="G803" s="25">
+        <v>30850371</v>
+      </c>
+      <c r="H803" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I803" s="27">
+        <v>0</v>
+      </c>
+      <c r="J803" s="31">
+        <v>5.0999999999999997E-2</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/record.xlsx
+++ b/public/data/record.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\cursor-usage\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B43935B0-8CE7-4B0E-AEE8-FD23EF133F47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAF3E877-D6FC-4795-830D-C11E6EF33A23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19020" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cursor Usageの記録" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1160" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1164" uniqueCount="31">
   <si>
     <t>番号</t>
   </si>
@@ -10713,7 +10713,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92559261-86B2-49A9-AE5C-FC3176987B65}">
-  <dimension ref="A1:E215"/>
+  <dimension ref="A1:E216"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="5.453125" bestFit="1" customWidth="1"/>
@@ -12108,7 +12108,7 @@
     </row>
     <row r="74" spans="1:5" s="5" customFormat="1" ht="14.5">
       <c r="A74" s="6">
-        <f t="shared" ref="A74:A215" si="2">ROW()-1</f>
+        <f t="shared" ref="A74:A216" si="2">ROW()-1</f>
         <v>73</v>
       </c>
       <c r="B74" s="7">
@@ -14167,7 +14167,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="7">
-        <f t="shared" ref="B179:B215" si="12">B178+1</f>
+        <f t="shared" ref="B179:B216" si="12">B178+1</f>
         <v>46259</v>
       </c>
       <c r="C179" s="6">
@@ -14271,7 +14271,7 @@
         <v>46264</v>
       </c>
       <c r="C184" s="6">
-        <f t="shared" ref="C184:C215" si="13">C183+1</f>
+        <f t="shared" ref="C184:C216" si="13">C183+1</f>
         <v>8</v>
       </c>
       <c r="D184" s="13">
@@ -14897,6 +14897,26 @@
         <v>1008</v>
       </c>
       <c r="E215" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5" ht="14" customHeight="1">
+      <c r="A216" s="6">
+        <f t="shared" si="2"/>
+        <v>215</v>
+      </c>
+      <c r="B216" s="7">
+        <f t="shared" si="12"/>
+        <v>46296</v>
+      </c>
+      <c r="C216" s="6">
+        <f t="shared" si="13"/>
+        <v>9</v>
+      </c>
+      <c r="D216" s="13">
+        <v>0</v>
+      </c>
+      <c r="E216" s="13">
         <v>0</v>
       </c>
     </row>
@@ -14909,7 +14929,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E31F5C3B-0571-4A35-9FD2-A50C21726EAB}">
-  <dimension ref="A1:J803"/>
+  <dimension ref="A1:J805"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="11.36328125" bestFit="1" customWidth="1"/>
@@ -38700,7 +38720,7 @@
     </row>
     <row r="722" spans="1:10">
       <c r="A722" s="24">
-        <f t="shared" ref="A722:A802" si="14">A720+1</f>
+        <f t="shared" ref="A722:A804" si="14">A720+1</f>
         <v>46255</v>
       </c>
       <c r="B722" s="23" t="s">
@@ -40845,7 +40865,7 @@
     </row>
     <row r="787" spans="1:10">
       <c r="A787" s="24">
-        <f t="shared" ref="A787:A803" si="15">A785+1</f>
+        <f t="shared" ref="A787:A805" si="15">A785+1</f>
         <v>46287</v>
       </c>
       <c r="B787" s="23" t="s">
@@ -41402,6 +41422,72 @@
       </c>
       <c r="J803" s="31">
         <v>5.0999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="804" spans="1:10">
+      <c r="A804" s="24">
+        <f t="shared" si="14"/>
+        <v>46296</v>
+      </c>
+      <c r="B804" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C804" s="25">
+        <v>28336598</v>
+      </c>
+      <c r="D804" s="25">
+        <v>1057007</v>
+      </c>
+      <c r="E804" s="25">
+        <v>2899285</v>
+      </c>
+      <c r="F804" s="25">
+        <v>385675</v>
+      </c>
+      <c r="G804" s="25">
+        <v>32678565</v>
+      </c>
+      <c r="H804" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I804" s="27">
+        <v>0</v>
+      </c>
+      <c r="J804" s="31">
+        <v>5.3999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="805" spans="1:10">
+      <c r="A805" s="24">
+        <f t="shared" si="15"/>
+        <v>46296</v>
+      </c>
+      <c r="B805" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C805" s="25">
+        <v>28336598</v>
+      </c>
+      <c r="D805" s="25">
+        <v>1057007</v>
+      </c>
+      <c r="E805" s="25">
+        <v>2899285</v>
+      </c>
+      <c r="F805" s="25">
+        <v>385675</v>
+      </c>
+      <c r="G805" s="25">
+        <v>32678565</v>
+      </c>
+      <c r="H805" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I805" s="27">
+        <v>0</v>
+      </c>
+      <c r="J805" s="31">
+        <v>5.3999999999999999E-2</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/record.xlsx
+++ b/public/data/record.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\cursor-usage\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAF3E877-D6FC-4795-830D-C11E6EF33A23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB8A852F-B0BD-49D4-A58A-F1D9A5137BF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19020" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cursor Usageの記録" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1164" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1168" uniqueCount="31">
   <si>
     <t>番号</t>
   </si>
@@ -10713,7 +10713,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92559261-86B2-49A9-AE5C-FC3176987B65}">
-  <dimension ref="A1:E216"/>
+  <dimension ref="A1:E217"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="5.453125" bestFit="1" customWidth="1"/>
@@ -12108,7 +12108,7 @@
     </row>
     <row r="74" spans="1:5" s="5" customFormat="1" ht="14.5">
       <c r="A74" s="6">
-        <f t="shared" ref="A74:A216" si="2">ROW()-1</f>
+        <f t="shared" ref="A74:A217" si="2">ROW()-1</f>
         <v>73</v>
       </c>
       <c r="B74" s="7">
@@ -14167,7 +14167,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="7">
-        <f t="shared" ref="B179:B216" si="12">B178+1</f>
+        <f t="shared" ref="B179:B217" si="12">B178+1</f>
         <v>46259</v>
       </c>
       <c r="C179" s="6">
@@ -14271,7 +14271,7 @@
         <v>46264</v>
       </c>
       <c r="C184" s="6">
-        <f t="shared" ref="C184:C216" si="13">C183+1</f>
+        <f t="shared" ref="C184:C217" si="13">C183+1</f>
         <v>8</v>
       </c>
       <c r="D184" s="13">
@@ -14917,6 +14917,26 @@
         <v>0</v>
       </c>
       <c r="E216" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5" ht="14" customHeight="1">
+      <c r="A217" s="6">
+        <f t="shared" si="2"/>
+        <v>216</v>
+      </c>
+      <c r="B217" s="7">
+        <f t="shared" si="12"/>
+        <v>46297</v>
+      </c>
+      <c r="C217" s="6">
+        <f t="shared" si="13"/>
+        <v>10</v>
+      </c>
+      <c r="D217" s="13">
+        <v>502</v>
+      </c>
+      <c r="E217" s="13">
         <v>0</v>
       </c>
     </row>
@@ -14929,7 +14949,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E31F5C3B-0571-4A35-9FD2-A50C21726EAB}">
-  <dimension ref="A1:J805"/>
+  <dimension ref="A1:J807"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="11.36328125" bestFit="1" customWidth="1"/>
@@ -38720,7 +38740,7 @@
     </row>
     <row r="722" spans="1:10">
       <c r="A722" s="24">
-        <f t="shared" ref="A722:A804" si="14">A720+1</f>
+        <f t="shared" ref="A722:A806" si="14">A720+1</f>
         <v>46255</v>
       </c>
       <c r="B722" s="23" t="s">
@@ -40865,7 +40885,7 @@
     </row>
     <row r="787" spans="1:10">
       <c r="A787" s="24">
-        <f t="shared" ref="A787:A805" si="15">A785+1</f>
+        <f t="shared" ref="A787:A807" si="15">A785+1</f>
         <v>46287</v>
       </c>
       <c r="B787" s="23" t="s">
@@ -41488,6 +41508,72 @@
       </c>
       <c r="J805" s="31">
         <v>5.3999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="806" spans="1:10">
+      <c r="A806" s="24">
+        <f t="shared" si="14"/>
+        <v>46297</v>
+      </c>
+      <c r="B806" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C806" s="25">
+        <v>31971338</v>
+      </c>
+      <c r="D806" s="25">
+        <v>1450846</v>
+      </c>
+      <c r="E806" s="25">
+        <v>2899471</v>
+      </c>
+      <c r="F806" s="25">
+        <v>427693</v>
+      </c>
+      <c r="G806" s="25">
+        <v>36749348</v>
+      </c>
+      <c r="H806" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I806" s="27">
+        <v>0</v>
+      </c>
+      <c r="J806" s="31">
+        <v>6.0999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="807" spans="1:10">
+      <c r="A807" s="24">
+        <f t="shared" si="15"/>
+        <v>46297</v>
+      </c>
+      <c r="B807" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C807" s="25">
+        <v>31971338</v>
+      </c>
+      <c r="D807" s="25">
+        <v>1450846</v>
+      </c>
+      <c r="E807" s="25">
+        <v>2899471</v>
+      </c>
+      <c r="F807" s="25">
+        <v>427693</v>
+      </c>
+      <c r="G807" s="25">
+        <v>36749348</v>
+      </c>
+      <c r="H807" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I807" s="27">
+        <v>0</v>
+      </c>
+      <c r="J807" s="31">
+        <v>6.0999999999999999E-2</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/record.xlsx
+++ b/public/data/record.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\cursor-usage\public\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\everyday-use\cursor-usage\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB8A852F-B0BD-49D4-A58A-F1D9A5137BF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53F2B011-72E8-48CE-A1C2-A06F0FF4301E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1168" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1172" uniqueCount="31">
   <si>
     <t>番号</t>
   </si>
@@ -10713,7 +10713,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92559261-86B2-49A9-AE5C-FC3176987B65}">
-  <dimension ref="A1:E217"/>
+  <dimension ref="A1:E218"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="5.453125" bestFit="1" customWidth="1"/>
@@ -12108,7 +12108,7 @@
     </row>
     <row r="74" spans="1:5" s="5" customFormat="1" ht="14.5">
       <c r="A74" s="6">
-        <f t="shared" ref="A74:A217" si="2">ROW()-1</f>
+        <f t="shared" ref="A74:A218" si="2">ROW()-1</f>
         <v>73</v>
       </c>
       <c r="B74" s="7">
@@ -14167,7 +14167,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="7">
-        <f t="shared" ref="B179:B217" si="12">B178+1</f>
+        <f t="shared" ref="B179:B218" si="12">B178+1</f>
         <v>46259</v>
       </c>
       <c r="C179" s="6">
@@ -14271,7 +14271,7 @@
         <v>46264</v>
       </c>
       <c r="C184" s="6">
-        <f t="shared" ref="C184:C217" si="13">C183+1</f>
+        <f t="shared" ref="C184:C218" si="13">C183+1</f>
         <v>8</v>
       </c>
       <c r="D184" s="13">
@@ -14937,6 +14937,26 @@
         <v>502</v>
       </c>
       <c r="E217" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5" ht="14" customHeight="1">
+      <c r="A218" s="6">
+        <f t="shared" si="2"/>
+        <v>217</v>
+      </c>
+      <c r="B218" s="7">
+        <f t="shared" si="12"/>
+        <v>46298</v>
+      </c>
+      <c r="C218" s="6">
+        <f t="shared" si="13"/>
+        <v>11</v>
+      </c>
+      <c r="D218" s="13">
+        <v>1883</v>
+      </c>
+      <c r="E218" s="13">
         <v>0</v>
       </c>
     </row>
@@ -14949,7 +14969,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E31F5C3B-0571-4A35-9FD2-A50C21726EAB}">
-  <dimension ref="A1:J807"/>
+  <dimension ref="A1:J809"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="11.36328125" bestFit="1" customWidth="1"/>
@@ -38740,7 +38760,7 @@
     </row>
     <row r="722" spans="1:10">
       <c r="A722" s="24">
-        <f t="shared" ref="A722:A806" si="14">A720+1</f>
+        <f t="shared" ref="A722:A808" si="14">A720+1</f>
         <v>46255</v>
       </c>
       <c r="B722" s="23" t="s">
@@ -40885,7 +40905,7 @@
     </row>
     <row r="787" spans="1:10">
       <c r="A787" s="24">
-        <f t="shared" ref="A787:A807" si="15">A785+1</f>
+        <f t="shared" ref="A787:A809" si="15">A785+1</f>
         <v>46287</v>
       </c>
       <c r="B787" s="23" t="s">
@@ -41574,6 +41594,72 @@
       </c>
       <c r="J807" s="31">
         <v>6.0999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="808" spans="1:10">
+      <c r="A808" s="24">
+        <f t="shared" si="14"/>
+        <v>46298</v>
+      </c>
+      <c r="B808" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C808" s="25">
+        <v>36721323</v>
+      </c>
+      <c r="D808" s="25">
+        <v>1818078</v>
+      </c>
+      <c r="E808" s="25">
+        <v>2899637</v>
+      </c>
+      <c r="F808" s="25">
+        <v>482060</v>
+      </c>
+      <c r="G808" s="25">
+        <v>41921098</v>
+      </c>
+      <c r="H808" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I808" s="27">
+        <v>0</v>
+      </c>
+      <c r="J808" s="31">
+        <v>6.8000000000000005E-2</v>
+      </c>
+    </row>
+    <row r="809" spans="1:10">
+      <c r="A809" s="24">
+        <f t="shared" si="15"/>
+        <v>46298</v>
+      </c>
+      <c r="B809" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C809" s="25">
+        <v>36721323</v>
+      </c>
+      <c r="D809" s="25">
+        <v>1818078</v>
+      </c>
+      <c r="E809" s="25">
+        <v>2899637</v>
+      </c>
+      <c r="F809" s="25">
+        <v>482060</v>
+      </c>
+      <c r="G809" s="25">
+        <v>41921098</v>
+      </c>
+      <c r="H809" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I809" s="27">
+        <v>0</v>
+      </c>
+      <c r="J809" s="31">
+        <v>6.8000000000000005E-2</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/record.xlsx
+++ b/public/data/record.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\everyday-use\cursor-usage\public\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\cursor-usage\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53F2B011-72E8-48CE-A1C2-A06F0FF4301E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA27100D-C35D-40A2-9ECC-3E619FDF0BA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cursor Usageの記録" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1172" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1176" uniqueCount="31">
   <si>
     <t>番号</t>
   </si>
@@ -10713,7 +10713,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92559261-86B2-49A9-AE5C-FC3176987B65}">
-  <dimension ref="A1:E218"/>
+  <dimension ref="A1:E219"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="5.453125" bestFit="1" customWidth="1"/>
@@ -12108,7 +12108,7 @@
     </row>
     <row r="74" spans="1:5" s="5" customFormat="1" ht="14.5">
       <c r="A74" s="6">
-        <f t="shared" ref="A74:A218" si="2">ROW()-1</f>
+        <f t="shared" ref="A74:A219" si="2">ROW()-1</f>
         <v>73</v>
       </c>
       <c r="B74" s="7">
@@ -14167,7 +14167,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="7">
-        <f t="shared" ref="B179:B218" si="12">B178+1</f>
+        <f t="shared" ref="B179:B219" si="12">B178+1</f>
         <v>46259</v>
       </c>
       <c r="C179" s="6">
@@ -14271,7 +14271,7 @@
         <v>46264</v>
       </c>
       <c r="C184" s="6">
-        <f t="shared" ref="C184:C218" si="13">C183+1</f>
+        <f t="shared" ref="C184:C219" si="13">C183+1</f>
         <v>8</v>
       </c>
       <c r="D184" s="13">
@@ -14957,6 +14957,26 @@
         <v>1883</v>
       </c>
       <c r="E218" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5" ht="14" customHeight="1">
+      <c r="A219" s="6">
+        <f t="shared" si="2"/>
+        <v>218</v>
+      </c>
+      <c r="B219" s="7">
+        <f t="shared" si="12"/>
+        <v>46299</v>
+      </c>
+      <c r="C219" s="6">
+        <f t="shared" si="13"/>
+        <v>12</v>
+      </c>
+      <c r="D219" s="13">
+        <v>0</v>
+      </c>
+      <c r="E219" s="13">
         <v>0</v>
       </c>
     </row>
@@ -14969,7 +14989,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E31F5C3B-0571-4A35-9FD2-A50C21726EAB}">
-  <dimension ref="A1:J809"/>
+  <dimension ref="A1:J811"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="11.36328125" bestFit="1" customWidth="1"/>
@@ -38760,7 +38780,7 @@
     </row>
     <row r="722" spans="1:10">
       <c r="A722" s="24">
-        <f t="shared" ref="A722:A808" si="14">A720+1</f>
+        <f t="shared" ref="A722:A810" si="14">A720+1</f>
         <v>46255</v>
       </c>
       <c r="B722" s="23" t="s">
@@ -40905,7 +40925,7 @@
     </row>
     <row r="787" spans="1:10">
       <c r="A787" s="24">
-        <f t="shared" ref="A787:A809" si="15">A785+1</f>
+        <f t="shared" ref="A787:A811" si="15">A785+1</f>
         <v>46287</v>
       </c>
       <c r="B787" s="23" t="s">
@@ -41659,6 +41679,72 @@
         <v>0</v>
       </c>
       <c r="J809" s="31">
+        <v>6.8000000000000005E-2</v>
+      </c>
+    </row>
+    <row r="810" spans="1:10">
+      <c r="A810" s="24">
+        <f t="shared" si="14"/>
+        <v>46299</v>
+      </c>
+      <c r="B810" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C810" s="25">
+        <v>36721323</v>
+      </c>
+      <c r="D810" s="25">
+        <v>1818078</v>
+      </c>
+      <c r="E810" s="25">
+        <v>2899637</v>
+      </c>
+      <c r="F810" s="25">
+        <v>482060</v>
+      </c>
+      <c r="G810" s="25">
+        <v>41921098</v>
+      </c>
+      <c r="H810" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I810" s="27">
+        <v>0</v>
+      </c>
+      <c r="J810" s="31">
+        <v>6.8000000000000005E-2</v>
+      </c>
+    </row>
+    <row r="811" spans="1:10">
+      <c r="A811" s="24">
+        <f t="shared" si="15"/>
+        <v>46299</v>
+      </c>
+      <c r="B811" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C811" s="25">
+        <v>36721323</v>
+      </c>
+      <c r="D811" s="25">
+        <v>1818078</v>
+      </c>
+      <c r="E811" s="25">
+        <v>2899637</v>
+      </c>
+      <c r="F811" s="25">
+        <v>482060</v>
+      </c>
+      <c r="G811" s="25">
+        <v>41921098</v>
+      </c>
+      <c r="H811" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I811" s="27">
+        <v>0</v>
+      </c>
+      <c r="J811" s="31">
         <v>6.8000000000000005E-2</v>
       </c>
     </row>

--- a/public/data/record.xlsx
+++ b/public/data/record.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\cursor-usage\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA27100D-C35D-40A2-9ECC-3E619FDF0BA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CB49EF8-354C-4F67-8D22-3DAAE1D68C24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cursor Usageの記録" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1176" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1180" uniqueCount="31">
   <si>
     <t>番号</t>
   </si>
@@ -10713,7 +10713,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92559261-86B2-49A9-AE5C-FC3176987B65}">
-  <dimension ref="A1:E219"/>
+  <dimension ref="A1:E220"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="5.453125" bestFit="1" customWidth="1"/>
@@ -12108,7 +12108,7 @@
     </row>
     <row r="74" spans="1:5" s="5" customFormat="1" ht="14.5">
       <c r="A74" s="6">
-        <f t="shared" ref="A74:A219" si="2">ROW()-1</f>
+        <f t="shared" ref="A74:A220" si="2">ROW()-1</f>
         <v>73</v>
       </c>
       <c r="B74" s="7">
@@ -14167,7 +14167,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="7">
-        <f t="shared" ref="B179:B219" si="12">B178+1</f>
+        <f t="shared" ref="B179:B220" si="12">B178+1</f>
         <v>46259</v>
       </c>
       <c r="C179" s="6">
@@ -14271,7 +14271,7 @@
         <v>46264</v>
       </c>
       <c r="C184" s="6">
-        <f t="shared" ref="C184:C219" si="13">C183+1</f>
+        <f t="shared" ref="C184:C220" si="13">C183+1</f>
         <v>8</v>
       </c>
       <c r="D184" s="13">
@@ -14977,6 +14977,26 @@
         <v>0</v>
       </c>
       <c r="E219" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5" ht="14" customHeight="1">
+      <c r="A220" s="6">
+        <f t="shared" si="2"/>
+        <v>219</v>
+      </c>
+      <c r="B220" s="7">
+        <f t="shared" si="12"/>
+        <v>46300</v>
+      </c>
+      <c r="C220" s="6">
+        <f t="shared" si="13"/>
+        <v>13</v>
+      </c>
+      <c r="D220" s="13">
+        <v>343</v>
+      </c>
+      <c r="E220" s="13">
         <v>0</v>
       </c>
     </row>
@@ -14989,7 +15009,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E31F5C3B-0571-4A35-9FD2-A50C21726EAB}">
-  <dimension ref="A1:J811"/>
+  <dimension ref="A1:J813"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="11.36328125" bestFit="1" customWidth="1"/>
@@ -38780,7 +38800,7 @@
     </row>
     <row r="722" spans="1:10">
       <c r="A722" s="24">
-        <f t="shared" ref="A722:A810" si="14">A720+1</f>
+        <f t="shared" ref="A722:A812" si="14">A720+1</f>
         <v>46255</v>
       </c>
       <c r="B722" s="23" t="s">
@@ -40925,7 +40945,7 @@
     </row>
     <row r="787" spans="1:10">
       <c r="A787" s="24">
-        <f t="shared" ref="A787:A811" si="15">A785+1</f>
+        <f t="shared" ref="A787:A813" si="15">A785+1</f>
         <v>46287</v>
       </c>
       <c r="B787" s="23" t="s">
@@ -41746,6 +41766,72 @@
       </c>
       <c r="J811" s="31">
         <v>6.8000000000000005E-2</v>
+      </c>
+    </row>
+    <row r="812" spans="1:10">
+      <c r="A812" s="24">
+        <f t="shared" si="14"/>
+        <v>46300</v>
+      </c>
+      <c r="B812" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C812" s="25">
+        <v>37419176</v>
+      </c>
+      <c r="D812" s="25">
+        <v>1936900</v>
+      </c>
+      <c r="E812" s="25">
+        <v>2899717</v>
+      </c>
+      <c r="F812" s="25">
+        <v>504561</v>
+      </c>
+      <c r="G812" s="25">
+        <v>42760354</v>
+      </c>
+      <c r="H812" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I812" s="27">
+        <v>0</v>
+      </c>
+      <c r="J812" s="31">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="813" spans="1:10">
+      <c r="A813" s="24">
+        <f t="shared" si="15"/>
+        <v>46300</v>
+      </c>
+      <c r="B813" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C813" s="25">
+        <v>37419176</v>
+      </c>
+      <c r="D813" s="25">
+        <v>1936900</v>
+      </c>
+      <c r="E813" s="25">
+        <v>2899717</v>
+      </c>
+      <c r="F813" s="25">
+        <v>504561</v>
+      </c>
+      <c r="G813" s="25">
+        <v>42760354</v>
+      </c>
+      <c r="H813" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I813" s="27">
+        <v>0</v>
+      </c>
+      <c r="J813" s="31">
+        <v>7.0000000000000007E-2</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/record.xlsx
+++ b/public/data/record.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\cursor-usage\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CB49EF8-354C-4F67-8D22-3DAAE1D68C24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC5D2858-B294-494A-8FF1-ED1F4F8991CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1180" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="31">
   <si>
     <t>番号</t>
   </si>
@@ -10713,7 +10713,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92559261-86B2-49A9-AE5C-FC3176987B65}">
-  <dimension ref="A1:E220"/>
+  <dimension ref="A1:E221"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="5.453125" bestFit="1" customWidth="1"/>
@@ -12108,7 +12108,7 @@
     </row>
     <row r="74" spans="1:5" s="5" customFormat="1" ht="14.5">
       <c r="A74" s="6">
-        <f t="shared" ref="A74:A220" si="2">ROW()-1</f>
+        <f t="shared" ref="A74:A221" si="2">ROW()-1</f>
         <v>73</v>
       </c>
       <c r="B74" s="7">
@@ -14167,7 +14167,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="7">
-        <f t="shared" ref="B179:B220" si="12">B178+1</f>
+        <f t="shared" ref="B179:B221" si="12">B178+1</f>
         <v>46259</v>
       </c>
       <c r="C179" s="6">
@@ -14271,7 +14271,7 @@
         <v>46264</v>
       </c>
       <c r="C184" s="6">
-        <f t="shared" ref="C184:C220" si="13">C183+1</f>
+        <f t="shared" ref="C184:C221" si="13">C183+1</f>
         <v>8</v>
       </c>
       <c r="D184" s="13">
@@ -14997,6 +14997,26 @@
         <v>343</v>
       </c>
       <c r="E220" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5" ht="14" customHeight="1">
+      <c r="A221" s="6">
+        <f t="shared" si="2"/>
+        <v>220</v>
+      </c>
+      <c r="B221" s="7">
+        <f t="shared" si="12"/>
+        <v>46301</v>
+      </c>
+      <c r="C221" s="6">
+        <f t="shared" si="13"/>
+        <v>14</v>
+      </c>
+      <c r="D221" s="13">
+        <v>21319</v>
+      </c>
+      <c r="E221" s="13">
         <v>0</v>
       </c>
     </row>
@@ -15009,7 +15029,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E31F5C3B-0571-4A35-9FD2-A50C21726EAB}">
-  <dimension ref="A1:J813"/>
+  <dimension ref="A1:J815"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="11.36328125" bestFit="1" customWidth="1"/>
@@ -38800,7 +38820,7 @@
     </row>
     <row r="722" spans="1:10">
       <c r="A722" s="24">
-        <f t="shared" ref="A722:A812" si="14">A720+1</f>
+        <f t="shared" ref="A722:A814" si="14">A720+1</f>
         <v>46255</v>
       </c>
       <c r="B722" s="23" t="s">
@@ -40945,7 +40965,7 @@
     </row>
     <row r="787" spans="1:10">
       <c r="A787" s="24">
-        <f t="shared" ref="A787:A813" si="15">A785+1</f>
+        <f t="shared" ref="A787:A815" si="15">A785+1</f>
         <v>46287</v>
       </c>
       <c r="B787" s="23" t="s">
@@ -41832,6 +41852,72 @@
       </c>
       <c r="J813" s="31">
         <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="814" spans="1:10">
+      <c r="A814" s="24">
+        <f t="shared" si="14"/>
+        <v>46301</v>
+      </c>
+      <c r="B814" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C814" s="25">
+        <v>58664636</v>
+      </c>
+      <c r="D814" s="25">
+        <v>2925715</v>
+      </c>
+      <c r="E814" s="25">
+        <v>2900105</v>
+      </c>
+      <c r="F814" s="25">
+        <v>764707</v>
+      </c>
+      <c r="G814" s="25">
+        <v>65255163</v>
+      </c>
+      <c r="H814" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I814" s="27">
+        <v>0</v>
+      </c>
+      <c r="J814" s="31">
+        <v>0.10100000000000001</v>
+      </c>
+    </row>
+    <row r="815" spans="1:10">
+      <c r="A815" s="24">
+        <f t="shared" si="15"/>
+        <v>46301</v>
+      </c>
+      <c r="B815" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C815" s="25">
+        <v>58664636</v>
+      </c>
+      <c r="D815" s="25">
+        <v>2925715</v>
+      </c>
+      <c r="E815" s="25">
+        <v>2900105</v>
+      </c>
+      <c r="F815" s="25">
+        <v>764707</v>
+      </c>
+      <c r="G815" s="25">
+        <v>65255163</v>
+      </c>
+      <c r="H815" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I815" s="27">
+        <v>0</v>
+      </c>
+      <c r="J815" s="31">
+        <v>0.10100000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/record.xlsx
+++ b/public/data/record.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\cursor-usage\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC5D2858-B294-494A-8FF1-ED1F4F8991CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B47F764-204D-4D10-829A-0D19AEC14D76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1188" uniqueCount="31">
   <si>
     <t>番号</t>
   </si>
@@ -10713,7 +10713,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92559261-86B2-49A9-AE5C-FC3176987B65}">
-  <dimension ref="A1:E221"/>
+  <dimension ref="A1:E222"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="5.453125" bestFit="1" customWidth="1"/>
@@ -12108,7 +12108,7 @@
     </row>
     <row r="74" spans="1:5" s="5" customFormat="1" ht="14.5">
       <c r="A74" s="6">
-        <f t="shared" ref="A74:A221" si="2">ROW()-1</f>
+        <f t="shared" ref="A74:A222" si="2">ROW()-1</f>
         <v>73</v>
       </c>
       <c r="B74" s="7">
@@ -14167,7 +14167,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="7">
-        <f t="shared" ref="B179:B221" si="12">B178+1</f>
+        <f t="shared" ref="B179:B222" si="12">B178+1</f>
         <v>46259</v>
       </c>
       <c r="C179" s="6">
@@ -14271,7 +14271,7 @@
         <v>46264</v>
       </c>
       <c r="C184" s="6">
-        <f t="shared" ref="C184:C221" si="13">C183+1</f>
+        <f t="shared" ref="C184:C222" si="13">C183+1</f>
         <v>8</v>
       </c>
       <c r="D184" s="13">
@@ -15017,6 +15017,26 @@
         <v>21319</v>
       </c>
       <c r="E221" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5" ht="14" customHeight="1">
+      <c r="A222" s="6">
+        <f t="shared" si="2"/>
+        <v>221</v>
+      </c>
+      <c r="B222" s="7">
+        <f t="shared" si="12"/>
+        <v>46302</v>
+      </c>
+      <c r="C222" s="6">
+        <f t="shared" si="13"/>
+        <v>15</v>
+      </c>
+      <c r="D222" s="13">
+        <v>1711</v>
+      </c>
+      <c r="E222" s="13">
         <v>0</v>
       </c>
     </row>
@@ -15029,7 +15049,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E31F5C3B-0571-4A35-9FD2-A50C21726EAB}">
-  <dimension ref="A1:J815"/>
+  <dimension ref="A1:J817"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="11.36328125" bestFit="1" customWidth="1"/>
@@ -38820,7 +38840,7 @@
     </row>
     <row r="722" spans="1:10">
       <c r="A722" s="24">
-        <f t="shared" ref="A722:A814" si="14">A720+1</f>
+        <f t="shared" ref="A722:A816" si="14">A720+1</f>
         <v>46255</v>
       </c>
       <c r="B722" s="23" t="s">
@@ -40965,7 +40985,7 @@
     </row>
     <row r="787" spans="1:10">
       <c r="A787" s="24">
-        <f t="shared" ref="A787:A815" si="15">A785+1</f>
+        <f t="shared" ref="A787:A817" si="15">A785+1</f>
         <v>46287</v>
       </c>
       <c r="B787" s="23" t="s">
@@ -41918,6 +41938,72 @@
       </c>
       <c r="J815" s="31">
         <v>0.10100000000000001</v>
+      </c>
+    </row>
+    <row r="816" spans="1:10">
+      <c r="A816" s="24">
+        <f t="shared" si="14"/>
+        <v>46302</v>
+      </c>
+      <c r="B816" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C816" s="25">
+        <v>62310961</v>
+      </c>
+      <c r="D816" s="25">
+        <v>3194173</v>
+      </c>
+      <c r="E816" s="25">
+        <v>2900241</v>
+      </c>
+      <c r="F816" s="25">
+        <v>812954</v>
+      </c>
+      <c r="G816" s="25">
+        <v>69218329</v>
+      </c>
+      <c r="H816" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I816" s="27">
+        <v>0</v>
+      </c>
+      <c r="J816" s="31">
+        <v>0.107</v>
+      </c>
+    </row>
+    <row r="817" spans="1:10">
+      <c r="A817" s="24">
+        <f t="shared" si="15"/>
+        <v>46302</v>
+      </c>
+      <c r="B817" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C817" s="25">
+        <v>62310961</v>
+      </c>
+      <c r="D817" s="25">
+        <v>3194173</v>
+      </c>
+      <c r="E817" s="25">
+        <v>2900241</v>
+      </c>
+      <c r="F817" s="25">
+        <v>812954</v>
+      </c>
+      <c r="G817" s="25">
+        <v>69218329</v>
+      </c>
+      <c r="H817" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I817" s="27">
+        <v>0</v>
+      </c>
+      <c r="J817" s="31">
+        <v>0.107</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/record.xlsx
+++ b/public/data/record.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\cursor-usage\public\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\everyday-use\cursor-usage\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B47F764-204D-4D10-829A-0D19AEC14D76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDF7E649-B56D-4163-A728-03B73102C9F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1188" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1192" uniqueCount="31">
   <si>
     <t>番号</t>
   </si>
@@ -10713,7 +10713,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92559261-86B2-49A9-AE5C-FC3176987B65}">
-  <dimension ref="A1:E222"/>
+  <dimension ref="A1:E223"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="5.453125" bestFit="1" customWidth="1"/>
@@ -12108,7 +12108,7 @@
     </row>
     <row r="74" spans="1:5" s="5" customFormat="1" ht="14.5">
       <c r="A74" s="6">
-        <f t="shared" ref="A74:A222" si="2">ROW()-1</f>
+        <f t="shared" ref="A74:A223" si="2">ROW()-1</f>
         <v>73</v>
       </c>
       <c r="B74" s="7">
@@ -14167,7 +14167,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="7">
-        <f t="shared" ref="B179:B222" si="12">B178+1</f>
+        <f t="shared" ref="B179:B223" si="12">B178+1</f>
         <v>46259</v>
       </c>
       <c r="C179" s="6">
@@ -14271,7 +14271,7 @@
         <v>46264</v>
       </c>
       <c r="C184" s="6">
-        <f t="shared" ref="C184:C222" si="13">C183+1</f>
+        <f t="shared" ref="C184:C223" si="13">C183+1</f>
         <v>8</v>
       </c>
       <c r="D184" s="13">
@@ -15037,6 +15037,26 @@
         <v>1711</v>
       </c>
       <c r="E222" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5" ht="14" customHeight="1">
+      <c r="A223" s="6">
+        <f t="shared" si="2"/>
+        <v>222</v>
+      </c>
+      <c r="B223" s="7">
+        <f t="shared" si="12"/>
+        <v>46303</v>
+      </c>
+      <c r="C223" s="6">
+        <f t="shared" si="13"/>
+        <v>16</v>
+      </c>
+      <c r="D223" s="13">
+        <v>1870</v>
+      </c>
+      <c r="E223" s="13">
         <v>0</v>
       </c>
     </row>
@@ -15049,7 +15069,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E31F5C3B-0571-4A35-9FD2-A50C21726EAB}">
-  <dimension ref="A1:J817"/>
+  <dimension ref="A1:J819"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="11.36328125" bestFit="1" customWidth="1"/>
@@ -38840,7 +38860,7 @@
     </row>
     <row r="722" spans="1:10">
       <c r="A722" s="24">
-        <f t="shared" ref="A722:A816" si="14">A720+1</f>
+        <f t="shared" ref="A722:A818" si="14">A720+1</f>
         <v>46255</v>
       </c>
       <c r="B722" s="23" t="s">
@@ -40985,7 +41005,7 @@
     </row>
     <row r="787" spans="1:10">
       <c r="A787" s="24">
-        <f t="shared" ref="A787:A817" si="15">A785+1</f>
+        <f t="shared" ref="A787:A819" si="15">A785+1</f>
         <v>46287</v>
       </c>
       <c r="B787" s="23" t="s">
@@ -42004,6 +42024,72 @@
       </c>
       <c r="J817" s="31">
         <v>0.107</v>
+      </c>
+    </row>
+    <row r="818" spans="1:10">
+      <c r="A818" s="24">
+        <f t="shared" si="14"/>
+        <v>46303</v>
+      </c>
+      <c r="B818" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C818" s="25">
+        <v>69129821</v>
+      </c>
+      <c r="D818" s="25">
+        <v>3780263</v>
+      </c>
+      <c r="E818" s="25">
+        <v>2900441</v>
+      </c>
+      <c r="F818" s="25">
+        <v>890592</v>
+      </c>
+      <c r="G818" s="25">
+        <v>76701117</v>
+      </c>
+      <c r="H818" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I818" s="27">
+        <v>0</v>
+      </c>
+      <c r="J818" s="31">
+        <v>0.11799999999999999</v>
+      </c>
+    </row>
+    <row r="819" spans="1:10">
+      <c r="A819" s="24">
+        <f t="shared" si="15"/>
+        <v>46303</v>
+      </c>
+      <c r="B819" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C819" s="25">
+        <v>69129821</v>
+      </c>
+      <c r="D819" s="25">
+        <v>3780263</v>
+      </c>
+      <c r="E819" s="25">
+        <v>2900441</v>
+      </c>
+      <c r="F819" s="25">
+        <v>890592</v>
+      </c>
+      <c r="G819" s="25">
+        <v>76701117</v>
+      </c>
+      <c r="H819" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I819" s="27">
+        <v>0</v>
+      </c>
+      <c r="J819" s="31">
+        <v>0.11799999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/record.xlsx
+++ b/public/data/record.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\everyday-use\cursor-usage\public\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\cursor-usage\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDF7E649-B56D-4163-A728-03B73102C9F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E924B406-091C-4783-8112-D78C3598246A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cursor Usageの記録" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1192" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1196" uniqueCount="31">
   <si>
     <t>番号</t>
   </si>
@@ -10713,7 +10713,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92559261-86B2-49A9-AE5C-FC3176987B65}">
-  <dimension ref="A1:E223"/>
+  <dimension ref="A1:E224"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="5.453125" bestFit="1" customWidth="1"/>
@@ -12108,7 +12108,7 @@
     </row>
     <row r="74" spans="1:5" s="5" customFormat="1" ht="14.5">
       <c r="A74" s="6">
-        <f t="shared" ref="A74:A223" si="2">ROW()-1</f>
+        <f t="shared" ref="A74:A224" si="2">ROW()-1</f>
         <v>73</v>
       </c>
       <c r="B74" s="7">
@@ -14167,7 +14167,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="7">
-        <f t="shared" ref="B179:B223" si="12">B178+1</f>
+        <f t="shared" ref="B179:B224" si="12">B178+1</f>
         <v>46259</v>
       </c>
       <c r="C179" s="6">
@@ -14271,7 +14271,7 @@
         <v>46264</v>
       </c>
       <c r="C184" s="6">
-        <f t="shared" ref="C184:C223" si="13">C183+1</f>
+        <f t="shared" ref="C184:C224" si="13">C183+1</f>
         <v>8</v>
       </c>
       <c r="D184" s="13">
@@ -15057,6 +15057,26 @@
         <v>1870</v>
       </c>
       <c r="E223" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5" ht="14" customHeight="1">
+      <c r="A224" s="6">
+        <f t="shared" si="2"/>
+        <v>223</v>
+      </c>
+      <c r="B224" s="7">
+        <f t="shared" si="12"/>
+        <v>46304</v>
+      </c>
+      <c r="C224" s="6">
+        <f t="shared" si="13"/>
+        <v>17</v>
+      </c>
+      <c r="D224" s="13">
+        <v>9920</v>
+      </c>
+      <c r="E224" s="13">
         <v>0</v>
       </c>
     </row>
@@ -15069,7 +15089,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E31F5C3B-0571-4A35-9FD2-A50C21726EAB}">
-  <dimension ref="A1:J819"/>
+  <dimension ref="A1:J821"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="11.36328125" bestFit="1" customWidth="1"/>
@@ -38860,7 +38880,7 @@
     </row>
     <row r="722" spans="1:10">
       <c r="A722" s="24">
-        <f t="shared" ref="A722:A818" si="14">A720+1</f>
+        <f t="shared" ref="A722:A820" si="14">A720+1</f>
         <v>46255</v>
       </c>
       <c r="B722" s="23" t="s">
@@ -41005,7 +41025,7 @@
     </row>
     <row r="787" spans="1:10">
       <c r="A787" s="24">
-        <f t="shared" ref="A787:A819" si="15">A785+1</f>
+        <f t="shared" ref="A787:A821" si="15">A785+1</f>
         <v>46287</v>
       </c>
       <c r="B787" s="23" t="s">
@@ -42090,6 +42110,72 @@
       </c>
       <c r="J819" s="31">
         <v>0.11799999999999999</v>
+      </c>
+    </row>
+    <row r="820" spans="1:10">
+      <c r="A820" s="24">
+        <f t="shared" si="14"/>
+        <v>46304</v>
+      </c>
+      <c r="B820" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C820" s="25">
+        <v>90416571</v>
+      </c>
+      <c r="D820" s="25">
+        <v>4804899</v>
+      </c>
+      <c r="E820" s="25">
+        <v>2900869</v>
+      </c>
+      <c r="F820" s="25">
+        <v>1110801</v>
+      </c>
+      <c r="G820" s="25">
+        <v>99233140</v>
+      </c>
+      <c r="H820" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I820" s="27">
+        <v>0</v>
+      </c>
+      <c r="J820" s="31">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="821" spans="1:10">
+      <c r="A821" s="24">
+        <f t="shared" si="15"/>
+        <v>46304</v>
+      </c>
+      <c r="B821" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C821" s="25">
+        <v>90416571</v>
+      </c>
+      <c r="D821" s="25">
+        <v>4804899</v>
+      </c>
+      <c r="E821" s="25">
+        <v>2900869</v>
+      </c>
+      <c r="F821" s="25">
+        <v>1110801</v>
+      </c>
+      <c r="G821" s="25">
+        <v>99233140</v>
+      </c>
+      <c r="H821" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I821" s="27">
+        <v>0</v>
+      </c>
+      <c r="J821" s="31">
+        <v>0.15</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/record.xlsx
+++ b/public/data/record.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\cursor-usage\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E924B406-091C-4783-8112-D78C3598246A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8BAD164-C56B-4D2A-8136-0166EC7EFA55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cursor Usageの記録" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1196" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1200" uniqueCount="31">
   <si>
     <t>番号</t>
   </si>
@@ -10713,11 +10713,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92559261-86B2-49A9-AE5C-FC3176987B65}">
-  <dimension ref="A1:E224"/>
+  <dimension ref="A1:E225"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="5.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="5.453125" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="13.90625" style="34" bestFit="1" customWidth="1"/>
   </cols>
@@ -12108,7 +12108,7 @@
     </row>
     <row r="74" spans="1:5" s="5" customFormat="1" ht="14.5">
       <c r="A74" s="6">
-        <f t="shared" ref="A74:A224" si="2">ROW()-1</f>
+        <f t="shared" ref="A74:A225" si="2">ROW()-1</f>
         <v>73</v>
       </c>
       <c r="B74" s="7">
@@ -14167,7 +14167,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="7">
-        <f t="shared" ref="B179:B224" si="12">B178+1</f>
+        <f t="shared" ref="B179:B225" si="12">B178+1</f>
         <v>46259</v>
       </c>
       <c r="C179" s="6">
@@ -14271,7 +14271,7 @@
         <v>46264</v>
       </c>
       <c r="C184" s="6">
-        <f t="shared" ref="C184:C224" si="13">C183+1</f>
+        <f t="shared" ref="C184:C225" si="13">C183+1</f>
         <v>8</v>
       </c>
       <c r="D184" s="13">
@@ -15077,6 +15077,26 @@
         <v>9920</v>
       </c>
       <c r="E224" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5" ht="14" customHeight="1">
+      <c r="A225" s="6">
+        <f t="shared" si="2"/>
+        <v>224</v>
+      </c>
+      <c r="B225" s="7">
+        <f t="shared" si="12"/>
+        <v>46305</v>
+      </c>
+      <c r="C225" s="6">
+        <f t="shared" si="13"/>
+        <v>18</v>
+      </c>
+      <c r="D225" s="13">
+        <v>8778</v>
+      </c>
+      <c r="E225" s="13">
         <v>0</v>
       </c>
     </row>
@@ -15089,7 +15109,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E31F5C3B-0571-4A35-9FD2-A50C21726EAB}">
-  <dimension ref="A1:J821"/>
+  <dimension ref="A1:J823"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="11.36328125" bestFit="1" customWidth="1"/>
@@ -15098,7 +15118,7 @@
     <col min="4" max="4" width="12.81640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.08984375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.54296875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.6328125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12.6328125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.7265625" bestFit="1" customWidth="1"/>
@@ -38880,7 +38900,7 @@
     </row>
     <row r="722" spans="1:10">
       <c r="A722" s="24">
-        <f t="shared" ref="A722:A820" si="14">A720+1</f>
+        <f t="shared" ref="A722:A822" si="14">A720+1</f>
         <v>46255</v>
       </c>
       <c r="B722" s="23" t="s">
@@ -41025,7 +41045,7 @@
     </row>
     <row r="787" spans="1:10">
       <c r="A787" s="24">
-        <f t="shared" ref="A787:A821" si="15">A785+1</f>
+        <f t="shared" ref="A787:A823" si="15">A785+1</f>
         <v>46287</v>
       </c>
       <c r="B787" s="23" t="s">
@@ -42176,6 +42196,72 @@
       </c>
       <c r="J821" s="31">
         <v>0.15</v>
+      </c>
+    </row>
+    <row r="822" spans="1:10">
+      <c r="A822" s="24">
+        <f t="shared" si="14"/>
+        <v>46305</v>
+      </c>
+      <c r="B822" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C822" s="25">
+        <v>109143774</v>
+      </c>
+      <c r="D822" s="25">
+        <v>6008110</v>
+      </c>
+      <c r="E822" s="25">
+        <v>2901259</v>
+      </c>
+      <c r="F822" s="25">
+        <v>1329816</v>
+      </c>
+      <c r="G822" s="25">
+        <v>119382959</v>
+      </c>
+      <c r="H822" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I822" s="27">
+        <v>0</v>
+      </c>
+      <c r="J822" s="31">
+        <v>0.17899999999999999</v>
+      </c>
+    </row>
+    <row r="823" spans="1:10">
+      <c r="A823" s="24">
+        <f t="shared" si="15"/>
+        <v>46305</v>
+      </c>
+      <c r="B823" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C823" s="25">
+        <v>109143774</v>
+      </c>
+      <c r="D823" s="25">
+        <v>6008110</v>
+      </c>
+      <c r="E823" s="25">
+        <v>2901259</v>
+      </c>
+      <c r="F823" s="25">
+        <v>1329816</v>
+      </c>
+      <c r="G823" s="25">
+        <v>119382959</v>
+      </c>
+      <c r="H823" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I823" s="27">
+        <v>0</v>
+      </c>
+      <c r="J823" s="31">
+        <v>0.17899999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/record.xlsx
+++ b/public/data/record.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\cursor-usage\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8BAD164-C56B-4D2A-8136-0166EC7EFA55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B0BB9D6-3A48-46C6-9BD1-87D1641D18D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1200" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1204" uniqueCount="31">
   <si>
     <t>番号</t>
   </si>
@@ -10713,7 +10713,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92559261-86B2-49A9-AE5C-FC3176987B65}">
-  <dimension ref="A1:E225"/>
+  <dimension ref="A1:E226"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="5.453125" bestFit="1" customWidth="1"/>
@@ -12108,7 +12108,7 @@
     </row>
     <row r="74" spans="1:5" s="5" customFormat="1" ht="14.5">
       <c r="A74" s="6">
-        <f t="shared" ref="A74:A225" si="2">ROW()-1</f>
+        <f t="shared" ref="A74:A226" si="2">ROW()-1</f>
         <v>73</v>
       </c>
       <c r="B74" s="7">
@@ -14167,7 +14167,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="7">
-        <f t="shared" ref="B179:B225" si="12">B178+1</f>
+        <f t="shared" ref="B179:B226" si="12">B178+1</f>
         <v>46259</v>
       </c>
       <c r="C179" s="6">
@@ -14271,7 +14271,7 @@
         <v>46264</v>
       </c>
       <c r="C184" s="6">
-        <f t="shared" ref="C184:C225" si="13">C183+1</f>
+        <f t="shared" ref="C184:C226" si="13">C183+1</f>
         <v>8</v>
       </c>
       <c r="D184" s="13">
@@ -15097,6 +15097,26 @@
         <v>8778</v>
       </c>
       <c r="E225" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5" ht="14" customHeight="1">
+      <c r="A226" s="6">
+        <f t="shared" si="2"/>
+        <v>225</v>
+      </c>
+      <c r="B226" s="7">
+        <f t="shared" si="12"/>
+        <v>46306</v>
+      </c>
+      <c r="C226" s="6">
+        <f t="shared" si="13"/>
+        <v>19</v>
+      </c>
+      <c r="D226" s="13">
+        <v>2067</v>
+      </c>
+      <c r="E226" s="13">
         <v>0</v>
       </c>
     </row>
@@ -15109,7 +15129,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E31F5C3B-0571-4A35-9FD2-A50C21726EAB}">
-  <dimension ref="A1:J823"/>
+  <dimension ref="A1:J825"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="11.36328125" bestFit="1" customWidth="1"/>
@@ -38900,7 +38920,7 @@
     </row>
     <row r="722" spans="1:10">
       <c r="A722" s="24">
-        <f t="shared" ref="A722:A822" si="14">A720+1</f>
+        <f t="shared" ref="A722:A824" si="14">A720+1</f>
         <v>46255</v>
       </c>
       <c r="B722" s="23" t="s">
@@ -41045,7 +41065,7 @@
     </row>
     <row r="787" spans="1:10">
       <c r="A787" s="24">
-        <f t="shared" ref="A787:A823" si="15">A785+1</f>
+        <f t="shared" ref="A787:A825" si="15">A785+1</f>
         <v>46287</v>
       </c>
       <c r="B787" s="23" t="s">
@@ -42262,6 +42282,72 @@
       </c>
       <c r="J823" s="31">
         <v>0.17899999999999999</v>
+      </c>
+    </row>
+    <row r="824" spans="1:10">
+      <c r="A824" s="24">
+        <f t="shared" si="14"/>
+        <v>46306</v>
+      </c>
+      <c r="B824" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C824" s="25">
+        <v>125567357</v>
+      </c>
+      <c r="D824" s="25">
+        <v>7273563</v>
+      </c>
+      <c r="E824" s="25">
+        <v>2901581</v>
+      </c>
+      <c r="F824" s="25">
+        <v>1463208</v>
+      </c>
+      <c r="G824" s="25">
+        <v>137205709</v>
+      </c>
+      <c r="H824" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I824" s="27">
+        <v>0</v>
+      </c>
+      <c r="J824" s="31">
+        <v>0.20399999999999999</v>
+      </c>
+    </row>
+    <row r="825" spans="1:10">
+      <c r="A825" s="24">
+        <f t="shared" si="15"/>
+        <v>46306</v>
+      </c>
+      <c r="B825" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C825" s="25">
+        <v>125567357</v>
+      </c>
+      <c r="D825" s="25">
+        <v>7273563</v>
+      </c>
+      <c r="E825" s="25">
+        <v>2901581</v>
+      </c>
+      <c r="F825" s="25">
+        <v>1463208</v>
+      </c>
+      <c r="G825" s="25">
+        <v>137205709</v>
+      </c>
+      <c r="H825" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I825" s="27">
+        <v>0</v>
+      </c>
+      <c r="J825" s="31">
+        <v>0.20399999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/record.xlsx
+++ b/public/data/record.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\cursor-usage\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B0BB9D6-3A48-46C6-9BD1-87D1641D18D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70114337-DA2C-4773-8A17-F1315E8D79EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1204" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1208" uniqueCount="31">
   <si>
     <t>番号</t>
   </si>
@@ -10713,7 +10713,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92559261-86B2-49A9-AE5C-FC3176987B65}">
-  <dimension ref="A1:E226"/>
+  <dimension ref="A1:E227"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="5.453125" bestFit="1" customWidth="1"/>
@@ -12108,7 +12108,7 @@
     </row>
     <row r="74" spans="1:5" s="5" customFormat="1" ht="14.5">
       <c r="A74" s="6">
-        <f t="shared" ref="A74:A226" si="2">ROW()-1</f>
+        <f t="shared" ref="A74:A227" si="2">ROW()-1</f>
         <v>73</v>
       </c>
       <c r="B74" s="7">
@@ -14167,7 +14167,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="7">
-        <f t="shared" ref="B179:B226" si="12">B178+1</f>
+        <f t="shared" ref="B179:B227" si="12">B178+1</f>
         <v>46259</v>
       </c>
       <c r="C179" s="6">
@@ -14271,7 +14271,7 @@
         <v>46264</v>
       </c>
       <c r="C184" s="6">
-        <f t="shared" ref="C184:C226" si="13">C183+1</f>
+        <f t="shared" ref="C184:C227" si="13">C183+1</f>
         <v>8</v>
       </c>
       <c r="D184" s="13">
@@ -15117,6 +15117,26 @@
         <v>2067</v>
       </c>
       <c r="E226" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5" ht="14" customHeight="1">
+      <c r="A227" s="6">
+        <f t="shared" si="2"/>
+        <v>226</v>
+      </c>
+      <c r="B227" s="7">
+        <f t="shared" si="12"/>
+        <v>46307</v>
+      </c>
+      <c r="C227" s="6">
+        <f t="shared" si="13"/>
+        <v>20</v>
+      </c>
+      <c r="D227" s="13">
+        <v>1284</v>
+      </c>
+      <c r="E227" s="13">
         <v>0</v>
       </c>
     </row>
@@ -15129,7 +15149,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E31F5C3B-0571-4A35-9FD2-A50C21726EAB}">
-  <dimension ref="A1:J825"/>
+  <dimension ref="A1:J827"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="11.36328125" bestFit="1" customWidth="1"/>
@@ -38920,7 +38940,7 @@
     </row>
     <row r="722" spans="1:10">
       <c r="A722" s="24">
-        <f t="shared" ref="A722:A824" si="14">A720+1</f>
+        <f t="shared" ref="A722:A826" si="14">A720+1</f>
         <v>46255</v>
       </c>
       <c r="B722" s="23" t="s">
@@ -41065,7 +41085,7 @@
     </row>
     <row r="787" spans="1:10">
       <c r="A787" s="24">
-        <f t="shared" ref="A787:A825" si="15">A785+1</f>
+        <f t="shared" ref="A787:A827" si="15">A785+1</f>
         <v>46287</v>
       </c>
       <c r="B787" s="23" t="s">
@@ -42348,6 +42368,72 @@
       </c>
       <c r="J825" s="31">
         <v>0.20399999999999999</v>
+      </c>
+    </row>
+    <row r="826" spans="1:10">
+      <c r="A826" s="24">
+        <f t="shared" si="14"/>
+        <v>46307</v>
+      </c>
+      <c r="B826" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C826" s="25">
+        <v>144787951</v>
+      </c>
+      <c r="D826" s="25">
+        <v>8688710</v>
+      </c>
+      <c r="E826" s="25">
+        <v>2901937</v>
+      </c>
+      <c r="F826" s="25">
+        <v>1599706</v>
+      </c>
+      <c r="G826" s="25">
+        <v>157978304</v>
+      </c>
+      <c r="H826" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I826" s="27">
+        <v>0</v>
+      </c>
+      <c r="J826" s="31">
+        <v>0.23400000000000001</v>
+      </c>
+    </row>
+    <row r="827" spans="1:10">
+      <c r="A827" s="24">
+        <f t="shared" si="15"/>
+        <v>46307</v>
+      </c>
+      <c r="B827" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C827" s="25">
+        <v>144787951</v>
+      </c>
+      <c r="D827" s="25">
+        <v>8688710</v>
+      </c>
+      <c r="E827" s="25">
+        <v>2901937</v>
+      </c>
+      <c r="F827" s="25">
+        <v>1599706</v>
+      </c>
+      <c r="G827" s="25">
+        <v>157978304</v>
+      </c>
+      <c r="H827" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I827" s="27">
+        <v>0</v>
+      </c>
+      <c r="J827" s="31">
+        <v>0.23400000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/record.xlsx
+++ b/public/data/record.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\cursor-usage\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70114337-DA2C-4773-8A17-F1315E8D79EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5E86467-D44A-44A4-9956-49A359327F98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1208" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1212" uniqueCount="31">
   <si>
     <t>番号</t>
   </si>
@@ -10713,7 +10713,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92559261-86B2-49A9-AE5C-FC3176987B65}">
-  <dimension ref="A1:E227"/>
+  <dimension ref="A1:E228"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="5.453125" bestFit="1" customWidth="1"/>
@@ -12108,7 +12108,7 @@
     </row>
     <row r="74" spans="1:5" s="5" customFormat="1" ht="14.5">
       <c r="A74" s="6">
-        <f t="shared" ref="A74:A227" si="2">ROW()-1</f>
+        <f t="shared" ref="A74:A228" si="2">ROW()-1</f>
         <v>73</v>
       </c>
       <c r="B74" s="7">
@@ -14167,7 +14167,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="7">
-        <f t="shared" ref="B179:B227" si="12">B178+1</f>
+        <f t="shared" ref="B179:B228" si="12">B178+1</f>
         <v>46259</v>
       </c>
       <c r="C179" s="6">
@@ -14271,7 +14271,7 @@
         <v>46264</v>
       </c>
       <c r="C184" s="6">
-        <f t="shared" ref="C184:C227" si="13">C183+1</f>
+        <f t="shared" ref="C184:C228" si="13">C183+1</f>
         <v>8</v>
       </c>
       <c r="D184" s="13">
@@ -15137,6 +15137,26 @@
         <v>1284</v>
       </c>
       <c r="E227" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5" ht="14" customHeight="1">
+      <c r="A228" s="6">
+        <f t="shared" si="2"/>
+        <v>227</v>
+      </c>
+      <c r="B228" s="7">
+        <f t="shared" si="12"/>
+        <v>46308</v>
+      </c>
+      <c r="C228" s="6">
+        <f t="shared" si="13"/>
+        <v>21</v>
+      </c>
+      <c r="D228" s="13">
+        <v>0</v>
+      </c>
+      <c r="E228" s="13">
         <v>0</v>
       </c>
     </row>
@@ -15149,7 +15169,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E31F5C3B-0571-4A35-9FD2-A50C21726EAB}">
-  <dimension ref="A1:J827"/>
+  <dimension ref="A1:J829"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="11.36328125" bestFit="1" customWidth="1"/>
@@ -38940,7 +38960,7 @@
     </row>
     <row r="722" spans="1:10">
       <c r="A722" s="24">
-        <f t="shared" ref="A722:A826" si="14">A720+1</f>
+        <f t="shared" ref="A722:A828" si="14">A720+1</f>
         <v>46255</v>
       </c>
       <c r="B722" s="23" t="s">
@@ -41085,7 +41105,7 @@
     </row>
     <row r="787" spans="1:10">
       <c r="A787" s="24">
-        <f t="shared" ref="A787:A827" si="15">A785+1</f>
+        <f t="shared" ref="A787:A829" si="15">A785+1</f>
         <v>46287</v>
       </c>
       <c r="B787" s="23" t="s">
@@ -42433,6 +42453,72 @@
         <v>0</v>
       </c>
       <c r="J827" s="31">
+        <v>0.23400000000000001</v>
+      </c>
+    </row>
+    <row r="828" spans="1:10">
+      <c r="A828" s="24">
+        <f t="shared" si="14"/>
+        <v>46308</v>
+      </c>
+      <c r="B828" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C828" s="25">
+        <v>144787951</v>
+      </c>
+      <c r="D828" s="25">
+        <v>8688710</v>
+      </c>
+      <c r="E828" s="25">
+        <v>2901937</v>
+      </c>
+      <c r="F828" s="25">
+        <v>1599706</v>
+      </c>
+      <c r="G828" s="25">
+        <v>157978304</v>
+      </c>
+      <c r="H828" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I828" s="27">
+        <v>0</v>
+      </c>
+      <c r="J828" s="31">
+        <v>0.23400000000000001</v>
+      </c>
+    </row>
+    <row r="829" spans="1:10">
+      <c r="A829" s="24">
+        <f t="shared" si="15"/>
+        <v>46308</v>
+      </c>
+      <c r="B829" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C829" s="25">
+        <v>144787951</v>
+      </c>
+      <c r="D829" s="25">
+        <v>8688710</v>
+      </c>
+      <c r="E829" s="25">
+        <v>2901937</v>
+      </c>
+      <c r="F829" s="25">
+        <v>1599706</v>
+      </c>
+      <c r="G829" s="25">
+        <v>157978304</v>
+      </c>
+      <c r="H829" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I829" s="27">
+        <v>0</v>
+      </c>
+      <c r="J829" s="31">
         <v>0.23400000000000001</v>
       </c>
     </row>

--- a/public/data/record.xlsx
+++ b/public/data/record.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\cursor-usage\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5E86467-D44A-44A4-9956-49A359327F98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33DF3135-B935-4FFE-AC96-7EA3AC3C4E1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1212" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1216" uniqueCount="31">
   <si>
     <t>番号</t>
   </si>
@@ -10713,7 +10713,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92559261-86B2-49A9-AE5C-FC3176987B65}">
-  <dimension ref="A1:E228"/>
+  <dimension ref="A1:E229"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="5.453125" bestFit="1" customWidth="1"/>
@@ -12108,7 +12108,7 @@
     </row>
     <row r="74" spans="1:5" s="5" customFormat="1" ht="14.5">
       <c r="A74" s="6">
-        <f t="shared" ref="A74:A228" si="2">ROW()-1</f>
+        <f t="shared" ref="A74:A229" si="2">ROW()-1</f>
         <v>73</v>
       </c>
       <c r="B74" s="7">
@@ -14167,7 +14167,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="7">
-        <f t="shared" ref="B179:B228" si="12">B178+1</f>
+        <f t="shared" ref="B179:B229" si="12">B178+1</f>
         <v>46259</v>
       </c>
       <c r="C179" s="6">
@@ -14271,7 +14271,7 @@
         <v>46264</v>
       </c>
       <c r="C184" s="6">
-        <f t="shared" ref="C184:C228" si="13">C183+1</f>
+        <f t="shared" ref="C184:C229" si="13">C183+1</f>
         <v>8</v>
       </c>
       <c r="D184" s="13">
@@ -15154,9 +15154,29 @@
         <v>21</v>
       </c>
       <c r="D228" s="13">
-        <v>0</v>
+        <v>3468</v>
       </c>
       <c r="E228" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5" ht="14" customHeight="1">
+      <c r="A229" s="6">
+        <f t="shared" si="2"/>
+        <v>228</v>
+      </c>
+      <c r="B229" s="7">
+        <f t="shared" si="12"/>
+        <v>46309</v>
+      </c>
+      <c r="C229" s="6">
+        <f t="shared" si="13"/>
+        <v>22</v>
+      </c>
+      <c r="D229" s="13">
+        <v>0</v>
+      </c>
+      <c r="E229" s="13">
         <v>0</v>
       </c>
     </row>
@@ -15169,7 +15189,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E31F5C3B-0571-4A35-9FD2-A50C21726EAB}">
-  <dimension ref="A1:J829"/>
+  <dimension ref="A1:J831"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="11.36328125" bestFit="1" customWidth="1"/>
@@ -38960,7 +38980,7 @@
     </row>
     <row r="722" spans="1:10">
       <c r="A722" s="24">
-        <f t="shared" ref="A722:A828" si="14">A720+1</f>
+        <f t="shared" ref="A722:A830" si="14">A720+1</f>
         <v>46255</v>
       </c>
       <c r="B722" s="23" t="s">
@@ -41105,7 +41125,7 @@
     </row>
     <row r="787" spans="1:10">
       <c r="A787" s="24">
-        <f t="shared" ref="A787:A829" si="15">A785+1</f>
+        <f t="shared" ref="A787:A831" si="15">A785+1</f>
         <v>46287</v>
       </c>
       <c r="B787" s="23" t="s">
@@ -42520,6 +42540,72 @@
       </c>
       <c r="J829" s="31">
         <v>0.23400000000000001</v>
+      </c>
+    </row>
+    <row r="830" spans="1:10">
+      <c r="A830" s="24">
+        <f t="shared" si="14"/>
+        <v>46309</v>
+      </c>
+      <c r="B830" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C830" s="25">
+        <v>152029544</v>
+      </c>
+      <c r="D830" s="25">
+        <v>9156395</v>
+      </c>
+      <c r="E830" s="25">
+        <v>2902221</v>
+      </c>
+      <c r="F830" s="25">
+        <v>1692157</v>
+      </c>
+      <c r="G830" s="25">
+        <v>165780317</v>
+      </c>
+      <c r="H830" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I830" s="27">
+        <v>0</v>
+      </c>
+      <c r="J830" s="31">
+        <v>0.245</v>
+      </c>
+    </row>
+    <row r="831" spans="1:10">
+      <c r="A831" s="24">
+        <f t="shared" si="15"/>
+        <v>46309</v>
+      </c>
+      <c r="B831" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C831" s="25">
+        <v>152029544</v>
+      </c>
+      <c r="D831" s="25">
+        <v>9156395</v>
+      </c>
+      <c r="E831" s="25">
+        <v>2902221</v>
+      </c>
+      <c r="F831" s="25">
+        <v>1692157</v>
+      </c>
+      <c r="G831" s="25">
+        <v>165780317</v>
+      </c>
+      <c r="H831" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I831" s="27">
+        <v>0</v>
+      </c>
+      <c r="J831" s="31">
+        <v>0.245</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/record.xlsx
+++ b/public/data/record.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\cursor-usage\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33DF3135-B935-4FFE-AC96-7EA3AC3C4E1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFFCB9A8-C074-4936-8AA0-5725F1C1F92B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1216" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1220" uniqueCount="31">
   <si>
     <t>番号</t>
   </si>
@@ -10713,7 +10713,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92559261-86B2-49A9-AE5C-FC3176987B65}">
-  <dimension ref="A1:E229"/>
+  <dimension ref="A1:E230"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="5.453125" bestFit="1" customWidth="1"/>
@@ -12108,7 +12108,7 @@
     </row>
     <row r="74" spans="1:5" s="5" customFormat="1" ht="14.5">
       <c r="A74" s="6">
-        <f t="shared" ref="A74:A229" si="2">ROW()-1</f>
+        <f t="shared" ref="A74:A230" si="2">ROW()-1</f>
         <v>73</v>
       </c>
       <c r="B74" s="7">
@@ -14167,7 +14167,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="7">
-        <f t="shared" ref="B179:B229" si="12">B178+1</f>
+        <f t="shared" ref="B179:B230" si="12">B178+1</f>
         <v>46259</v>
       </c>
       <c r="C179" s="6">
@@ -14271,7 +14271,7 @@
         <v>46264</v>
       </c>
       <c r="C184" s="6">
-        <f t="shared" ref="C184:C229" si="13">C183+1</f>
+        <f t="shared" ref="C184:C230" si="13">C183+1</f>
         <v>8</v>
       </c>
       <c r="D184" s="13">
@@ -15177,6 +15177,26 @@
         <v>0</v>
       </c>
       <c r="E229" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5" ht="14" customHeight="1">
+      <c r="A230" s="6">
+        <f t="shared" si="2"/>
+        <v>229</v>
+      </c>
+      <c r="B230" s="7">
+        <f t="shared" si="12"/>
+        <v>46310</v>
+      </c>
+      <c r="C230" s="6">
+        <f t="shared" si="13"/>
+        <v>23</v>
+      </c>
+      <c r="D230" s="13">
+        <v>0</v>
+      </c>
+      <c r="E230" s="13">
         <v>0</v>
       </c>
     </row>
@@ -15189,7 +15209,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E31F5C3B-0571-4A35-9FD2-A50C21726EAB}">
-  <dimension ref="A1:J831"/>
+  <dimension ref="A1:J833"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="11.36328125" bestFit="1" customWidth="1"/>
@@ -38980,7 +39000,7 @@
     </row>
     <row r="722" spans="1:10">
       <c r="A722" s="24">
-        <f t="shared" ref="A722:A830" si="14">A720+1</f>
+        <f t="shared" ref="A722:A832" si="14">A720+1</f>
         <v>46255</v>
       </c>
       <c r="B722" s="23" t="s">
@@ -41125,7 +41145,7 @@
     </row>
     <row r="787" spans="1:10">
       <c r="A787" s="24">
-        <f t="shared" ref="A787:A831" si="15">A785+1</f>
+        <f t="shared" ref="A787:A833" si="15">A785+1</f>
         <v>46287</v>
       </c>
       <c r="B787" s="23" t="s">
@@ -42605,6 +42625,72 @@
         <v>0</v>
       </c>
       <c r="J831" s="31">
+        <v>0.245</v>
+      </c>
+    </row>
+    <row r="832" spans="1:10">
+      <c r="A832" s="24">
+        <f t="shared" si="14"/>
+        <v>46310</v>
+      </c>
+      <c r="B832" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C832" s="25">
+        <v>152029544</v>
+      </c>
+      <c r="D832" s="25">
+        <v>9156395</v>
+      </c>
+      <c r="E832" s="25">
+        <v>2902221</v>
+      </c>
+      <c r="F832" s="25">
+        <v>1692157</v>
+      </c>
+      <c r="G832" s="25">
+        <v>165780317</v>
+      </c>
+      <c r="H832" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I832" s="27">
+        <v>0</v>
+      </c>
+      <c r="J832" s="31">
+        <v>0.245</v>
+      </c>
+    </row>
+    <row r="833" spans="1:10">
+      <c r="A833" s="24">
+        <f t="shared" si="15"/>
+        <v>46310</v>
+      </c>
+      <c r="B833" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C833" s="25">
+        <v>152029544</v>
+      </c>
+      <c r="D833" s="25">
+        <v>9156395</v>
+      </c>
+      <c r="E833" s="25">
+        <v>2902221</v>
+      </c>
+      <c r="F833" s="25">
+        <v>1692157</v>
+      </c>
+      <c r="G833" s="25">
+        <v>165780317</v>
+      </c>
+      <c r="H833" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I833" s="27">
+        <v>0</v>
+      </c>
+      <c r="J833" s="31">
         <v>0.245</v>
       </c>
     </row>

--- a/public/data/record.xlsx
+++ b/public/data/record.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\cursor-usage\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFFCB9A8-C074-4936-8AA0-5725F1C1F92B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5595D47E-1429-4951-8C2C-B76ECD7BB9DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19110" yWindow="0" windowWidth="19290" windowHeight="20880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cursor Usageの記録" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1220" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1228" uniqueCount="31">
   <si>
     <t>番号</t>
   </si>
@@ -10713,7 +10713,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92559261-86B2-49A9-AE5C-FC3176987B65}">
-  <dimension ref="A1:E230"/>
+  <dimension ref="A1:E231"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="5.453125" bestFit="1" customWidth="1"/>
@@ -12108,7 +12108,7 @@
     </row>
     <row r="74" spans="1:5" s="5" customFormat="1" ht="14.5">
       <c r="A74" s="6">
-        <f t="shared" ref="A74:A230" si="2">ROW()-1</f>
+        <f t="shared" ref="A74:A231" si="2">ROW()-1</f>
         <v>73</v>
       </c>
       <c r="B74" s="7">
@@ -14167,7 +14167,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="7">
-        <f t="shared" ref="B179:B230" si="12">B178+1</f>
+        <f t="shared" ref="B179:B231" si="12">B178+1</f>
         <v>46259</v>
       </c>
       <c r="C179" s="6">
@@ -14271,7 +14271,7 @@
         <v>46264</v>
       </c>
       <c r="C184" s="6">
-        <f t="shared" ref="C184:C230" si="13">C183+1</f>
+        <f t="shared" ref="C184:C231" si="13">C183+1</f>
         <v>8</v>
       </c>
       <c r="D184" s="13">
@@ -15146,15 +15146,15 @@
         <v>227</v>
       </c>
       <c r="B228" s="7">
-        <f t="shared" si="12"/>
+        <f>B227+1</f>
         <v>46308</v>
       </c>
       <c r="C228" s="6">
-        <f t="shared" si="13"/>
+        <f>C227+1</f>
         <v>21</v>
       </c>
       <c r="D228" s="13">
-        <v>3468</v>
+        <v>0</v>
       </c>
       <c r="E228" s="13">
         <v>0</v>
@@ -15174,7 +15174,7 @@
         <v>22</v>
       </c>
       <c r="D229" s="13">
-        <v>0</v>
+        <v>3468</v>
       </c>
       <c r="E229" s="13">
         <v>0</v>
@@ -15197,6 +15197,26 @@
         <v>0</v>
       </c>
       <c r="E230" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5" ht="14" customHeight="1">
+      <c r="A231" s="6">
+        <f t="shared" si="2"/>
+        <v>230</v>
+      </c>
+      <c r="B231" s="7">
+        <f t="shared" si="12"/>
+        <v>46311</v>
+      </c>
+      <c r="C231" s="6">
+        <f t="shared" si="13"/>
+        <v>24</v>
+      </c>
+      <c r="D231" s="13">
+        <v>6540</v>
+      </c>
+      <c r="E231" s="13">
         <v>0</v>
       </c>
     </row>
@@ -15209,7 +15229,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E31F5C3B-0571-4A35-9FD2-A50C21726EAB}">
-  <dimension ref="A1:J833"/>
+  <dimension ref="A1:J837"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="11.36328125" bestFit="1" customWidth="1"/>
@@ -39000,7 +39020,7 @@
     </row>
     <row r="722" spans="1:10">
       <c r="A722" s="24">
-        <f t="shared" ref="A722:A832" si="14">A720+1</f>
+        <f t="shared" ref="A722:A836" si="14">A720+1</f>
         <v>46255</v>
       </c>
       <c r="B722" s="23" t="s">
@@ -41145,7 +41165,7 @@
     </row>
     <row r="787" spans="1:10">
       <c r="A787" s="24">
-        <f t="shared" ref="A787:A833" si="15">A785+1</f>
+        <f t="shared" ref="A787:A837" si="15">A785+1</f>
         <v>46287</v>
       </c>
       <c r="B787" s="23" t="s">
@@ -42692,6 +42712,138 @@
       </c>
       <c r="J833" s="31">
         <v>0.245</v>
+      </c>
+    </row>
+    <row r="834" spans="1:10">
+      <c r="A834" s="24">
+        <f t="shared" si="14"/>
+        <v>46311</v>
+      </c>
+      <c r="B834" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C834" s="25">
+        <v>152029544</v>
+      </c>
+      <c r="D834" s="25">
+        <v>9156395</v>
+      </c>
+      <c r="E834" s="25">
+        <v>2902221</v>
+      </c>
+      <c r="F834" s="25">
+        <v>1692157</v>
+      </c>
+      <c r="G834" s="25">
+        <v>165780317</v>
+      </c>
+      <c r="H834" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I834" s="27">
+        <v>0</v>
+      </c>
+      <c r="J834" s="31">
+        <v>0.245</v>
+      </c>
+    </row>
+    <row r="835" spans="1:10">
+      <c r="A835" s="24">
+        <f t="shared" si="15"/>
+        <v>46311</v>
+      </c>
+      <c r="B835" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C835" s="25">
+        <v>152029544</v>
+      </c>
+      <c r="D835" s="25">
+        <v>9156395</v>
+      </c>
+      <c r="E835" s="25">
+        <v>2902221</v>
+      </c>
+      <c r="F835" s="25">
+        <v>1692157</v>
+      </c>
+      <c r="G835" s="25">
+        <v>165780317</v>
+      </c>
+      <c r="H835" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I835" s="27">
+        <v>0</v>
+      </c>
+      <c r="J835" s="31">
+        <v>0.245</v>
+      </c>
+    </row>
+    <row r="836" spans="1:10">
+      <c r="A836" s="24">
+        <f t="shared" si="14"/>
+        <v>46312</v>
+      </c>
+      <c r="B836" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C836" s="25">
+        <v>163762280</v>
+      </c>
+      <c r="D836" s="25">
+        <v>9156395</v>
+      </c>
+      <c r="E836" s="25">
+        <v>3539204</v>
+      </c>
+      <c r="F836" s="25">
+        <v>1779370</v>
+      </c>
+      <c r="G836" s="25">
+        <v>178257249</v>
+      </c>
+      <c r="H836" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I836" s="27">
+        <v>0</v>
+      </c>
+      <c r="J836" s="31">
+        <v>0.26200000000000001</v>
+      </c>
+    </row>
+    <row r="837" spans="1:10">
+      <c r="A837" s="24">
+        <f t="shared" si="15"/>
+        <v>46312</v>
+      </c>
+      <c r="B837" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C837" s="25">
+        <v>163762280</v>
+      </c>
+      <c r="D837" s="25">
+        <v>9156395</v>
+      </c>
+      <c r="E837" s="25">
+        <v>3539204</v>
+      </c>
+      <c r="F837" s="25">
+        <v>1779370</v>
+      </c>
+      <c r="G837" s="25">
+        <v>178257249</v>
+      </c>
+      <c r="H837" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I837" s="27">
+        <v>0</v>
+      </c>
+      <c r="J837" s="31">
+        <v>0.26200000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/record.xlsx
+++ b/public/data/record.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\cursor-usage\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5595D47E-1429-4951-8C2C-B76ECD7BB9DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EBE154E-F399-4341-A94F-466DC2BB0EF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19110" yWindow="0" windowWidth="19290" windowHeight="20880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cursor Usageの記録" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1228" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1232" uniqueCount="31">
   <si>
     <t>番号</t>
   </si>
@@ -10713,7 +10713,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92559261-86B2-49A9-AE5C-FC3176987B65}">
-  <dimension ref="A1:E231"/>
+  <dimension ref="A1:E232"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="5.453125" bestFit="1" customWidth="1"/>
@@ -12108,7 +12108,7 @@
     </row>
     <row r="74" spans="1:5" s="5" customFormat="1" ht="14.5">
       <c r="A74" s="6">
-        <f t="shared" ref="A74:A231" si="2">ROW()-1</f>
+        <f t="shared" ref="A74:A232" si="2">ROW()-1</f>
         <v>73</v>
       </c>
       <c r="B74" s="7">
@@ -14167,7 +14167,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="7">
-        <f t="shared" ref="B179:B231" si="12">B178+1</f>
+        <f t="shared" ref="B179:B232" si="12">B178+1</f>
         <v>46259</v>
       </c>
       <c r="C179" s="6">
@@ -14271,7 +14271,7 @@
         <v>46264</v>
       </c>
       <c r="C184" s="6">
-        <f t="shared" ref="C184:C231" si="13">C183+1</f>
+        <f t="shared" ref="C184:C232" si="13">C183+1</f>
         <v>8</v>
       </c>
       <c r="D184" s="13">
@@ -15217,6 +15217,26 @@
         <v>6540</v>
       </c>
       <c r="E231" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5" ht="14" customHeight="1">
+      <c r="A232" s="6">
+        <f t="shared" si="2"/>
+        <v>231</v>
+      </c>
+      <c r="B232" s="7">
+        <f t="shared" si="12"/>
+        <v>46312</v>
+      </c>
+      <c r="C232" s="6">
+        <f t="shared" si="13"/>
+        <v>25</v>
+      </c>
+      <c r="D232" s="13">
+        <v>1614</v>
+      </c>
+      <c r="E232" s="13">
         <v>0</v>
       </c>
     </row>
@@ -15229,7 +15249,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E31F5C3B-0571-4A35-9FD2-A50C21726EAB}">
-  <dimension ref="A1:J837"/>
+  <dimension ref="A1:J839"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="11.36328125" bestFit="1" customWidth="1"/>
@@ -39020,7 +39040,7 @@
     </row>
     <row r="722" spans="1:10">
       <c r="A722" s="24">
-        <f t="shared" ref="A722:A836" si="14">A720+1</f>
+        <f t="shared" ref="A722:A838" si="14">A720+1</f>
         <v>46255</v>
       </c>
       <c r="B722" s="23" t="s">
@@ -41165,7 +41185,7 @@
     </row>
     <row r="787" spans="1:10">
       <c r="A787" s="24">
-        <f t="shared" ref="A787:A837" si="15">A785+1</f>
+        <f t="shared" ref="A787:A839" si="15">A785+1</f>
         <v>46287</v>
       </c>
       <c r="B787" s="23" t="s">
@@ -42844,6 +42864,72 @@
       </c>
       <c r="J837" s="31">
         <v>0.26200000000000001</v>
+      </c>
+    </row>
+    <row r="838" spans="1:10">
+      <c r="A838" s="24">
+        <f t="shared" si="14"/>
+        <v>46313</v>
+      </c>
+      <c r="B838" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C838" s="25">
+        <v>173514984</v>
+      </c>
+      <c r="D838" s="25">
+        <v>9156395</v>
+      </c>
+      <c r="E838" s="25">
+        <v>4151337</v>
+      </c>
+      <c r="F838" s="25">
+        <v>1897992</v>
+      </c>
+      <c r="G838" s="25">
+        <v>188720708</v>
+      </c>
+      <c r="H838" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I838" s="27">
+        <v>0</v>
+      </c>
+      <c r="J838" s="31">
+        <v>0.27700000000000002</v>
+      </c>
+    </row>
+    <row r="839" spans="1:10">
+      <c r="A839" s="24">
+        <f t="shared" si="15"/>
+        <v>46313</v>
+      </c>
+      <c r="B839" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C839" s="25">
+        <v>173514984</v>
+      </c>
+      <c r="D839" s="25">
+        <v>9156395</v>
+      </c>
+      <c r="E839" s="25">
+        <v>4151337</v>
+      </c>
+      <c r="F839" s="25">
+        <v>1897992</v>
+      </c>
+      <c r="G839" s="25">
+        <v>188720708</v>
+      </c>
+      <c r="H839" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I839" s="27">
+        <v>0</v>
+      </c>
+      <c r="J839" s="31">
+        <v>0.27700000000000002</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/record.xlsx
+++ b/public/data/record.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\cursor-usage\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EBE154E-F399-4341-A94F-466DC2BB0EF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C0FC889-686B-46D0-90B7-E95D97D89FC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1232" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1236" uniqueCount="31">
   <si>
     <t>番号</t>
   </si>
@@ -10713,7 +10713,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92559261-86B2-49A9-AE5C-FC3176987B65}">
-  <dimension ref="A1:E232"/>
+  <dimension ref="A1:E233"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="5.453125" bestFit="1" customWidth="1"/>
@@ -12108,7 +12108,7 @@
     </row>
     <row r="74" spans="1:5" s="5" customFormat="1" ht="14.5">
       <c r="A74" s="6">
-        <f t="shared" ref="A74:A232" si="2">ROW()-1</f>
+        <f t="shared" ref="A74:A233" si="2">ROW()-1</f>
         <v>73</v>
       </c>
       <c r="B74" s="7">
@@ -14167,7 +14167,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="7">
-        <f t="shared" ref="B179:B232" si="12">B178+1</f>
+        <f t="shared" ref="B179:B233" si="12">B178+1</f>
         <v>46259</v>
       </c>
       <c r="C179" s="6">
@@ -14271,7 +14271,7 @@
         <v>46264</v>
       </c>
       <c r="C184" s="6">
-        <f t="shared" ref="C184:C232" si="13">C183+1</f>
+        <f t="shared" ref="C184:C233" si="13">C183+1</f>
         <v>8</v>
       </c>
       <c r="D184" s="13">
@@ -15237,6 +15237,26 @@
         <v>1614</v>
       </c>
       <c r="E232" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5" ht="14" customHeight="1">
+      <c r="A233" s="6">
+        <f t="shared" si="2"/>
+        <v>232</v>
+      </c>
+      <c r="B233" s="7">
+        <f t="shared" si="12"/>
+        <v>46313</v>
+      </c>
+      <c r="C233" s="6">
+        <f t="shared" si="13"/>
+        <v>26</v>
+      </c>
+      <c r="D233" s="13">
+        <v>2382</v>
+      </c>
+      <c r="E233" s="13">
         <v>0</v>
       </c>
     </row>
@@ -15249,7 +15269,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E31F5C3B-0571-4A35-9FD2-A50C21726EAB}">
-  <dimension ref="A1:J839"/>
+  <dimension ref="A1:J841"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="11.36328125" bestFit="1" customWidth="1"/>
@@ -39040,7 +39060,7 @@
     </row>
     <row r="722" spans="1:10">
       <c r="A722" s="24">
-        <f t="shared" ref="A722:A838" si="14">A720+1</f>
+        <f t="shared" ref="A722:A840" si="14">A720+1</f>
         <v>46255</v>
       </c>
       <c r="B722" s="23" t="s">
@@ -41185,7 +41205,7 @@
     </row>
     <row r="787" spans="1:10">
       <c r="A787" s="24">
-        <f t="shared" ref="A787:A839" si="15">A785+1</f>
+        <f t="shared" ref="A787:A841" si="15">A785+1</f>
         <v>46287</v>
       </c>
       <c r="B787" s="23" t="s">
@@ -42930,6 +42950,72 @@
       </c>
       <c r="J839" s="31">
         <v>0.27700000000000002</v>
+      </c>
+    </row>
+    <row r="840" spans="1:10">
+      <c r="A840" s="24">
+        <f t="shared" si="14"/>
+        <v>46314</v>
+      </c>
+      <c r="B840" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C840" s="25">
+        <v>183452392</v>
+      </c>
+      <c r="D840" s="25">
+        <v>9156395</v>
+      </c>
+      <c r="E840" s="25">
+        <v>5097675</v>
+      </c>
+      <c r="F840" s="25">
+        <v>2023847</v>
+      </c>
+      <c r="G840" s="25">
+        <v>199730309</v>
+      </c>
+      <c r="H840" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I840" s="27">
+        <v>0</v>
+      </c>
+      <c r="J840" s="31">
+        <v>0.29399999999999998</v>
+      </c>
+    </row>
+    <row r="841" spans="1:10">
+      <c r="A841" s="24">
+        <f t="shared" si="15"/>
+        <v>46314</v>
+      </c>
+      <c r="B841" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C841" s="25">
+        <v>183452392</v>
+      </c>
+      <c r="D841" s="25">
+        <v>9156395</v>
+      </c>
+      <c r="E841" s="25">
+        <v>5097675</v>
+      </c>
+      <c r="F841" s="25">
+        <v>2023847</v>
+      </c>
+      <c r="G841" s="25">
+        <v>199730309</v>
+      </c>
+      <c r="H841" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I841" s="27">
+        <v>0</v>
+      </c>
+      <c r="J841" s="31">
+        <v>0.29399999999999998</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/record.xlsx
+++ b/public/data/record.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\cursor-usage\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C0FC889-686B-46D0-90B7-E95D97D89FC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{440585C8-DAA4-4DB5-8B22-4E9D8C054635}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1236" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1240" uniqueCount="31">
   <si>
     <t>番号</t>
   </si>
@@ -10713,7 +10713,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92559261-86B2-49A9-AE5C-FC3176987B65}">
-  <dimension ref="A1:E233"/>
+  <dimension ref="A1:E234"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="5.453125" bestFit="1" customWidth="1"/>
@@ -12108,7 +12108,7 @@
     </row>
     <row r="74" spans="1:5" s="5" customFormat="1" ht="14.5">
       <c r="A74" s="6">
-        <f t="shared" ref="A74:A233" si="2">ROW()-1</f>
+        <f t="shared" ref="A74:A234" si="2">ROW()-1</f>
         <v>73</v>
       </c>
       <c r="B74" s="7">
@@ -14167,7 +14167,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="7">
-        <f t="shared" ref="B179:B233" si="12">B178+1</f>
+        <f t="shared" ref="B179:B234" si="12">B178+1</f>
         <v>46259</v>
       </c>
       <c r="C179" s="6">
@@ -14271,7 +14271,7 @@
         <v>46264</v>
       </c>
       <c r="C184" s="6">
-        <f t="shared" ref="C184:C233" si="13">C183+1</f>
+        <f t="shared" ref="C184:C234" si="13">C183+1</f>
         <v>8</v>
       </c>
       <c r="D184" s="13">
@@ -15257,6 +15257,26 @@
         <v>2382</v>
       </c>
       <c r="E233" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5" ht="14" customHeight="1">
+      <c r="A234" s="6">
+        <f t="shared" si="2"/>
+        <v>233</v>
+      </c>
+      <c r="B234" s="7">
+        <f t="shared" si="12"/>
+        <v>46314</v>
+      </c>
+      <c r="C234" s="6">
+        <f t="shared" si="13"/>
+        <v>27</v>
+      </c>
+      <c r="D234" s="13">
+        <v>2699</v>
+      </c>
+      <c r="E234" s="13">
         <v>0</v>
       </c>
     </row>
@@ -15269,7 +15289,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E31F5C3B-0571-4A35-9FD2-A50C21726EAB}">
-  <dimension ref="A1:J841"/>
+  <dimension ref="A1:J843"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="11.36328125" bestFit="1" customWidth="1"/>
@@ -39060,7 +39080,7 @@
     </row>
     <row r="722" spans="1:10">
       <c r="A722" s="24">
-        <f t="shared" ref="A722:A840" si="14">A720+1</f>
+        <f t="shared" ref="A722:A842" si="14">A720+1</f>
         <v>46255</v>
       </c>
       <c r="B722" s="23" t="s">
@@ -41205,7 +41225,7 @@
     </row>
     <row r="787" spans="1:10">
       <c r="A787" s="24">
-        <f t="shared" ref="A787:A841" si="15">A785+1</f>
+        <f t="shared" ref="A787:A843" si="15">A785+1</f>
         <v>46287</v>
       </c>
       <c r="B787" s="23" t="s">
@@ -43016,6 +43036,72 @@
       </c>
       <c r="J841" s="31">
         <v>0.29399999999999998</v>
+      </c>
+    </row>
+    <row r="842" spans="1:10">
+      <c r="A842" s="24">
+        <f t="shared" si="14"/>
+        <v>46315</v>
+      </c>
+      <c r="B842" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C842" s="25">
+        <v>195225320</v>
+      </c>
+      <c r="D842" s="25">
+        <v>9156395</v>
+      </c>
+      <c r="E842" s="25">
+        <v>6149598</v>
+      </c>
+      <c r="F842" s="25">
+        <v>2148869</v>
+      </c>
+      <c r="G842" s="25">
+        <v>212680182</v>
+      </c>
+      <c r="H842" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I842" s="27">
+        <v>0</v>
+      </c>
+      <c r="J842" s="31">
+        <v>0.314</v>
+      </c>
+    </row>
+    <row r="843" spans="1:10">
+      <c r="A843" s="24">
+        <f t="shared" si="15"/>
+        <v>46315</v>
+      </c>
+      <c r="B843" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C843" s="25">
+        <v>195225320</v>
+      </c>
+      <c r="D843" s="25">
+        <v>9156395</v>
+      </c>
+      <c r="E843" s="25">
+        <v>6149598</v>
+      </c>
+      <c r="F843" s="25">
+        <v>2148869</v>
+      </c>
+      <c r="G843" s="25">
+        <v>212680182</v>
+      </c>
+      <c r="H843" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I843" s="27">
+        <v>0</v>
+      </c>
+      <c r="J843" s="31">
+        <v>0.314</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/record.xlsx
+++ b/public/data/record.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\cursor-usage\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{440585C8-DAA4-4DB5-8B22-4E9D8C054635}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25363C84-DC0F-491A-AEB7-E5371FFDE7A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1240" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1244" uniqueCount="31">
   <si>
     <t>番号</t>
   </si>
@@ -10713,7 +10713,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92559261-86B2-49A9-AE5C-FC3176987B65}">
-  <dimension ref="A1:E234"/>
+  <dimension ref="A1:E235"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="5.453125" bestFit="1" customWidth="1"/>
@@ -12108,7 +12108,7 @@
     </row>
     <row r="74" spans="1:5" s="5" customFormat="1" ht="14.5">
       <c r="A74" s="6">
-        <f t="shared" ref="A74:A234" si="2">ROW()-1</f>
+        <f t="shared" ref="A74:A235" si="2">ROW()-1</f>
         <v>73</v>
       </c>
       <c r="B74" s="7">
@@ -14167,7 +14167,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="7">
-        <f t="shared" ref="B179:B234" si="12">B178+1</f>
+        <f t="shared" ref="B179:B235" si="12">B178+1</f>
         <v>46259</v>
       </c>
       <c r="C179" s="6">
@@ -14271,7 +14271,7 @@
         <v>46264</v>
       </c>
       <c r="C184" s="6">
-        <f t="shared" ref="C184:C234" si="13">C183+1</f>
+        <f t="shared" ref="C184:C235" si="13">C183+1</f>
         <v>8</v>
       </c>
       <c r="D184" s="13">
@@ -15279,6 +15279,24 @@
       <c r="E234" s="13">
         <v>0</v>
       </c>
+    </row>
+    <row r="235" spans="1:5" ht="14" customHeight="1">
+      <c r="A235" s="6">
+        <f t="shared" si="2"/>
+        <v>234</v>
+      </c>
+      <c r="B235" s="7">
+        <f t="shared" si="12"/>
+        <v>46315</v>
+      </c>
+      <c r="C235" s="6">
+        <f t="shared" si="13"/>
+        <v>28</v>
+      </c>
+      <c r="D235" s="13">
+        <v>8613</v>
+      </c>
+      <c r="E235" s="13"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4"/>
@@ -15289,7 +15307,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E31F5C3B-0571-4A35-9FD2-A50C21726EAB}">
-  <dimension ref="A1:J843"/>
+  <dimension ref="A1:J845"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="11.36328125" bestFit="1" customWidth="1"/>
@@ -39080,7 +39098,7 @@
     </row>
     <row r="722" spans="1:10">
       <c r="A722" s="24">
-        <f t="shared" ref="A722:A842" si="14">A720+1</f>
+        <f t="shared" ref="A722:A844" si="14">A720+1</f>
         <v>46255</v>
       </c>
       <c r="B722" s="23" t="s">
@@ -41225,7 +41243,7 @@
     </row>
     <row r="787" spans="1:10">
       <c r="A787" s="24">
-        <f t="shared" ref="A787:A843" si="15">A785+1</f>
+        <f t="shared" ref="A787:A845" si="15">A785+1</f>
         <v>46287</v>
       </c>
       <c r="B787" s="23" t="s">
@@ -43102,6 +43120,72 @@
       </c>
       <c r="J843" s="31">
         <v>0.314</v>
+      </c>
+    </row>
+    <row r="844" spans="1:10">
+      <c r="A844" s="24">
+        <f t="shared" si="14"/>
+        <v>46316</v>
+      </c>
+      <c r="B844" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C844" s="25">
+        <v>216363368</v>
+      </c>
+      <c r="D844" s="25">
+        <v>9156395</v>
+      </c>
+      <c r="E844" s="25">
+        <v>7828642</v>
+      </c>
+      <c r="F844" s="25">
+        <v>2415312</v>
+      </c>
+      <c r="G844" s="25">
+        <v>235763717</v>
+      </c>
+      <c r="H844" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I844" s="27">
+        <v>0</v>
+      </c>
+      <c r="J844" s="31">
+        <v>0.34799999999999998</v>
+      </c>
+    </row>
+    <row r="845" spans="1:10">
+      <c r="A845" s="24">
+        <f t="shared" si="15"/>
+        <v>46316</v>
+      </c>
+      <c r="B845" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C845" s="25">
+        <v>216363368</v>
+      </c>
+      <c r="D845" s="25">
+        <v>9156395</v>
+      </c>
+      <c r="E845" s="25">
+        <v>7828642</v>
+      </c>
+      <c r="F845" s="25">
+        <v>2415312</v>
+      </c>
+      <c r="G845" s="25">
+        <v>235763717</v>
+      </c>
+      <c r="H845" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I845" s="27">
+        <v>0</v>
+      </c>
+      <c r="J845" s="31">
+        <v>0.34799999999999998</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/record.xlsx
+++ b/public/data/record.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\cursor-usage\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25363C84-DC0F-491A-AEB7-E5371FFDE7A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1735D4E2-6C98-4D2B-9DE7-1EDEC9CDC412}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1244" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1248" uniqueCount="31">
   <si>
     <t>番号</t>
   </si>
@@ -10713,7 +10713,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92559261-86B2-49A9-AE5C-FC3176987B65}">
-  <dimension ref="A1:E235"/>
+  <dimension ref="A1:E236"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="5.453125" bestFit="1" customWidth="1"/>
@@ -12108,7 +12108,7 @@
     </row>
     <row r="74" spans="1:5" s="5" customFormat="1" ht="14.5">
       <c r="A74" s="6">
-        <f t="shared" ref="A74:A235" si="2">ROW()-1</f>
+        <f t="shared" ref="A74:A236" si="2">ROW()-1</f>
         <v>73</v>
       </c>
       <c r="B74" s="7">
@@ -14167,7 +14167,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="7">
-        <f t="shared" ref="B179:B235" si="12">B178+1</f>
+        <f t="shared" ref="B179:B236" si="12">B178+1</f>
         <v>46259</v>
       </c>
       <c r="C179" s="6">
@@ -14271,7 +14271,7 @@
         <v>46264</v>
       </c>
       <c r="C184" s="6">
-        <f t="shared" ref="C184:C235" si="13">C183+1</f>
+        <f t="shared" ref="C184:C236" si="13">C183+1</f>
         <v>8</v>
       </c>
       <c r="D184" s="13">
@@ -15296,7 +15296,29 @@
       <c r="D235" s="13">
         <v>8613</v>
       </c>
-      <c r="E235" s="13"/>
+      <c r="E235" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5" ht="14" customHeight="1">
+      <c r="A236" s="6">
+        <f t="shared" si="2"/>
+        <v>235</v>
+      </c>
+      <c r="B236" s="7">
+        <f t="shared" si="12"/>
+        <v>46316</v>
+      </c>
+      <c r="C236" s="6">
+        <f t="shared" si="13"/>
+        <v>29</v>
+      </c>
+      <c r="D236" s="13">
+        <v>1268</v>
+      </c>
+      <c r="E236" s="13">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="4"/>
@@ -15307,7 +15329,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E31F5C3B-0571-4A35-9FD2-A50C21726EAB}">
-  <dimension ref="A1:J845"/>
+  <dimension ref="A1:J847"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="11.36328125" bestFit="1" customWidth="1"/>
@@ -39098,7 +39120,7 @@
     </row>
     <row r="722" spans="1:10">
       <c r="A722" s="24">
-        <f t="shared" ref="A722:A844" si="14">A720+1</f>
+        <f t="shared" ref="A722:A846" si="14">A720+1</f>
         <v>46255</v>
       </c>
       <c r="B722" s="23" t="s">
@@ -41243,7 +41265,7 @@
     </row>
     <row r="787" spans="1:10">
       <c r="A787" s="24">
-        <f t="shared" ref="A787:A845" si="15">A785+1</f>
+        <f t="shared" ref="A787:A847" si="15">A785+1</f>
         <v>46287</v>
       </c>
       <c r="B787" s="23" t="s">
@@ -43186,6 +43208,72 @@
       </c>
       <c r="J845" s="31">
         <v>0.34799999999999998</v>
+      </c>
+    </row>
+    <row r="846" spans="1:10">
+      <c r="A846" s="24">
+        <f t="shared" si="14"/>
+        <v>46317</v>
+      </c>
+      <c r="B846" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C846" s="25">
+        <v>224737128</v>
+      </c>
+      <c r="D846" s="25">
+        <v>9156395</v>
+      </c>
+      <c r="E846" s="25">
+        <v>8711343</v>
+      </c>
+      <c r="F846" s="25">
+        <v>2558264</v>
+      </c>
+      <c r="G846" s="25">
+        <v>245163130</v>
+      </c>
+      <c r="H846" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I846" s="27">
+        <v>0</v>
+      </c>
+      <c r="J846" s="31">
+        <v>0.36299999999999999</v>
+      </c>
+    </row>
+    <row r="847" spans="1:10">
+      <c r="A847" s="24">
+        <f t="shared" si="15"/>
+        <v>46317</v>
+      </c>
+      <c r="B847" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C847" s="25">
+        <v>224737128</v>
+      </c>
+      <c r="D847" s="25">
+        <v>9156395</v>
+      </c>
+      <c r="E847" s="25">
+        <v>8711343</v>
+      </c>
+      <c r="F847" s="25">
+        <v>2558264</v>
+      </c>
+      <c r="G847" s="25">
+        <v>245163130</v>
+      </c>
+      <c r="H847" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I847" s="27">
+        <v>0</v>
+      </c>
+      <c r="J847" s="31">
+        <v>0.36299999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/record.xlsx
+++ b/public/data/record.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\cursor-usage\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1735D4E2-6C98-4D2B-9DE7-1EDEC9CDC412}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42AD01F2-2EFB-43FB-AF9A-001473D3F251}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1248" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1252" uniqueCount="31">
   <si>
     <t>番号</t>
   </si>
@@ -10713,7 +10713,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92559261-86B2-49A9-AE5C-FC3176987B65}">
-  <dimension ref="A1:E236"/>
+  <dimension ref="A1:E237"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="5.453125" bestFit="1" customWidth="1"/>
@@ -12108,7 +12108,7 @@
     </row>
     <row r="74" spans="1:5" s="5" customFormat="1" ht="14.5">
       <c r="A74" s="6">
-        <f t="shared" ref="A74:A236" si="2">ROW()-1</f>
+        <f t="shared" ref="A74:A237" si="2">ROW()-1</f>
         <v>73</v>
       </c>
       <c r="B74" s="7">
@@ -14167,7 +14167,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="7">
-        <f t="shared" ref="B179:B236" si="12">B178+1</f>
+        <f t="shared" ref="B179:B237" si="12">B178+1</f>
         <v>46259</v>
       </c>
       <c r="C179" s="6">
@@ -14271,7 +14271,7 @@
         <v>46264</v>
       </c>
       <c r="C184" s="6">
-        <f t="shared" ref="C184:C236" si="13">C183+1</f>
+        <f t="shared" ref="C184:C237" si="13">C183+1</f>
         <v>8</v>
       </c>
       <c r="D184" s="13">
@@ -15317,6 +15317,26 @@
         <v>1268</v>
       </c>
       <c r="E236" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5" ht="14" customHeight="1">
+      <c r="A237" s="6">
+        <f t="shared" si="2"/>
+        <v>236</v>
+      </c>
+      <c r="B237" s="7">
+        <f t="shared" si="12"/>
+        <v>46317</v>
+      </c>
+      <c r="C237" s="6">
+        <f t="shared" si="13"/>
+        <v>30</v>
+      </c>
+      <c r="D237" s="13">
+        <v>1397</v>
+      </c>
+      <c r="E237" s="13">
         <v>0</v>
       </c>
     </row>
@@ -15329,7 +15349,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E31F5C3B-0571-4A35-9FD2-A50C21726EAB}">
-  <dimension ref="A1:J847"/>
+  <dimension ref="A1:J849"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="11.36328125" bestFit="1" customWidth="1"/>
@@ -39120,7 +39140,7 @@
     </row>
     <row r="722" spans="1:10">
       <c r="A722" s="24">
-        <f t="shared" ref="A722:A846" si="14">A720+1</f>
+        <f t="shared" ref="A722:A848" si="14">A720+1</f>
         <v>46255</v>
       </c>
       <c r="B722" s="23" t="s">
@@ -41265,7 +41285,7 @@
     </row>
     <row r="787" spans="1:10">
       <c r="A787" s="24">
-        <f t="shared" ref="A787:A847" si="15">A785+1</f>
+        <f t="shared" ref="A787:A849" si="15">A785+1</f>
         <v>46287</v>
       </c>
       <c r="B787" s="23" t="s">
@@ -43274,6 +43294,72 @@
       </c>
       <c r="J847" s="31">
         <v>0.36299999999999999</v>
+      </c>
+    </row>
+    <row r="848" spans="1:10">
+      <c r="A848" s="24">
+        <f t="shared" si="14"/>
+        <v>46318</v>
+      </c>
+      <c r="B848" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C848" s="25">
+        <v>238535144</v>
+      </c>
+      <c r="D848" s="25">
+        <v>9156395</v>
+      </c>
+      <c r="E848" s="25">
+        <v>9501451</v>
+      </c>
+      <c r="F848" s="25">
+        <v>2701354</v>
+      </c>
+      <c r="G848" s="25">
+        <v>259894344</v>
+      </c>
+      <c r="H848" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I848" s="27">
+        <v>0</v>
+      </c>
+      <c r="J848" s="31">
+        <v>0.38400000000000001</v>
+      </c>
+    </row>
+    <row r="849" spans="1:10">
+      <c r="A849" s="24">
+        <f t="shared" si="15"/>
+        <v>46318</v>
+      </c>
+      <c r="B849" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C849" s="25">
+        <v>238535144</v>
+      </c>
+      <c r="D849" s="25">
+        <v>9156395</v>
+      </c>
+      <c r="E849" s="25">
+        <v>9501451</v>
+      </c>
+      <c r="F849" s="25">
+        <v>2701354</v>
+      </c>
+      <c r="G849" s="25">
+        <v>259894344</v>
+      </c>
+      <c r="H849" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I849" s="27">
+        <v>0</v>
+      </c>
+      <c r="J849" s="31">
+        <v>0.38400000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/record.xlsx
+++ b/public/data/record.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\cursor-usage\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42AD01F2-2EFB-43FB-AF9A-001473D3F251}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CCE15C8-C341-4FBA-AB68-E90CD099BAA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1252" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1260" uniqueCount="31">
   <si>
     <t>番号</t>
   </si>
@@ -10713,7 +10713,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92559261-86B2-49A9-AE5C-FC3176987B65}">
-  <dimension ref="A1:E237"/>
+  <dimension ref="A1:E239"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="5.453125" bestFit="1" customWidth="1"/>
@@ -12108,7 +12108,7 @@
     </row>
     <row r="74" spans="1:5" s="5" customFormat="1" ht="14.5">
       <c r="A74" s="6">
-        <f t="shared" ref="A74:A237" si="2">ROW()-1</f>
+        <f t="shared" ref="A74:A239" si="2">ROW()-1</f>
         <v>73</v>
       </c>
       <c r="B74" s="7">
@@ -14167,7 +14167,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="7">
-        <f t="shared" ref="B179:B237" si="12">B178+1</f>
+        <f t="shared" ref="B179:B239" si="12">B178+1</f>
         <v>46259</v>
       </c>
       <c r="C179" s="6">
@@ -15338,6 +15338,44 @@
       </c>
       <c r="E237" s="13">
         <v>0</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5" ht="14" customHeight="1">
+      <c r="A238" s="6">
+        <f t="shared" si="2"/>
+        <v>237</v>
+      </c>
+      <c r="B238" s="7">
+        <f t="shared" si="12"/>
+        <v>46318</v>
+      </c>
+      <c r="C238" s="6">
+        <v>1</v>
+      </c>
+      <c r="D238" s="13">
+        <v>1782</v>
+      </c>
+      <c r="E238" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5" ht="14" customHeight="1">
+      <c r="A239" s="6">
+        <f t="shared" si="2"/>
+        <v>238</v>
+      </c>
+      <c r="B239" s="7">
+        <f t="shared" si="12"/>
+        <v>46319</v>
+      </c>
+      <c r="C239" s="6">
+        <v>1</v>
+      </c>
+      <c r="D239" s="13">
+        <v>515</v>
+      </c>
+      <c r="E239" s="13">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -15349,7 +15387,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E31F5C3B-0571-4A35-9FD2-A50C21726EAB}">
-  <dimension ref="A1:J849"/>
+  <dimension ref="A1:J853"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="11.36328125" bestFit="1" customWidth="1"/>
@@ -39140,7 +39178,7 @@
     </row>
     <row r="722" spans="1:10">
       <c r="A722" s="24">
-        <f t="shared" ref="A722:A848" si="14">A720+1</f>
+        <f t="shared" ref="A722:A852" si="14">A720+1</f>
         <v>46255</v>
       </c>
       <c r="B722" s="23" t="s">
@@ -41285,7 +41323,7 @@
     </row>
     <row r="787" spans="1:10">
       <c r="A787" s="24">
-        <f t="shared" ref="A787:A849" si="15">A785+1</f>
+        <f t="shared" ref="A787:A853" si="15">A785+1</f>
         <v>46287</v>
       </c>
       <c r="B787" s="23" t="s">
@@ -43360,6 +43398,138 @@
       </c>
       <c r="J849" s="31">
         <v>0.38400000000000001</v>
+      </c>
+    </row>
+    <row r="850" spans="1:10">
+      <c r="A850" s="24">
+        <f t="shared" si="14"/>
+        <v>46319</v>
+      </c>
+      <c r="B850" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C850" s="25">
+        <v>253911528</v>
+      </c>
+      <c r="D850" s="25">
+        <v>9156395</v>
+      </c>
+      <c r="E850" s="25">
+        <v>10452393</v>
+      </c>
+      <c r="F850" s="25">
+        <v>2884773</v>
+      </c>
+      <c r="G850" s="25">
+        <v>276405089</v>
+      </c>
+      <c r="H850" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I850" s="27">
+        <v>0</v>
+      </c>
+      <c r="J850" s="31">
+        <v>0.41299999999999998</v>
+      </c>
+    </row>
+    <row r="851" spans="1:10">
+      <c r="A851" s="24">
+        <f t="shared" si="15"/>
+        <v>46319</v>
+      </c>
+      <c r="B851" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C851" s="25">
+        <v>253911528</v>
+      </c>
+      <c r="D851" s="25">
+        <v>9156395</v>
+      </c>
+      <c r="E851" s="25">
+        <v>10452393</v>
+      </c>
+      <c r="F851" s="25">
+        <v>2884773</v>
+      </c>
+      <c r="G851" s="25">
+        <v>276405089</v>
+      </c>
+      <c r="H851" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I851" s="27">
+        <v>0</v>
+      </c>
+      <c r="J851" s="31">
+        <v>0.41299999999999998</v>
+      </c>
+    </row>
+    <row r="852" spans="1:10">
+      <c r="A852" s="24">
+        <f t="shared" si="14"/>
+        <v>46320</v>
+      </c>
+      <c r="B852" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C852" s="25">
+        <v>6063872</v>
+      </c>
+      <c r="D852" s="25">
+        <v>0</v>
+      </c>
+      <c r="E852" s="25">
+        <v>559927</v>
+      </c>
+      <c r="F852" s="25">
+        <v>82924</v>
+      </c>
+      <c r="G852" s="25">
+        <v>6706723</v>
+      </c>
+      <c r="H852" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I852" s="27">
+        <v>0</v>
+      </c>
+      <c r="J852" s="31">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="853" spans="1:10">
+      <c r="A853" s="24">
+        <f t="shared" si="15"/>
+        <v>46320</v>
+      </c>
+      <c r="B853" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C853" s="25">
+        <v>6063872</v>
+      </c>
+      <c r="D853" s="25">
+        <v>0</v>
+      </c>
+      <c r="E853" s="25">
+        <v>559927</v>
+      </c>
+      <c r="F853" s="25">
+        <v>82924</v>
+      </c>
+      <c r="G853" s="25">
+        <v>6706723</v>
+      </c>
+      <c r="H853" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I853" s="27">
+        <v>0</v>
+      </c>
+      <c r="J853" s="31">
+        <v>0.01</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/record.xlsx
+++ b/public/data/record.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\cursor-usage\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CCE15C8-C341-4FBA-AB68-E90CD099BAA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D29C2A75-6A25-4F22-A227-4F42089B674D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1260" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1264" uniqueCount="31">
   <si>
     <t>番号</t>
   </si>
@@ -10713,7 +10713,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92559261-86B2-49A9-AE5C-FC3176987B65}">
-  <dimension ref="A1:E239"/>
+  <dimension ref="A1:E240"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="5.453125" bestFit="1" customWidth="1"/>
@@ -12108,7 +12108,7 @@
     </row>
     <row r="74" spans="1:5" s="5" customFormat="1" ht="14.5">
       <c r="A74" s="6">
-        <f t="shared" ref="A74:A239" si="2">ROW()-1</f>
+        <f t="shared" ref="A74:A240" si="2">ROW()-1</f>
         <v>73</v>
       </c>
       <c r="B74" s="7">
@@ -14167,7 +14167,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="7">
-        <f t="shared" ref="B179:B239" si="12">B178+1</f>
+        <f t="shared" ref="B179:B240" si="12">B178+1</f>
         <v>46259</v>
       </c>
       <c r="C179" s="6">
@@ -15369,13 +15369,34 @@
         <v>46319</v>
       </c>
       <c r="C239" s="6">
-        <v>1</v>
+        <f>C238+1</f>
+        <v>2</v>
       </c>
       <c r="D239" s="13">
         <v>515</v>
       </c>
       <c r="E239" s="13">
         <v>1</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5" ht="14" customHeight="1">
+      <c r="A240" s="6">
+        <f t="shared" si="2"/>
+        <v>239</v>
+      </c>
+      <c r="B240" s="7">
+        <f t="shared" si="12"/>
+        <v>46320</v>
+      </c>
+      <c r="C240" s="6">
+        <f>C239+1</f>
+        <v>3</v>
+      </c>
+      <c r="D240" s="13">
+        <v>2586</v>
+      </c>
+      <c r="E240" s="13">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -15387,7 +15408,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E31F5C3B-0571-4A35-9FD2-A50C21726EAB}">
-  <dimension ref="A1:J853"/>
+  <dimension ref="A1:J855"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="11.36328125" bestFit="1" customWidth="1"/>
@@ -39178,7 +39199,7 @@
     </row>
     <row r="722" spans="1:10">
       <c r="A722" s="24">
-        <f t="shared" ref="A722:A852" si="14">A720+1</f>
+        <f t="shared" ref="A722:A854" si="14">A720+1</f>
         <v>46255</v>
       </c>
       <c r="B722" s="23" t="s">
@@ -41323,7 +41344,7 @@
     </row>
     <row r="787" spans="1:10">
       <c r="A787" s="24">
-        <f t="shared" ref="A787:A853" si="15">A785+1</f>
+        <f t="shared" ref="A787:A855" si="15">A785+1</f>
         <v>46287</v>
       </c>
       <c r="B787" s="23" t="s">
@@ -43530,6 +43551,72 @@
       </c>
       <c r="J853" s="31">
         <v>0.01</v>
+      </c>
+    </row>
+    <row r="854" spans="1:10">
+      <c r="A854" s="24">
+        <f t="shared" si="14"/>
+        <v>46321</v>
+      </c>
+      <c r="B854" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C854" s="25">
+        <v>23565824</v>
+      </c>
+      <c r="D854" s="25">
+        <v>0</v>
+      </c>
+      <c r="E854" s="25">
+        <v>1239901</v>
+      </c>
+      <c r="F854" s="25">
+        <v>243345</v>
+      </c>
+      <c r="G854" s="25">
+        <v>25049070</v>
+      </c>
+      <c r="H854" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I854" s="27">
+        <v>0</v>
+      </c>
+      <c r="J854" s="31">
+        <v>3.5000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="855" spans="1:10">
+      <c r="A855" s="24">
+        <f t="shared" si="15"/>
+        <v>46321</v>
+      </c>
+      <c r="B855" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C855" s="25">
+        <v>23565824</v>
+      </c>
+      <c r="D855" s="25">
+        <v>0</v>
+      </c>
+      <c r="E855" s="25">
+        <v>1239901</v>
+      </c>
+      <c r="F855" s="25">
+        <v>243345</v>
+      </c>
+      <c r="G855" s="25">
+        <v>25049070</v>
+      </c>
+      <c r="H855" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I855" s="27">
+        <v>0</v>
+      </c>
+      <c r="J855" s="31">
+        <v>3.5000000000000003E-2</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/record.xlsx
+++ b/public/data/record.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\cursor-usage\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D29C2A75-6A25-4F22-A227-4F42089B674D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C703E91E-5B37-41E8-A14F-7D0315781439}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1264" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1268" uniqueCount="31">
   <si>
     <t>番号</t>
   </si>
@@ -10713,7 +10713,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92559261-86B2-49A9-AE5C-FC3176987B65}">
-  <dimension ref="A1:E240"/>
+  <dimension ref="A1:E242"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="5.453125" bestFit="1" customWidth="1"/>
@@ -12108,7 +12108,7 @@
     </row>
     <row r="74" spans="1:5" s="5" customFormat="1" ht="14.5">
       <c r="A74" s="6">
-        <f t="shared" ref="A74:A240" si="2">ROW()-1</f>
+        <f t="shared" ref="A74:A242" si="2">ROW()-1</f>
         <v>73</v>
       </c>
       <c r="B74" s="7">
@@ -14167,7 +14167,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="7">
-        <f t="shared" ref="B179:B240" si="12">B178+1</f>
+        <f t="shared" ref="B179:B242" si="12">B178+1</f>
         <v>46259</v>
       </c>
       <c r="C179" s="6">
@@ -15396,6 +15396,46 @@
         <v>2586</v>
       </c>
       <c r="E240" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5" ht="14" customHeight="1">
+      <c r="A241" s="6">
+        <f t="shared" si="2"/>
+        <v>240</v>
+      </c>
+      <c r="B241" s="7">
+        <f t="shared" si="12"/>
+        <v>46321</v>
+      </c>
+      <c r="C241" s="6">
+        <f>C240+1</f>
+        <v>4</v>
+      </c>
+      <c r="D241" s="13">
+        <v>59</v>
+      </c>
+      <c r="E241" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5" ht="14" customHeight="1">
+      <c r="A242" s="6">
+        <f t="shared" si="2"/>
+        <v>241</v>
+      </c>
+      <c r="B242" s="7">
+        <f t="shared" si="12"/>
+        <v>46322</v>
+      </c>
+      <c r="C242" s="6">
+        <f>C241+1</f>
+        <v>5</v>
+      </c>
+      <c r="D242" s="13">
+        <v>0</v>
+      </c>
+      <c r="E242" s="13">
         <v>0</v>
       </c>
     </row>
@@ -15408,7 +15448,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E31F5C3B-0571-4A35-9FD2-A50C21726EAB}">
-  <dimension ref="A1:J855"/>
+  <dimension ref="A1:J857"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="11.36328125" bestFit="1" customWidth="1"/>
@@ -39199,7 +39239,7 @@
     </row>
     <row r="722" spans="1:10">
       <c r="A722" s="24">
-        <f t="shared" ref="A722:A854" si="14">A720+1</f>
+        <f t="shared" ref="A722:A856" si="14">A720+1</f>
         <v>46255</v>
       </c>
       <c r="B722" s="23" t="s">
@@ -41344,7 +41384,7 @@
     </row>
     <row r="787" spans="1:10">
       <c r="A787" s="24">
-        <f t="shared" ref="A787:A855" si="15">A785+1</f>
+        <f t="shared" ref="A787:A857" si="15">A785+1</f>
         <v>46287</v>
       </c>
       <c r="B787" s="23" t="s">
@@ -43617,6 +43657,72 @@
       </c>
       <c r="J855" s="31">
         <v>3.5000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="856" spans="1:10">
+      <c r="A856" s="24">
+        <f t="shared" si="14"/>
+        <v>46322</v>
+      </c>
+      <c r="B856" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C856" s="25">
+        <v>26224000</v>
+      </c>
+      <c r="D856" s="25">
+        <v>0</v>
+      </c>
+      <c r="E856" s="25">
+        <v>1680208</v>
+      </c>
+      <c r="F856" s="25">
+        <v>310884</v>
+      </c>
+      <c r="G856" s="25">
+        <v>28215092</v>
+      </c>
+      <c r="H856" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I856" s="27">
+        <v>0</v>
+      </c>
+      <c r="J856" s="31">
+        <v>4.1000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="857" spans="1:10">
+      <c r="A857" s="24">
+        <f t="shared" si="15"/>
+        <v>46322</v>
+      </c>
+      <c r="B857" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C857" s="25">
+        <v>26224000</v>
+      </c>
+      <c r="D857" s="25">
+        <v>0</v>
+      </c>
+      <c r="E857" s="25">
+        <v>1680208</v>
+      </c>
+      <c r="F857" s="25">
+        <v>310884</v>
+      </c>
+      <c r="G857" s="25">
+        <v>28215092</v>
+      </c>
+      <c r="H857" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I857" s="27">
+        <v>0</v>
+      </c>
+      <c r="J857" s="31">
+        <v>4.1000000000000002E-2</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/record.xlsx
+++ b/public/data/record.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\cursor-usage\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C703E91E-5B37-41E8-A14F-7D0315781439}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{295B4B81-CC7F-459E-8A6C-F1BB43C5BA19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1268" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1272" uniqueCount="31">
   <si>
     <t>番号</t>
   </si>
@@ -10713,7 +10713,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92559261-86B2-49A9-AE5C-FC3176987B65}">
-  <dimension ref="A1:E242"/>
+  <dimension ref="A1:E243"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="5.453125" bestFit="1" customWidth="1"/>
@@ -12108,7 +12108,7 @@
     </row>
     <row r="74" spans="1:5" s="5" customFormat="1" ht="14.5">
       <c r="A74" s="6">
-        <f t="shared" ref="A74:A242" si="2">ROW()-1</f>
+        <f t="shared" ref="A74:A243" si="2">ROW()-1</f>
         <v>73</v>
       </c>
       <c r="B74" s="7">
@@ -14167,7 +14167,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="7">
-        <f t="shared" ref="B179:B242" si="12">B178+1</f>
+        <f t="shared" ref="B179:B243" si="12">B178+1</f>
         <v>46259</v>
       </c>
       <c r="C179" s="6">
@@ -15436,6 +15436,26 @@
         <v>0</v>
       </c>
       <c r="E242" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5" ht="14" customHeight="1">
+      <c r="A243" s="6">
+        <f t="shared" si="2"/>
+        <v>242</v>
+      </c>
+      <c r="B243" s="7">
+        <f t="shared" si="12"/>
+        <v>46323</v>
+      </c>
+      <c r="C243" s="6">
+        <f>C242+1</f>
+        <v>6</v>
+      </c>
+      <c r="D243" s="13">
+        <v>0</v>
+      </c>
+      <c r="E243" s="13">
         <v>0</v>
       </c>
     </row>
@@ -15448,7 +15468,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E31F5C3B-0571-4A35-9FD2-A50C21726EAB}">
-  <dimension ref="A1:J857"/>
+  <dimension ref="A1:J859"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="11.36328125" bestFit="1" customWidth="1"/>
@@ -39239,7 +39259,7 @@
     </row>
     <row r="722" spans="1:10">
       <c r="A722" s="24">
-        <f t="shared" ref="A722:A856" si="14">A720+1</f>
+        <f t="shared" ref="A722:A858" si="14">A720+1</f>
         <v>46255</v>
       </c>
       <c r="B722" s="23" t="s">
@@ -41384,7 +41404,7 @@
     </row>
     <row r="787" spans="1:10">
       <c r="A787" s="24">
-        <f t="shared" ref="A787:A857" si="15">A785+1</f>
+        <f t="shared" ref="A787:A859" si="15">A785+1</f>
         <v>46287</v>
       </c>
       <c r="B787" s="23" t="s">
@@ -43722,6 +43742,72 @@
         <v>0</v>
       </c>
       <c r="J857" s="31">
+        <v>4.1000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="858" spans="1:10">
+      <c r="A858" s="24">
+        <f t="shared" si="14"/>
+        <v>46323</v>
+      </c>
+      <c r="B858" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C858" s="25">
+        <v>26443776</v>
+      </c>
+      <c r="D858" s="25">
+        <v>0</v>
+      </c>
+      <c r="E858" s="25">
+        <v>1712144</v>
+      </c>
+      <c r="F858" s="25">
+        <v>313531</v>
+      </c>
+      <c r="G858" s="25">
+        <v>28469451</v>
+      </c>
+      <c r="H858" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I858" s="27">
+        <v>0</v>
+      </c>
+      <c r="J858" s="31">
+        <v>4.1000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="859" spans="1:10">
+      <c r="A859" s="24">
+        <f t="shared" si="15"/>
+        <v>46323</v>
+      </c>
+      <c r="B859" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C859" s="25">
+        <v>26443776</v>
+      </c>
+      <c r="D859" s="25">
+        <v>0</v>
+      </c>
+      <c r="E859" s="25">
+        <v>1712144</v>
+      </c>
+      <c r="F859" s="25">
+        <v>313531</v>
+      </c>
+      <c r="G859" s="25">
+        <v>28469451</v>
+      </c>
+      <c r="H859" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I859" s="27">
+        <v>0</v>
+      </c>
+      <c r="J859" s="31">
         <v>4.1000000000000002E-2</v>
       </c>
     </row>

--- a/public/data/record.xlsx
+++ b/public/data/record.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\cursor-usage\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{295B4B81-CC7F-459E-8A6C-F1BB43C5BA19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D649B2EE-6317-4070-AFE4-D52A9D01B4F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1272" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1276" uniqueCount="31">
   <si>
     <t>番号</t>
   </si>
@@ -10713,7 +10713,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92559261-86B2-49A9-AE5C-FC3176987B65}">
-  <dimension ref="A1:E243"/>
+  <dimension ref="A1:E244"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="5.453125" bestFit="1" customWidth="1"/>
@@ -12108,7 +12108,7 @@
     </row>
     <row r="74" spans="1:5" s="5" customFormat="1" ht="14.5">
       <c r="A74" s="6">
-        <f t="shared" ref="A74:A243" si="2">ROW()-1</f>
+        <f t="shared" ref="A74:A244" si="2">ROW()-1</f>
         <v>73</v>
       </c>
       <c r="B74" s="7">
@@ -14167,7 +14167,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="7">
-        <f t="shared" ref="B179:B243" si="12">B178+1</f>
+        <f t="shared" ref="B179:B244" si="12">B178+1</f>
         <v>46259</v>
       </c>
       <c r="C179" s="6">
@@ -15456,6 +15456,26 @@
         <v>0</v>
       </c>
       <c r="E243" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5" ht="14" customHeight="1">
+      <c r="A244" s="6">
+        <f t="shared" si="2"/>
+        <v>243</v>
+      </c>
+      <c r="B244" s="7">
+        <f t="shared" si="12"/>
+        <v>46324</v>
+      </c>
+      <c r="C244" s="6">
+        <f>C243+1</f>
+        <v>7</v>
+      </c>
+      <c r="D244" s="13">
+        <v>74</v>
+      </c>
+      <c r="E244" s="13">
         <v>0</v>
       </c>
     </row>
@@ -15468,7 +15488,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E31F5C3B-0571-4A35-9FD2-A50C21726EAB}">
-  <dimension ref="A1:J859"/>
+  <dimension ref="A1:J861"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="11.36328125" bestFit="1" customWidth="1"/>
@@ -39259,7 +39279,7 @@
     </row>
     <row r="722" spans="1:10">
       <c r="A722" s="24">
-        <f t="shared" ref="A722:A858" si="14">A720+1</f>
+        <f t="shared" ref="A722:A860" si="14">A720+1</f>
         <v>46255</v>
       </c>
       <c r="B722" s="23" t="s">
@@ -41404,7 +41424,7 @@
     </row>
     <row r="787" spans="1:10">
       <c r="A787" s="24">
-        <f t="shared" ref="A787:A859" si="15">A785+1</f>
+        <f t="shared" ref="A787:A861" si="15">A785+1</f>
         <v>46287</v>
       </c>
       <c r="B787" s="23" t="s">
@@ -43809,6 +43829,72 @@
       </c>
       <c r="J859" s="31">
         <v>4.1000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="860" spans="1:10">
+      <c r="A860" s="24">
+        <f t="shared" si="14"/>
+        <v>46324</v>
+      </c>
+      <c r="B860" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C860" s="25">
+        <v>29052928</v>
+      </c>
+      <c r="D860" s="25">
+        <v>0</v>
+      </c>
+      <c r="E860" s="25">
+        <v>2189683</v>
+      </c>
+      <c r="F860" s="25">
+        <v>368267</v>
+      </c>
+      <c r="G860" s="25">
+        <v>31610878</v>
+      </c>
+      <c r="H860" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I860" s="27">
+        <v>0</v>
+      </c>
+      <c r="J860" s="31">
+        <v>4.7E-2</v>
+      </c>
+    </row>
+    <row r="861" spans="1:10">
+      <c r="A861" s="24">
+        <f t="shared" si="15"/>
+        <v>46324</v>
+      </c>
+      <c r="B861" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C861" s="25">
+        <v>29052928</v>
+      </c>
+      <c r="D861" s="25">
+        <v>0</v>
+      </c>
+      <c r="E861" s="25">
+        <v>2189683</v>
+      </c>
+      <c r="F861" s="25">
+        <v>368267</v>
+      </c>
+      <c r="G861" s="25">
+        <v>31610878</v>
+      </c>
+      <c r="H861" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I861" s="27">
+        <v>0</v>
+      </c>
+      <c r="J861" s="31">
+        <v>4.7E-2</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/record.xlsx
+++ b/public/data/record.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\cursor-usage\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D649B2EE-6317-4070-AFE4-D52A9D01B4F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{558752A1-F391-453B-ABEE-2744CAC05C7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19020" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cursor Usageの記録" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1276" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1284" uniqueCount="32">
   <si>
     <t>番号</t>
   </si>
@@ -157,6 +157,10 @@
   </si>
   <si>
     <t>Included</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>gpt-5.6-sol-medium</t>
     <phoneticPr fontId="4"/>
   </si>
 </sst>
@@ -10713,7 +10717,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92559261-86B2-49A9-AE5C-FC3176987B65}">
-  <dimension ref="A1:E244"/>
+  <dimension ref="A1:E245"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="5.453125" bestFit="1" customWidth="1"/>
@@ -12108,7 +12112,7 @@
     </row>
     <row r="74" spans="1:5" s="5" customFormat="1" ht="14.5">
       <c r="A74" s="6">
-        <f t="shared" ref="A74:A244" si="2">ROW()-1</f>
+        <f t="shared" ref="A74:A245" si="2">ROW()-1</f>
         <v>73</v>
       </c>
       <c r="B74" s="7">
@@ -14167,7 +14171,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="7">
-        <f t="shared" ref="B179:B244" si="12">B178+1</f>
+        <f t="shared" ref="B179:B245" si="12">B178+1</f>
         <v>46259</v>
       </c>
       <c r="C179" s="6">
@@ -15369,7 +15373,7 @@
         <v>46319</v>
       </c>
       <c r="C239" s="6">
-        <f>C238+1</f>
+        <f t="shared" ref="C239:C244" si="14">C238+1</f>
         <v>2</v>
       </c>
       <c r="D239" s="13">
@@ -15389,7 +15393,7 @@
         <v>46320</v>
       </c>
       <c r="C240" s="6">
-        <f>C239+1</f>
+        <f t="shared" si="14"/>
         <v>3</v>
       </c>
       <c r="D240" s="13">
@@ -15409,7 +15413,7 @@
         <v>46321</v>
       </c>
       <c r="C241" s="6">
-        <f>C240+1</f>
+        <f t="shared" si="14"/>
         <v>4</v>
       </c>
       <c r="D241" s="13">
@@ -15429,7 +15433,7 @@
         <v>46322</v>
       </c>
       <c r="C242" s="6">
-        <f>C241+1</f>
+        <f t="shared" si="14"/>
         <v>5</v>
       </c>
       <c r="D242" s="13">
@@ -15449,7 +15453,7 @@
         <v>46323</v>
       </c>
       <c r="C243" s="6">
-        <f>C242+1</f>
+        <f t="shared" si="14"/>
         <v>6</v>
       </c>
       <c r="D243" s="13">
@@ -15469,13 +15473,33 @@
         <v>46324</v>
       </c>
       <c r="C244" s="6">
-        <f>C243+1</f>
+        <f t="shared" si="14"/>
         <v>7</v>
       </c>
       <c r="D244" s="13">
         <v>74</v>
       </c>
       <c r="E244" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5" ht="14" customHeight="1">
+      <c r="A245" s="6">
+        <f t="shared" si="2"/>
+        <v>244</v>
+      </c>
+      <c r="B245" s="7">
+        <f t="shared" si="12"/>
+        <v>46325</v>
+      </c>
+      <c r="C245" s="6">
+        <f t="shared" ref="C245" si="15">C244+1</f>
+        <v>8</v>
+      </c>
+      <c r="D245" s="13">
+        <v>1683</v>
+      </c>
+      <c r="E245" s="13">
         <v>0</v>
       </c>
     </row>
@@ -15488,7 +15512,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E31F5C3B-0571-4A35-9FD2-A50C21726EAB}">
-  <dimension ref="A1:J861"/>
+  <dimension ref="A1:J865"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="11.36328125" bestFit="1" customWidth="1"/>
@@ -39279,7 +39303,7 @@
     </row>
     <row r="722" spans="1:10">
       <c r="A722" s="24">
-        <f t="shared" ref="A722:A860" si="14">A720+1</f>
+        <f t="shared" ref="A722:A864" si="14">A720+1</f>
         <v>46255</v>
       </c>
       <c r="B722" s="23" t="s">
@@ -41424,7 +41448,7 @@
     </row>
     <row r="787" spans="1:10">
       <c r="A787" s="24">
-        <f t="shared" ref="A787:A861" si="15">A785+1</f>
+        <f t="shared" ref="A787:A865" si="15">A785+1</f>
         <v>46287</v>
       </c>
       <c r="B787" s="23" t="s">
@@ -43895,6 +43919,138 @@
       </c>
       <c r="J861" s="31">
         <v>4.7E-2</v>
+      </c>
+    </row>
+    <row r="862" spans="1:10">
+      <c r="A862" s="24">
+        <f t="shared" si="14"/>
+        <v>46325</v>
+      </c>
+      <c r="B862" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C862" s="25">
+        <v>39600896</v>
+      </c>
+      <c r="D862" s="25">
+        <v>0</v>
+      </c>
+      <c r="E862" s="25">
+        <v>2779139</v>
+      </c>
+      <c r="F862" s="25">
+        <v>475678</v>
+      </c>
+      <c r="G862" s="25">
+        <v>42855713</v>
+      </c>
+      <c r="H862" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I862" s="27">
+        <v>0</v>
+      </c>
+      <c r="J862" s="31">
+        <v>6.3E-2</v>
+      </c>
+    </row>
+    <row r="863" spans="1:10">
+      <c r="A863" s="24">
+        <f t="shared" si="15"/>
+        <v>46325</v>
+      </c>
+      <c r="B863" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C863" s="25">
+        <v>39600896</v>
+      </c>
+      <c r="D863" s="25">
+        <v>0</v>
+      </c>
+      <c r="E863" s="25">
+        <v>2779139</v>
+      </c>
+      <c r="F863" s="25">
+        <v>475678</v>
+      </c>
+      <c r="G863" s="25">
+        <v>42855713</v>
+      </c>
+      <c r="H863" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I863" s="27">
+        <v>0</v>
+      </c>
+      <c r="J863" s="31">
+        <v>6.3E-2</v>
+      </c>
+    </row>
+    <row r="864" spans="1:10">
+      <c r="A864" s="24">
+        <f>A860+1</f>
+        <v>46325</v>
+      </c>
+      <c r="B864" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="C864" s="25">
+        <v>425711</v>
+      </c>
+      <c r="D864" s="25">
+        <v>99127</v>
+      </c>
+      <c r="E864" s="25">
+        <v>45</v>
+      </c>
+      <c r="F864" s="25">
+        <v>11440</v>
+      </c>
+      <c r="G864" s="25">
+        <v>536323</v>
+      </c>
+      <c r="H864" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I864" s="27">
+        <v>0</v>
+      </c>
+      <c r="J864" s="31">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="865" spans="1:10">
+      <c r="A865" s="24">
+        <f>A861+1</f>
+        <v>46325</v>
+      </c>
+      <c r="B865" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="C865" s="25">
+        <v>425711</v>
+      </c>
+      <c r="D865" s="25">
+        <v>99127</v>
+      </c>
+      <c r="E865" s="25">
+        <v>45</v>
+      </c>
+      <c r="F865" s="25">
+        <v>11440</v>
+      </c>
+      <c r="G865" s="25">
+        <v>536323</v>
+      </c>
+      <c r="H865" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I865" s="27">
+        <v>0</v>
+      </c>
+      <c r="J865" s="31">
+        <v>0.02</v>
       </c>
     </row>
   </sheetData>
